--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10765,13 +10765,13 @@
         <v>6259348</v>
       </c>
       <c r="H258" t="n">
-        <v>4103866.22</v>
+        <v>4166945.97</v>
       </c>
       <c r="I258" t="n">
-        <v>395111.47</v>
+        <v>405771.94</v>
       </c>
       <c r="J258" t="n">
-        <v>2155481.78</v>
+        <v>2092402.03</v>
       </c>
     </row>
     <row r="259">
@@ -14085,13 +14085,13 @@
         <v>24865514.03</v>
       </c>
       <c r="H341" t="n">
-        <v>19081139.9</v>
+        <v>19326094.83</v>
       </c>
       <c r="I341" t="n">
-        <v>1866858.42</v>
+        <v>1904605.97</v>
       </c>
       <c r="J341" t="n">
-        <v>5784374.13</v>
+        <v>5539419.2</v>
       </c>
     </row>
     <row r="342">
@@ -19605,13 +19605,13 @@
         <v>36255903.57</v>
       </c>
       <c r="H479" t="n">
-        <v>29682574.51</v>
+        <v>29691073.84</v>
       </c>
       <c r="I479" t="n">
-        <v>1537266.09</v>
+        <v>1538612.38</v>
       </c>
       <c r="J479" t="n">
-        <v>6573329.06</v>
+        <v>6564829.73</v>
       </c>
     </row>
     <row r="480">
@@ -19685,13 +19685,13 @@
         <v>34335611.48</v>
       </c>
       <c r="H481" t="n">
-        <v>1088863.01</v>
+        <v>1218346.34</v>
       </c>
       <c r="I481" t="n">
-        <v>38320.24</v>
+        <v>44782.51</v>
       </c>
       <c r="J481" t="n">
-        <v>33246748.47</v>
+        <v>33117265.14</v>
       </c>
     </row>
     <row r="482">
@@ -21405,13 +21405,13 @@
         <v>2867205</v>
       </c>
       <c r="H524" t="n">
-        <v>2405449.02</v>
+        <v>2496053.43</v>
       </c>
       <c r="I524" t="n">
-        <v>560999.49</v>
+        <v>586504.63</v>
       </c>
       <c r="J524" t="n">
-        <v>461755.98</v>
+        <v>371151.57</v>
       </c>
     </row>
     <row r="525">
@@ -23525,13 +23525,13 @@
         <v>31994041.87</v>
       </c>
       <c r="H577" t="n">
-        <v>27718358.53</v>
+        <v>28187412.61</v>
       </c>
       <c r="I577" t="n">
-        <v>1647276.72</v>
+        <v>1706546.64</v>
       </c>
       <c r="J577" t="n">
-        <v>4275683.34</v>
+        <v>3806629.26</v>
       </c>
     </row>
     <row r="578">
@@ -25325,13 +25325,13 @@
         <v>11569905.95</v>
       </c>
       <c r="H622" t="n">
-        <v>5627585.97</v>
+        <v>6145327.29</v>
       </c>
       <c r="I622" t="n">
-        <v>167893.21</v>
+        <v>186278.45</v>
       </c>
       <c r="J622" t="n">
-        <v>5942319.98</v>
+        <v>5424578.66</v>
       </c>
     </row>
     <row r="623">
@@ -25485,13 +25485,13 @@
         <v>21765965.24</v>
       </c>
       <c r="H626" t="n">
-        <v>6163693.81</v>
+        <v>6971429.23</v>
       </c>
       <c r="I626" t="n">
-        <v>252711.38</v>
+        <v>312645.34</v>
       </c>
       <c r="J626" t="n">
-        <v>15602271.43</v>
+        <v>14794536.01</v>
       </c>
     </row>
     <row r="627">
@@ -25805,13 +25805,13 @@
         <v>5978999.99</v>
       </c>
       <c r="H634" t="n">
-        <v>1968382.06</v>
+        <v>2046657.96</v>
       </c>
       <c r="I634" t="n">
         <v>0</v>
       </c>
       <c r="J634" t="n">
-        <v>4010617.93</v>
+        <v>3932342.03</v>
       </c>
     </row>
     <row r="635">
@@ -25845,13 +25845,13 @@
         <v>181409015</v>
       </c>
       <c r="H635" t="n">
-        <v>12779560.18</v>
+        <v>16670167.3</v>
       </c>
       <c r="I635" t="n">
-        <v>57885.95</v>
+        <v>120439.75</v>
       </c>
       <c r="J635" t="n">
-        <v>168629454.82</v>
+        <v>164738847.7</v>
       </c>
     </row>
     <row r="636">
@@ -26205,13 +26205,13 @@
         <v>1935938.33</v>
       </c>
       <c r="H644" t="n">
-        <v>218527.45</v>
+        <v>273980.42</v>
       </c>
       <c r="I644" t="n">
-        <v>6010.71</v>
+        <v>8012.56</v>
       </c>
       <c r="J644" t="n">
-        <v>1717410.88</v>
+        <v>1661957.91</v>
       </c>
     </row>
     <row r="645">
@@ -26365,13 +26365,13 @@
         <v>5903947.49</v>
       </c>
       <c r="H648" t="n">
-        <v>153306.65</v>
+        <v>255873.45</v>
       </c>
       <c r="I648" t="n">
-        <v>2372.81</v>
+        <v>6075.47</v>
       </c>
       <c r="J648" t="n">
-        <v>5750640.84</v>
+        <v>5648074.04</v>
       </c>
     </row>
     <row r="649">
@@ -26405,13 +26405,13 @@
         <v>1152374.25</v>
       </c>
       <c r="H649" t="n">
-        <v>68518.28</v>
+        <v>112684.5</v>
       </c>
       <c r="I649" t="n">
-        <v>1556.95</v>
+        <v>3151.35</v>
       </c>
       <c r="J649" t="n">
-        <v>1083855.97</v>
+        <v>1039689.75</v>
       </c>
     </row>
     <row r="650">
@@ -28045,13 +28045,13 @@
         <v>2363126.32</v>
       </c>
       <c r="H690" t="n">
-        <v>774057.36</v>
+        <v>779075.34</v>
       </c>
       <c r="I690" t="n">
-        <v>73226.34</v>
+        <v>73999.61</v>
       </c>
       <c r="J690" t="n">
-        <v>1589068.96</v>
+        <v>1584050.98</v>
       </c>
     </row>
     <row r="691">
@@ -28205,13 +28205,13 @@
         <v>891896.45</v>
       </c>
       <c r="H694" t="n">
-        <v>415627.84</v>
+        <v>465765.29</v>
       </c>
       <c r="I694" t="n">
-        <v>43114.53</v>
+        <v>50840.71</v>
       </c>
       <c r="J694" t="n">
-        <v>476268.61</v>
+        <v>426131.16</v>
       </c>
     </row>
     <row r="695">
@@ -31325,13 +31325,13 @@
         <v>47556790.26</v>
       </c>
       <c r="H772" t="n">
-        <v>29227276.55</v>
+        <v>30046325.33</v>
       </c>
       <c r="I772" t="n">
-        <v>1198761.02</v>
+        <v>1241995.65</v>
       </c>
       <c r="J772" t="n">
-        <v>18329513.71</v>
+        <v>17510464.93</v>
       </c>
     </row>
     <row r="773">
@@ -31565,13 +31565,13 @@
         <v>47758833.23</v>
       </c>
       <c r="H778" t="n">
-        <v>24425482.74</v>
+        <v>25863099.21</v>
       </c>
       <c r="I778" t="n">
-        <v>956916.6</v>
+        <v>1032030.54</v>
       </c>
       <c r="J778" t="n">
-        <v>23333350.49</v>
+        <v>21895734.02</v>
       </c>
     </row>
     <row r="779">
@@ -31885,13 +31885,13 @@
         <v>61821473.21</v>
       </c>
       <c r="H786" t="n">
-        <v>45621127.04</v>
+        <v>45821274.56</v>
       </c>
       <c r="I786" t="n">
-        <v>1365904.41</v>
+        <v>1373475.56</v>
       </c>
       <c r="J786" t="n">
-        <v>16200346.17</v>
+        <v>16000198.65</v>
       </c>
     </row>
     <row r="787">
@@ -32805,13 +32805,13 @@
         <v>4776981.58</v>
       </c>
       <c r="H809" t="n">
-        <v>2325981.28</v>
+        <v>2691068.21</v>
       </c>
       <c r="I809" t="n">
-        <v>69304.95</v>
+        <v>84648.03999999999</v>
       </c>
       <c r="J809" t="n">
-        <v>2451000.3</v>
+        <v>2085913.37</v>
       </c>
     </row>
     <row r="810">
@@ -34405,13 +34405,13 @@
         <v>24309955.5</v>
       </c>
       <c r="H849" t="n">
-        <v>12680602.25</v>
+        <v>13284295.25</v>
       </c>
       <c r="I849" t="n">
-        <v>43244.23</v>
+        <v>74469.48</v>
       </c>
       <c r="J849" t="n">
-        <v>11629353.25</v>
+        <v>11025660.25</v>
       </c>
     </row>
     <row r="850">
@@ -34685,13 +34685,13 @@
         <v>2624909.09</v>
       </c>
       <c r="H856" t="n">
-        <v>0</v>
+        <v>59420.08</v>
       </c>
       <c r="I856" t="n">
         <v>0</v>
       </c>
       <c r="J856" t="n">
-        <v>2624909.09</v>
+        <v>2565489.01</v>
       </c>
     </row>
     <row r="857">
@@ -35845,13 +35845,13 @@
         <v>1076033.27</v>
       </c>
       <c r="H885" t="n">
-        <v>20644.37</v>
+        <v>44657.22</v>
       </c>
       <c r="I885" t="n">
-        <v>0</v>
+        <v>1395.14</v>
       </c>
       <c r="J885" t="n">
-        <v>1055388.9</v>
+        <v>1031376.05</v>
       </c>
     </row>
     <row r="886">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -3365,13 +3365,13 @@
         <v>10345741.94</v>
       </c>
       <c r="H73" t="n">
-        <v>9209284.949999999</v>
+        <v>9910778.640000001</v>
       </c>
       <c r="I73" t="n">
-        <v>3741239.22</v>
+        <v>4089109.93</v>
       </c>
       <c r="J73" t="n">
-        <v>1136456.99</v>
+        <v>434963.3</v>
       </c>
     </row>
     <row r="74">
@@ -5885,13 +5885,13 @@
         <v>60076721.44</v>
       </c>
       <c r="H136" t="n">
-        <v>50710844.54</v>
+        <v>50791767.14</v>
       </c>
       <c r="I136" t="n">
-        <v>10867833.27</v>
+        <v>10888629.1</v>
       </c>
       <c r="J136" t="n">
-        <v>9365876.9</v>
+        <v>9284954.300000001</v>
       </c>
     </row>
     <row r="137">
@@ -21245,13 +21245,13 @@
         <v>2926844.27</v>
       </c>
       <c r="H520" t="n">
-        <v>2039847.63</v>
+        <v>2135466.77</v>
       </c>
       <c r="I520" t="n">
-        <v>184234.68</v>
+        <v>197841.28</v>
       </c>
       <c r="J520" t="n">
-        <v>886996.64</v>
+        <v>791377.5</v>
       </c>
     </row>
     <row r="521">
@@ -21285,13 +21285,13 @@
         <v>2334223.12</v>
       </c>
       <c r="H521" t="n">
-        <v>1305034.14</v>
+        <v>1376723.51</v>
       </c>
       <c r="I521" t="n">
-        <v>116078.65</v>
+        <v>126280.04</v>
       </c>
       <c r="J521" t="n">
-        <v>1029188.98</v>
+        <v>957499.61</v>
       </c>
     </row>
     <row r="522">
@@ -23685,13 +23685,13 @@
         <v>27994383.03</v>
       </c>
       <c r="H581" t="n">
-        <v>18451942.87</v>
+        <v>18713554.37</v>
       </c>
       <c r="I581" t="n">
-        <v>3015037.13</v>
+        <v>3070775.51</v>
       </c>
       <c r="J581" t="n">
-        <v>9542440.16</v>
+        <v>9280828.66</v>
       </c>
     </row>
     <row r="582">
@@ -23725,13 +23725,13 @@
         <v>8190120.05</v>
       </c>
       <c r="H582" t="n">
-        <v>1635756.38</v>
+        <v>1697483.94</v>
       </c>
       <c r="I582" t="n">
-        <v>129077.07</v>
+        <v>136218.94</v>
       </c>
       <c r="J582" t="n">
-        <v>6554363.67</v>
+        <v>6492636.11</v>
       </c>
     </row>
     <row r="583">
@@ -23885,13 +23885,13 @@
         <v>33721624.27</v>
       </c>
       <c r="H586" t="n">
-        <v>16663696.96</v>
+        <v>17120516.56</v>
       </c>
       <c r="I586" t="n">
-        <v>923669.6</v>
+        <v>972473.9</v>
       </c>
       <c r="J586" t="n">
-        <v>17057927.31</v>
+        <v>16601107.71</v>
       </c>
     </row>
     <row r="587">
@@ -24605,13 +24605,13 @@
         <v>28277547.59</v>
       </c>
       <c r="H604" t="n">
-        <v>23519638.18</v>
+        <v>24320830.23</v>
       </c>
       <c r="I604" t="n">
         <v>970501.73</v>
       </c>
       <c r="J604" t="n">
-        <v>4757909.41</v>
+        <v>3956717.36</v>
       </c>
     </row>
     <row r="605">
@@ -24845,13 +24845,13 @@
         <v>13130895.05</v>
       </c>
       <c r="H610" t="n">
-        <v>5307831.93</v>
+        <v>5380311.26</v>
       </c>
       <c r="I610" t="n">
-        <v>640244.16</v>
+        <v>652192.1800000001</v>
       </c>
       <c r="J610" t="n">
-        <v>7823063.12</v>
+        <v>7750583.79</v>
       </c>
     </row>
     <row r="611">
@@ -25399,19 +25399,19 @@
         <v>25953920.64</v>
       </c>
       <c r="F624" t="n">
-        <v>0</v>
+        <v>4918151.66</v>
       </c>
       <c r="G624" t="n">
-        <v>25953920.64</v>
+        <v>30872072.3</v>
       </c>
       <c r="H624" t="n">
-        <v>2651758.01</v>
+        <v>3148412.06</v>
       </c>
       <c r="I624" t="n">
-        <v>51351.27</v>
+        <v>69280.47</v>
       </c>
       <c r="J624" t="n">
-        <v>23302162.63</v>
+        <v>27723660.24</v>
       </c>
     </row>
     <row r="625">
@@ -25445,13 +25445,13 @@
         <v>1453805.42</v>
       </c>
       <c r="H625" t="n">
-        <v>1056981.69</v>
+        <v>1076354.4</v>
       </c>
       <c r="I625" t="n">
-        <v>24350.53</v>
+        <v>25117.68</v>
       </c>
       <c r="J625" t="n">
-        <v>396823.73</v>
+        <v>377451.02</v>
       </c>
     </row>
     <row r="626">
@@ -25605,13 +25605,13 @@
         <v>3900717.4</v>
       </c>
       <c r="H629" t="n">
-        <v>1163016.5</v>
+        <v>1379727.43</v>
       </c>
       <c r="I629" t="n">
-        <v>593487.28</v>
+        <v>704074.86</v>
       </c>
       <c r="J629" t="n">
-        <v>2737700.9</v>
+        <v>2520989.97</v>
       </c>
     </row>
     <row r="630">
@@ -25685,13 +25685,13 @@
         <v>44573000</v>
       </c>
       <c r="H631" t="n">
-        <v>3589416.22</v>
+        <v>4087799.31</v>
       </c>
       <c r="I631" t="n">
-        <v>38056.94</v>
+        <v>50292.73</v>
       </c>
       <c r="J631" t="n">
-        <v>40983583.78</v>
+        <v>40485200.69</v>
       </c>
     </row>
     <row r="632">
@@ -25965,13 +25965,13 @@
         <v>2994277.86</v>
       </c>
       <c r="H638" t="n">
-        <v>705769.7</v>
+        <v>826233.28</v>
       </c>
       <c r="I638" t="n">
-        <v>52297.51</v>
+        <v>61223.86</v>
       </c>
       <c r="J638" t="n">
-        <v>2288508.16</v>
+        <v>2168044.58</v>
       </c>
     </row>
     <row r="639">
@@ -26045,13 +26045,13 @@
         <v>4296601.11</v>
       </c>
       <c r="H640" t="n">
-        <v>366048.49</v>
+        <v>464999.03</v>
       </c>
       <c r="I640" t="n">
-        <v>12098.05</v>
+        <v>15670.14</v>
       </c>
       <c r="J640" t="n">
-        <v>3930552.62</v>
+        <v>3831602.08</v>
       </c>
     </row>
     <row r="641">
@@ -26085,13 +26085,13 @@
         <v>1064844.54</v>
       </c>
       <c r="H641" t="n">
-        <v>430287.11</v>
+        <v>486604.48</v>
       </c>
       <c r="I641" t="n">
-        <v>23372.85</v>
+        <v>26960.26</v>
       </c>
       <c r="J641" t="n">
-        <v>634557.4300000001</v>
+        <v>578240.0600000001</v>
       </c>
     </row>
     <row r="642">
@@ -26165,13 +26165,13 @@
         <v>6871059.81</v>
       </c>
       <c r="H643" t="n">
-        <v>186873.93</v>
+        <v>244069.39</v>
       </c>
       <c r="I643" t="n">
         <v>0</v>
       </c>
       <c r="J643" t="n">
-        <v>6684185.88</v>
+        <v>6626990.42</v>
       </c>
     </row>
     <row r="644">
@@ -26485,13 +26485,13 @@
         <v>526403.28</v>
       </c>
       <c r="H651" t="n">
-        <v>42325.25</v>
+        <v>46939.31</v>
       </c>
       <c r="I651" t="n">
-        <v>1236.25</v>
+        <v>1402.81</v>
       </c>
       <c r="J651" t="n">
-        <v>484078.03</v>
+        <v>479463.97</v>
       </c>
     </row>
     <row r="652">
@@ -26525,13 +26525,13 @@
         <v>522440.12</v>
       </c>
       <c r="H652" t="n">
-        <v>69164.92</v>
+        <v>87532.48</v>
       </c>
       <c r="I652" t="n">
-        <v>2496.84</v>
+        <v>3159.9</v>
       </c>
       <c r="J652" t="n">
-        <v>453275.2</v>
+        <v>434907.64</v>
       </c>
     </row>
     <row r="653">
@@ -26645,13 +26645,13 @@
         <v>930110.42</v>
       </c>
       <c r="H655" t="n">
-        <v>63820.58</v>
+        <v>103610.35</v>
       </c>
       <c r="I655" t="n">
-        <v>1586.38</v>
+        <v>3022.79</v>
       </c>
       <c r="J655" t="n">
-        <v>866289.84</v>
+        <v>826500.0699999999</v>
       </c>
     </row>
     <row r="656">
@@ -26725,13 +26725,13 @@
         <v>454802.11</v>
       </c>
       <c r="H657" t="n">
-        <v>61743.96</v>
+        <v>85793.13</v>
       </c>
       <c r="I657" t="n">
-        <v>2228.95</v>
+        <v>3097.12</v>
       </c>
       <c r="J657" t="n">
-        <v>393058.15</v>
+        <v>369008.98</v>
       </c>
     </row>
     <row r="658">
@@ -26805,13 +26805,13 @@
         <v>550759.72</v>
       </c>
       <c r="H659" t="n">
-        <v>64252.66</v>
+        <v>76382.64</v>
       </c>
       <c r="I659" t="n">
-        <v>2319.5</v>
+        <v>2757.39</v>
       </c>
       <c r="J659" t="n">
-        <v>486507.06</v>
+        <v>474377.08</v>
       </c>
     </row>
     <row r="660">
@@ -26885,13 +26885,13 @@
         <v>8799802.35</v>
       </c>
       <c r="H661" t="n">
-        <v>265984.68</v>
+        <v>342819.75</v>
       </c>
       <c r="I661" t="n">
-        <v>0</v>
+        <v>4464.11</v>
       </c>
       <c r="J661" t="n">
-        <v>8533817.67</v>
+        <v>8456982.6</v>
       </c>
     </row>
     <row r="662">
@@ -27445,13 +27445,13 @@
         <v>864235.72</v>
       </c>
       <c r="H675" t="n">
-        <v>211109.54</v>
+        <v>212331.48</v>
       </c>
       <c r="I675" t="n">
-        <v>21018.14</v>
+        <v>21206.44</v>
       </c>
       <c r="J675" t="n">
-        <v>653126.1800000001</v>
+        <v>651904.24</v>
       </c>
     </row>
     <row r="676">
@@ -27485,13 +27485,13 @@
         <v>634467.04</v>
       </c>
       <c r="H676" t="n">
-        <v>155065.55</v>
+        <v>155920.32</v>
       </c>
       <c r="I676" t="n">
-        <v>16172.56</v>
+        <v>16304.28</v>
       </c>
       <c r="J676" t="n">
-        <v>479401.49</v>
+        <v>478546.72</v>
       </c>
     </row>
     <row r="677">
@@ -27525,13 +27525,13 @@
         <v>1131117.06</v>
       </c>
       <c r="H677" t="n">
-        <v>706224.88</v>
+        <v>748993.38</v>
       </c>
       <c r="I677" t="n">
-        <v>75738.50999999999</v>
+        <v>82329.13</v>
       </c>
       <c r="J677" t="n">
-        <v>424892.18</v>
+        <v>382123.68</v>
       </c>
     </row>
     <row r="678">
@@ -27645,13 +27645,13 @@
         <v>1720953.51</v>
       </c>
       <c r="H680" t="n">
-        <v>1348606.01</v>
+        <v>1355967.86</v>
       </c>
       <c r="I680" t="n">
-        <v>145355.57</v>
+        <v>146490.03</v>
       </c>
       <c r="J680" t="n">
-        <v>372347.5</v>
+        <v>364985.65</v>
       </c>
     </row>
     <row r="681">
@@ -27685,13 +27685,13 @@
         <v>410983.4</v>
       </c>
       <c r="H681" t="n">
-        <v>104919.5</v>
+        <v>105834.09</v>
       </c>
       <c r="I681" t="n">
-        <v>10472.18</v>
+        <v>10613.11</v>
       </c>
       <c r="J681" t="n">
-        <v>306063.9</v>
+        <v>305149.31</v>
       </c>
     </row>
     <row r="682">
@@ -29645,13 +29645,13 @@
         <v>269217.53</v>
       </c>
       <c r="H730" t="n">
-        <v>86964.60000000001</v>
+        <v>88707.60000000001</v>
       </c>
       <c r="I730" t="n">
-        <v>6770.21</v>
+        <v>6995.4</v>
       </c>
       <c r="J730" t="n">
-        <v>182252.93</v>
+        <v>180509.93</v>
       </c>
     </row>
     <row r="731">
@@ -29845,13 +29845,13 @@
         <v>75139.77</v>
       </c>
       <c r="H735" t="n">
-        <v>50707.36</v>
+        <v>54825.8</v>
       </c>
       <c r="I735" t="n">
-        <v>3866.34</v>
+        <v>4398.44</v>
       </c>
       <c r="J735" t="n">
-        <v>24432.41</v>
+        <v>20313.97</v>
       </c>
     </row>
     <row r="736">
@@ -30965,13 +30965,13 @@
         <v>9873282.51</v>
       </c>
       <c r="H763" t="n">
-        <v>4198184.38</v>
+        <v>4423778.37</v>
       </c>
       <c r="I763" t="n">
-        <v>332637.85</v>
+        <v>358739.07</v>
       </c>
       <c r="J763" t="n">
-        <v>5675098.13</v>
+        <v>5449504.14</v>
       </c>
     </row>
     <row r="764">
@@ -31085,13 +31085,13 @@
         <v>19392294.81</v>
       </c>
       <c r="H766" t="n">
-        <v>8215439.39</v>
+        <v>10012154.47</v>
       </c>
       <c r="I766" t="n">
-        <v>640198.8</v>
+        <v>870537.67</v>
       </c>
       <c r="J766" t="n">
-        <v>11176855.42</v>
+        <v>9380140.34</v>
       </c>
     </row>
     <row r="767">
@@ -31805,13 +31805,13 @@
         <v>7150184.18</v>
       </c>
       <c r="H784" t="n">
-        <v>255646.39</v>
+        <v>312841.85</v>
       </c>
       <c r="I784" t="n">
         <v>3596.79</v>
       </c>
       <c r="J784" t="n">
-        <v>6894537.79</v>
+        <v>6837342.33</v>
       </c>
     </row>
     <row r="785">
@@ -32005,13 +32005,13 @@
         <v>13375792.1</v>
       </c>
       <c r="H789" t="n">
-        <v>9485353.26</v>
+        <v>9920529.5</v>
       </c>
       <c r="I789" t="n">
-        <v>643443.58</v>
+        <v>694838.84</v>
       </c>
       <c r="J789" t="n">
-        <v>3890438.84</v>
+        <v>3455262.6</v>
       </c>
     </row>
     <row r="790">
@@ -32045,13 +32045,13 @@
         <v>15487402.45</v>
       </c>
       <c r="H790" t="n">
-        <v>15253657.16</v>
+        <v>15486997.79</v>
       </c>
       <c r="I790" t="n">
-        <v>951786.11</v>
+        <v>979092.86</v>
       </c>
       <c r="J790" t="n">
-        <v>233745.29</v>
+        <v>404.66</v>
       </c>
     </row>
     <row r="791">
@@ -33285,13 +33285,13 @@
         <v>1124265.48</v>
       </c>
       <c r="H821" t="n">
-        <v>386605.19</v>
+        <v>488769.62</v>
       </c>
       <c r="I821" t="n">
-        <v>14762.9</v>
+        <v>18808.61</v>
       </c>
       <c r="J821" t="n">
-        <v>737660.29</v>
+        <v>635495.86</v>
       </c>
     </row>
     <row r="822">
@@ -33359,10 +33359,10 @@
         <v>2380000</v>
       </c>
       <c r="F823" t="n">
-        <v>0</v>
+        <v>496761.94</v>
       </c>
       <c r="G823" t="n">
-        <v>2380000</v>
+        <v>2876761.94</v>
       </c>
       <c r="H823" t="n">
         <v>1971628.84</v>
@@ -33371,7 +33371,7 @@
         <v>82353.46000000001</v>
       </c>
       <c r="J823" t="n">
-        <v>408371.16</v>
+        <v>905133.1</v>
       </c>
     </row>
     <row r="824">
@@ -33525,13 +33525,13 @@
         <v>17307984.42</v>
       </c>
       <c r="H827" t="n">
-        <v>1522267.75</v>
+        <v>1808681.17</v>
       </c>
       <c r="I827" t="n">
-        <v>112799.09</v>
+        <v>134022.24</v>
       </c>
       <c r="J827" t="n">
-        <v>15785716.67</v>
+        <v>15499303.25</v>
       </c>
     </row>
     <row r="828">
@@ -33645,13 +33645,13 @@
         <v>8229064.65</v>
       </c>
       <c r="H830" t="n">
-        <v>620555.4</v>
+        <v>882846.65</v>
       </c>
       <c r="I830" t="n">
-        <v>45983.13</v>
+        <v>65418.91</v>
       </c>
       <c r="J830" t="n">
-        <v>7608509.25</v>
+        <v>7346218</v>
       </c>
     </row>
     <row r="831">
@@ -33845,13 +33845,13 @@
         <v>9364991.890000001</v>
       </c>
       <c r="H835" t="n">
-        <v>106297.31</v>
+        <v>127232.53</v>
       </c>
       <c r="I835" t="n">
-        <v>0</v>
+        <v>1216.33</v>
       </c>
       <c r="J835" t="n">
-        <v>9258694.58</v>
+        <v>9237759.359999999</v>
       </c>
     </row>
     <row r="836">
@@ -34805,13 +34805,13 @@
         <v>27994383.03</v>
       </c>
       <c r="H859" t="n">
-        <v>0</v>
+        <v>745082.63</v>
       </c>
       <c r="I859" t="n">
-        <v>0</v>
+        <v>158757.19</v>
       </c>
       <c r="J859" t="n">
-        <v>27994383.03</v>
+        <v>27249300.4</v>
       </c>
     </row>
     <row r="860">
@@ -34885,13 +34885,13 @@
         <v>18749931.77</v>
       </c>
       <c r="H861" t="n">
-        <v>586288.49</v>
+        <v>1373218.42</v>
       </c>
       <c r="I861" t="n">
-        <v>124445.34</v>
+        <v>291480.71</v>
       </c>
       <c r="J861" t="n">
-        <v>18163643.28</v>
+        <v>17376713.35</v>
       </c>
     </row>
     <row r="862">
@@ -35765,13 +35765,13 @@
         <v>12396693.42</v>
       </c>
       <c r="H883" t="n">
-        <v>154160.44</v>
+        <v>258336.65</v>
       </c>
       <c r="I883" t="n">
         <v>0</v>
       </c>
       <c r="J883" t="n">
-        <v>12242532.98</v>
+        <v>12138356.77</v>
       </c>
     </row>
     <row r="884">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$685</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$689</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J685"/>
+  <dimension ref="A1:J689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11165,13 +11165,13 @@
         <v>24865514.03</v>
       </c>
       <c r="H268" t="n">
-        <v>19326094.83</v>
+        <v>19863600.32</v>
       </c>
       <c r="I268" t="n">
-        <v>1904605.97</v>
+        <v>1987435.56</v>
       </c>
       <c r="J268" t="n">
-        <v>5539419.2</v>
+        <v>5001913.71</v>
       </c>
     </row>
     <row r="269">
@@ -16617,7 +16617,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>DO-001/2021-ANO 2</t>
+          <t>DO-001/2021- B</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -16645,13 +16645,13 @@
         <v>2867205</v>
       </c>
       <c r="H405" t="n">
-        <v>2496053.43</v>
+        <v>2586657.84</v>
       </c>
       <c r="I405" t="n">
-        <v>586504.63</v>
+        <v>612009.77</v>
       </c>
       <c r="J405" t="n">
-        <v>371151.57</v>
+        <v>280547.16</v>
       </c>
     </row>
     <row r="406">
@@ -16845,13 +16845,13 @@
         <v>2600522.52</v>
       </c>
       <c r="H410" t="n">
-        <v>1497276.52</v>
+        <v>1507542.69</v>
       </c>
       <c r="I410" t="n">
-        <v>173580.03</v>
+        <v>175162.04</v>
       </c>
       <c r="J410" t="n">
-        <v>1103246</v>
+        <v>1092979.83</v>
       </c>
     </row>
     <row r="411">
@@ -18405,13 +18405,13 @@
         <v>29715772.52</v>
       </c>
       <c r="H449" t="n">
-        <v>22736464.34</v>
+        <v>23090287.3</v>
       </c>
       <c r="I449" t="n">
-        <v>1130138.3</v>
+        <v>1177613.07</v>
       </c>
       <c r="J449" t="n">
-        <v>6979308.18</v>
+        <v>6625485.22</v>
       </c>
     </row>
     <row r="450">
@@ -18925,13 +18925,13 @@
         <v>50256753.54</v>
       </c>
       <c r="H462" t="n">
-        <v>39257997.13</v>
+        <v>40609650.97</v>
       </c>
       <c r="I462" t="n">
-        <v>1387247.2</v>
+        <v>1467687.93</v>
       </c>
       <c r="J462" t="n">
-        <v>10998756.41</v>
+        <v>9647102.57</v>
       </c>
     </row>
     <row r="463">
@@ -19805,13 +19805,13 @@
         <v>28955069.4</v>
       </c>
       <c r="H484" t="n">
-        <v>12191198.01</v>
+        <v>14314001.61</v>
       </c>
       <c r="I484" t="n">
-        <v>281590.16</v>
+        <v>337730.55</v>
       </c>
       <c r="J484" t="n">
-        <v>16763871.39</v>
+        <v>14641067.79</v>
       </c>
     </row>
     <row r="485">
@@ -19965,13 +19965,13 @@
         <v>42794139.74</v>
       </c>
       <c r="H488" t="n">
-        <v>24626355.83</v>
+        <v>34319619.39</v>
       </c>
       <c r="I488" t="n">
-        <v>228610.44</v>
+        <v>452643.71</v>
       </c>
       <c r="J488" t="n">
-        <v>18167783.91</v>
+        <v>8474520.35</v>
       </c>
     </row>
     <row r="489">
@@ -20045,13 +20045,13 @@
         <v>10364111.47</v>
       </c>
       <c r="H490" t="n">
-        <v>2249322.37</v>
+        <v>2579642.02</v>
       </c>
       <c r="I490" t="n">
-        <v>622123.54</v>
+        <v>713477.2</v>
       </c>
       <c r="J490" t="n">
-        <v>8114789.1</v>
+        <v>7784469.45</v>
       </c>
     </row>
     <row r="491">
@@ -20285,13 +20285,13 @@
         <v>5978999.99</v>
       </c>
       <c r="H496" t="n">
-        <v>2046657.96</v>
+        <v>2550950.75</v>
       </c>
       <c r="I496" t="n">
-        <v>0</v>
+        <v>2027.55</v>
       </c>
       <c r="J496" t="n">
-        <v>3932342.03</v>
+        <v>3428049.24</v>
       </c>
     </row>
     <row r="497">
@@ -20525,13 +20525,13 @@
         <v>5903947.49</v>
       </c>
       <c r="H502" t="n">
-        <v>255873.45</v>
+        <v>327634.99</v>
       </c>
       <c r="I502" t="n">
-        <v>6075.47</v>
+        <v>8666.059999999999</v>
       </c>
       <c r="J502" t="n">
-        <v>5648074.04</v>
+        <v>5576312.5</v>
       </c>
     </row>
     <row r="503">
@@ -20565,13 +20565,13 @@
         <v>1152374.25</v>
       </c>
       <c r="H503" t="n">
-        <v>112684.5</v>
+        <v>130152.94</v>
       </c>
       <c r="I503" t="n">
-        <v>3151.35</v>
+        <v>3781.96</v>
       </c>
       <c r="J503" t="n">
-        <v>1039689.75</v>
+        <v>1022221.31</v>
       </c>
     </row>
     <row r="504">
@@ -20845,13 +20845,13 @@
         <v>2086583.52</v>
       </c>
       <c r="H510" t="n">
-        <v>85060.98</v>
+        <v>120945.94</v>
       </c>
       <c r="I510" t="n">
-        <v>5367.33</v>
+        <v>7631.67</v>
       </c>
       <c r="J510" t="n">
-        <v>2001522.54</v>
+        <v>1965637.58</v>
       </c>
     </row>
     <row r="511">
@@ -21525,13 +21525,13 @@
         <v>2451612.34</v>
       </c>
       <c r="H527" t="n">
-        <v>1474482.82</v>
+        <v>1561028.2</v>
       </c>
       <c r="I527" t="n">
-        <v>181219.16</v>
+        <v>194555.8</v>
       </c>
       <c r="J527" t="n">
-        <v>977129.52</v>
+        <v>890584.14</v>
       </c>
     </row>
     <row r="528">
@@ -21605,13 +21605,13 @@
         <v>1584639.21</v>
       </c>
       <c r="H529" t="n">
-        <v>926873.49</v>
+        <v>999355.53</v>
       </c>
       <c r="I529" t="n">
-        <v>118290.63</v>
+        <v>129460.11</v>
       </c>
       <c r="J529" t="n">
-        <v>657765.72</v>
+        <v>585283.6800000001</v>
       </c>
     </row>
     <row r="530">
@@ -23925,13 +23925,13 @@
         <v>24582835.86</v>
       </c>
       <c r="H587" t="n">
-        <v>9983016.92</v>
+        <v>10631286.79</v>
       </c>
       <c r="I587" t="n">
-        <v>1595448.01</v>
+        <v>1705956.1</v>
       </c>
       <c r="J587" t="n">
-        <v>14599818.94</v>
+        <v>13951549.07</v>
       </c>
     </row>
     <row r="588">
@@ -23965,13 +23965,13 @@
         <v>9488185</v>
       </c>
       <c r="H588" t="n">
-        <v>4009285.82</v>
+        <v>4295388.42</v>
       </c>
       <c r="I588" t="n">
-        <v>641850.46</v>
+        <v>690402.04</v>
       </c>
       <c r="J588" t="n">
-        <v>5478899.18</v>
+        <v>5192796.58</v>
       </c>
     </row>
     <row r="589">
@@ -24245,13 +24245,13 @@
         <v>47556790.26</v>
       </c>
       <c r="H595" t="n">
-        <v>30046325.33</v>
+        <v>31001351.31</v>
       </c>
       <c r="I595" t="n">
-        <v>1241995.65</v>
+        <v>1306191.62</v>
       </c>
       <c r="J595" t="n">
-        <v>17510464.93</v>
+        <v>16555438.95</v>
       </c>
     </row>
     <row r="596">
@@ -24685,13 +24685,13 @@
         <v>61821473.21</v>
       </c>
       <c r="H606" t="n">
-        <v>45821274.56</v>
+        <v>46257291.3</v>
       </c>
       <c r="I606" t="n">
-        <v>1373475.56</v>
+        <v>1387864.19</v>
       </c>
       <c r="J606" t="n">
-        <v>16000198.65</v>
+        <v>15564181.91</v>
       </c>
     </row>
     <row r="607">
@@ -24885,13 +24885,13 @@
         <v>14460009.01</v>
       </c>
       <c r="H611" t="n">
-        <v>8747448.59</v>
+        <v>10322430.28</v>
       </c>
       <c r="I611" t="n">
-        <v>688392</v>
+        <v>876565.33</v>
       </c>
       <c r="J611" t="n">
-        <v>5712560.42</v>
+        <v>4137578.73</v>
       </c>
     </row>
     <row r="612">
@@ -25125,13 +25125,13 @@
         <v>42281241.69</v>
       </c>
       <c r="H617" t="n">
-        <v>38538663.15</v>
+        <v>40491145.19</v>
       </c>
       <c r="I617" t="n">
-        <v>1634358.53</v>
+        <v>1737807.72</v>
       </c>
       <c r="J617" t="n">
-        <v>3742578.54</v>
+        <v>1790096.5</v>
       </c>
     </row>
     <row r="618">
@@ -25285,13 +25285,13 @@
         <v>5947278.86</v>
       </c>
       <c r="H621" t="n">
-        <v>2993959.86</v>
+        <v>3734042.86</v>
       </c>
       <c r="I621" t="n">
-        <v>122752.33</v>
+        <v>177666.48</v>
       </c>
       <c r="J621" t="n">
-        <v>2953319</v>
+        <v>2213236</v>
       </c>
     </row>
     <row r="622">
@@ -25445,13 +25445,13 @@
         <v>9659997.08</v>
       </c>
       <c r="H625" t="n">
-        <v>104456.58</v>
+        <v>153335</v>
       </c>
       <c r="I625" t="n">
-        <v>9662.219999999999</v>
+        <v>14183.47</v>
       </c>
       <c r="J625" t="n">
-        <v>9555540.5</v>
+        <v>9506662.08</v>
       </c>
     </row>
     <row r="626">
@@ -25525,13 +25525,13 @@
         <v>5774752.44</v>
       </c>
       <c r="H627" t="n">
-        <v>1576702.74</v>
+        <v>1744569.6</v>
       </c>
       <c r="I627" t="n">
-        <v>56247.51</v>
+        <v>66890.25999999999</v>
       </c>
       <c r="J627" t="n">
-        <v>4198049.7</v>
+        <v>4030182.84</v>
       </c>
     </row>
     <row r="628">
@@ -25805,13 +25805,13 @@
         <v>13934048.38</v>
       </c>
       <c r="H634" t="n">
-        <v>4072181.76</v>
+        <v>4685070</v>
       </c>
       <c r="I634" t="n">
-        <v>1125476.8</v>
+        <v>1294868.36</v>
       </c>
       <c r="J634" t="n">
-        <v>9861866.619999999</v>
+        <v>9248978.380000001</v>
       </c>
     </row>
     <row r="635">
@@ -25845,13 +25845,13 @@
         <v>9104897.41</v>
       </c>
       <c r="H635" t="n">
-        <v>2264927.88</v>
+        <v>2625143.15</v>
       </c>
       <c r="I635" t="n">
-        <v>626679.2</v>
+        <v>726351.11</v>
       </c>
       <c r="J635" t="n">
-        <v>6839969.53</v>
+        <v>6479754.26</v>
       </c>
     </row>
     <row r="636">
@@ -25885,13 +25885,13 @@
         <v>15276741.09</v>
       </c>
       <c r="H636" t="n">
-        <v>3665515.93</v>
+        <v>4187262.13</v>
       </c>
       <c r="I636" t="n">
-        <v>1012888.24</v>
+        <v>1157069.81</v>
       </c>
       <c r="J636" t="n">
-        <v>11611225.16</v>
+        <v>11089478.96</v>
       </c>
     </row>
     <row r="637">
@@ -26045,13 +26045,13 @@
         <v>2876761.94</v>
       </c>
       <c r="H640" t="n">
-        <v>1971628.84</v>
+        <v>2383339.88</v>
       </c>
       <c r="I640" t="n">
-        <v>82353.46000000001</v>
+        <v>99049.57000000001</v>
       </c>
       <c r="J640" t="n">
-        <v>905133.1</v>
+        <v>493422.06</v>
       </c>
     </row>
     <row r="641">
@@ -26125,13 +26125,13 @@
         <v>51814575.44</v>
       </c>
       <c r="H642" t="n">
-        <v>5285927.92</v>
+        <v>5982264.67</v>
       </c>
       <c r="I642" t="n">
-        <v>55132.21</v>
+        <v>74117.67999999999</v>
       </c>
       <c r="J642" t="n">
-        <v>46528647.52</v>
+        <v>45832310.77</v>
       </c>
     </row>
     <row r="643">
@@ -26725,13 +26725,13 @@
         <v>27994383.03</v>
       </c>
       <c r="H657" t="n">
-        <v>745082.63</v>
+        <v>1555732.35</v>
       </c>
       <c r="I657" t="n">
-        <v>158757.19</v>
+        <v>331506.92</v>
       </c>
       <c r="J657" t="n">
-        <v>27249300.4</v>
+        <v>26438650.68</v>
       </c>
     </row>
     <row r="658">
@@ -26805,13 +26805,13 @@
         <v>18749931.77</v>
       </c>
       <c r="H659" t="n">
-        <v>1373218.42</v>
+        <v>2160121.29</v>
       </c>
       <c r="I659" t="n">
-        <v>291480.71</v>
+        <v>458510.34</v>
       </c>
       <c r="J659" t="n">
-        <v>17376713.35</v>
+        <v>16589810.48</v>
       </c>
     </row>
     <row r="660">
@@ -26885,13 +26885,13 @@
         <v>14929346.95</v>
       </c>
       <c r="H661" t="n">
-        <v>239923.68</v>
+        <v>551298.7</v>
       </c>
       <c r="I661" t="n">
-        <v>51524.34</v>
+        <v>118361.5</v>
       </c>
       <c r="J661" t="n">
-        <v>14689423.27</v>
+        <v>14378048.25</v>
       </c>
     </row>
     <row r="662">
@@ -26925,13 +26925,13 @@
         <v>3028048.96</v>
       </c>
       <c r="H662" t="n">
-        <v>0</v>
+        <v>151508.22</v>
       </c>
       <c r="I662" t="n">
-        <v>0</v>
+        <v>4833.11</v>
       </c>
       <c r="J662" t="n">
-        <v>3028048.96</v>
+        <v>2876540.74</v>
       </c>
     </row>
     <row r="663">
@@ -27245,13 +27245,13 @@
         <v>4324285.68</v>
       </c>
       <c r="H670" t="n">
-        <v>0</v>
+        <v>70934.85000000001</v>
       </c>
       <c r="I670" t="n">
-        <v>0</v>
+        <v>2262.82</v>
       </c>
       <c r="J670" t="n">
-        <v>4324285.68</v>
+        <v>4253350.83</v>
       </c>
     </row>
     <row r="671">
@@ -27525,13 +27525,13 @@
         <v>14398046.07</v>
       </c>
       <c r="H677" t="n">
-        <v>0</v>
+        <v>318583.52</v>
       </c>
       <c r="I677" t="n">
-        <v>0</v>
+        <v>30598.96</v>
       </c>
       <c r="J677" t="n">
-        <v>14398046.07</v>
+        <v>14079462.55</v>
       </c>
     </row>
     <row r="678">
@@ -27817,45 +27817,205 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
+          <t>DC-9495596/2026</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Obra de Arte Especial</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>12246076.65</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" t="n">
+        <v>12246076.65</v>
+      </c>
+      <c r="H685" t="n">
+        <v>0</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0</v>
+      </c>
+      <c r="J685" t="n">
+        <v>12246076.65</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
           <t>DC-9493529/2026</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
         <is>
           <t>Rodovia</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr">
+      <c r="D686" t="inlineStr">
         <is>
           <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
-      <c r="E685" t="n">
+      <c r="E686" t="n">
         <v>37600000</v>
       </c>
-      <c r="F685" t="n">
-        <v>0</v>
-      </c>
-      <c r="G685" t="n">
+      <c r="F686" t="n">
+        <v>0</v>
+      </c>
+      <c r="G686" t="n">
         <v>37600000</v>
       </c>
-      <c r="H685" t="n">
-        <v>0</v>
-      </c>
-      <c r="I685" t="n">
-        <v>0</v>
-      </c>
-      <c r="J685" t="n">
+      <c r="H686" t="n">
+        <v>0</v>
+      </c>
+      <c r="I686" t="n">
+        <v>0</v>
+      </c>
+      <c r="J686" t="n">
         <v>37600000</v>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>1099724.43</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0</v>
+      </c>
+      <c r="G687" t="n">
+        <v>1099724.43</v>
+      </c>
+      <c r="H687" t="n">
+        <v>0</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J687" t="n">
+        <v>1099724.43</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0</v>
+      </c>
+      <c r="G688" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0</v>
+      </c>
+      <c r="J688" t="n">
+        <v>14264750.82</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+      <c r="G689" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0</v>
+      </c>
+      <c r="J689" t="n">
+        <v>32998445.8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J685"/>
+  <autoFilter ref="A1:J689"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$689</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$691</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J689"/>
+  <dimension ref="A1:J691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -19359,10 +19359,10 @@
         <v>12752614.39</v>
       </c>
       <c r="F473" t="n">
-        <v>0</v>
+        <v>-1770212.62</v>
       </c>
       <c r="G473" t="n">
-        <v>12752614.39</v>
+        <v>10982401.77</v>
       </c>
       <c r="H473" t="n">
         <v>2457083.86</v>
@@ -19371,7 +19371,7 @@
         <v>100284.57</v>
       </c>
       <c r="J473" t="n">
-        <v>10295530.53</v>
+        <v>8525317.91</v>
       </c>
     </row>
     <row r="474">
@@ -19479,10 +19479,10 @@
         <v>145747385.61</v>
       </c>
       <c r="F476" t="n">
-        <v>0</v>
+        <v>6428844.12</v>
       </c>
       <c r="G476" t="n">
-        <v>145747385.61</v>
+        <v>152176229.73</v>
       </c>
       <c r="H476" t="n">
         <v>58599411.96</v>
@@ -19491,7 +19491,7 @@
         <v>2225363.92</v>
       </c>
       <c r="J476" t="n">
-        <v>87147973.65000001</v>
+        <v>93576817.77</v>
       </c>
     </row>
     <row r="477">
@@ -19879,10 +19879,10 @@
         <v>78647423.75</v>
       </c>
       <c r="F486" t="n">
-        <v>8753988.41</v>
+        <v>17014249.18</v>
       </c>
       <c r="G486" t="n">
-        <v>87401412.16</v>
+        <v>95661672.93000001</v>
       </c>
       <c r="H486" t="n">
         <v>12480224.9</v>
@@ -19891,7 +19891,7 @@
         <v>540755.11</v>
       </c>
       <c r="J486" t="n">
-        <v>74921187.26000001</v>
+        <v>83181448.03</v>
       </c>
     </row>
     <row r="487">
@@ -19959,10 +19959,10 @@
         <v>35900000</v>
       </c>
       <c r="F488" t="n">
-        <v>6894139.74</v>
+        <v>7889355.88</v>
       </c>
       <c r="G488" t="n">
-        <v>42794139.74</v>
+        <v>43789355.88</v>
       </c>
       <c r="H488" t="n">
         <v>34319619.39</v>
@@ -19971,7 +19971,7 @@
         <v>452643.71</v>
       </c>
       <c r="J488" t="n">
-        <v>8474520.35</v>
+        <v>9469736.49</v>
       </c>
     </row>
     <row r="489">
@@ -20439,10 +20439,10 @@
         <v>7710000</v>
       </c>
       <c r="F500" t="n">
-        <v>0</v>
+        <v>1924126.24</v>
       </c>
       <c r="G500" t="n">
-        <v>7710000</v>
+        <v>9634126.24</v>
       </c>
       <c r="H500" t="n">
         <v>3808666.66</v>
@@ -20451,7 +20451,7 @@
         <v>68016.03999999999</v>
       </c>
       <c r="J500" t="n">
-        <v>3901333.34</v>
+        <v>5825459.58</v>
       </c>
     </row>
     <row r="501">
@@ -23925,13 +23925,13 @@
         <v>24582835.86</v>
       </c>
       <c r="H587" t="n">
-        <v>10631286.79</v>
+        <v>11273665.11</v>
       </c>
       <c r="I587" t="n">
-        <v>1705956.1</v>
+        <v>1842969.56</v>
       </c>
       <c r="J587" t="n">
-        <v>13951549.07</v>
+        <v>13309170.75</v>
       </c>
     </row>
     <row r="588">
@@ -23965,13 +23965,13 @@
         <v>9488185</v>
       </c>
       <c r="H588" t="n">
-        <v>4295388.42</v>
+        <v>4585196.15</v>
       </c>
       <c r="I588" t="n">
-        <v>690402.04</v>
+        <v>751841.25</v>
       </c>
       <c r="J588" t="n">
-        <v>5192796.58</v>
+        <v>4902988.85</v>
       </c>
     </row>
     <row r="589">
@@ -26645,13 +26645,13 @@
         <v>22167830.47</v>
       </c>
       <c r="H655" t="n">
-        <v>1466960.34</v>
+        <v>2304211.64</v>
       </c>
       <c r="I655" t="n">
-        <v>313064.99</v>
+        <v>491722.4</v>
       </c>
       <c r="J655" t="n">
-        <v>20700870.13</v>
+        <v>19863618.83</v>
       </c>
     </row>
     <row r="656">
@@ -27365,13 +27365,13 @@
         <v>6677404.33</v>
       </c>
       <c r="H673" t="n">
-        <v>0</v>
+        <v>119550.83</v>
       </c>
       <c r="I673" t="n">
-        <v>0</v>
+        <v>3813.67</v>
       </c>
       <c r="J673" t="n">
-        <v>6677404.33</v>
+        <v>6557853.5</v>
       </c>
     </row>
     <row r="674">
@@ -28014,8 +28014,88 @@
         <v>32998445.8</v>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>0</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0</v>
+      </c>
+      <c r="G690" t="n">
+        <v>0</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>0</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>0</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J689"/>
+  <autoFilter ref="A1:J691"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$691</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$696</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J691"/>
+  <dimension ref="A1:J696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18485,13 +18485,13 @@
         <v>33479427.94</v>
       </c>
       <c r="H451" t="n">
-        <v>18674361.7</v>
+        <v>19221395.57</v>
       </c>
       <c r="I451" t="n">
-        <v>960635.3100000001</v>
+        <v>1019396.32</v>
       </c>
       <c r="J451" t="n">
-        <v>14805066.24</v>
+        <v>14258032.37</v>
       </c>
     </row>
     <row r="452">
@@ -19365,13 +19365,13 @@
         <v>10982401.77</v>
       </c>
       <c r="H473" t="n">
-        <v>2457083.86</v>
+        <v>2486659.38</v>
       </c>
       <c r="I473" t="n">
-        <v>100284.57</v>
+        <v>101795.87</v>
       </c>
       <c r="J473" t="n">
-        <v>8525317.91</v>
+        <v>8495742.390000001</v>
       </c>
     </row>
     <row r="474">
@@ -19485,13 +19485,13 @@
         <v>152176229.73</v>
       </c>
       <c r="H476" t="n">
-        <v>58599411.96</v>
+        <v>61434407.65</v>
       </c>
       <c r="I476" t="n">
-        <v>2225363.92</v>
+        <v>2379545.29</v>
       </c>
       <c r="J476" t="n">
-        <v>93576817.77</v>
+        <v>90741822.08</v>
       </c>
     </row>
     <row r="477">
@@ -19765,13 +19765,13 @@
         <v>44482154.94</v>
       </c>
       <c r="H483" t="n">
-        <v>6069911.22</v>
+        <v>17027419.71</v>
       </c>
       <c r="I483" t="n">
-        <v>231447.84</v>
+        <v>515574.38</v>
       </c>
       <c r="J483" t="n">
-        <v>38412243.72</v>
+        <v>27454735.23</v>
       </c>
     </row>
     <row r="484">
@@ -24205,13 +24205,13 @@
         <v>37153801.63</v>
       </c>
       <c r="H594" t="n">
-        <v>29264265.66</v>
+        <v>30132401.34</v>
       </c>
       <c r="I594" t="n">
-        <v>1337201.47</v>
+        <v>1413980.61</v>
       </c>
       <c r="J594" t="n">
-        <v>7889535.97</v>
+        <v>7021400.29</v>
       </c>
     </row>
     <row r="595">
@@ -26325,13 +26325,13 @@
         <v>53573999.99</v>
       </c>
       <c r="H647" t="n">
-        <v>5441922.82</v>
+        <v>6093202.3</v>
       </c>
       <c r="I647" t="n">
-        <v>52013.78</v>
+        <v>63545.71</v>
       </c>
       <c r="J647" t="n">
-        <v>48132077.17</v>
+        <v>47480797.69</v>
       </c>
     </row>
     <row r="648">
@@ -27937,7 +27937,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482017/2025</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -27947,22 +27947,22 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>14264750.82</v>
+        <v>47349998.43</v>
       </c>
       <c r="F688" t="n">
         <v>0</v>
       </c>
       <c r="G688" t="n">
-        <v>14264750.82</v>
+        <v>47349998.43</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -27971,13 +27971,13 @@
         <v>0</v>
       </c>
       <c r="J688" t="n">
-        <v>14264750.82</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9493205/2026</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -27987,22 +27987,22 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>32998445.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="F689" t="n">
         <v>0</v>
       </c>
       <c r="G689" t="n">
-        <v>32998445.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -28011,13 +28011,13 @@
         <v>0</v>
       </c>
       <c r="J689" t="n">
-        <v>32998445.8</v>
+        <v>31699998.96</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>D0-009482032/2025</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -28032,17 +28032,17 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>0</v>
+        <v>35989998.13</v>
       </c>
       <c r="F690" t="n">
         <v>0</v>
       </c>
       <c r="G690" t="n">
-        <v>0</v>
+        <v>35989998.13</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -28051,51 +28051,251 @@
         <v>0</v>
       </c>
       <c r="J690" t="n">
-        <v>0</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
+          <t>DO-9481987/2025</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+      <c r="G691" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J691" t="n">
+        <v>23434999.8</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>DO-009482055/2025</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0</v>
+      </c>
+      <c r="G692" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="H692" t="n">
+        <v>0</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0</v>
+      </c>
+      <c r="J692" t="n">
+        <v>32097999.96</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0</v>
+      </c>
+      <c r="G693" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="H693" t="n">
+        <v>0</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J693" t="n">
+        <v>14264750.82</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0</v>
+      </c>
+      <c r="G694" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="H694" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0</v>
+      </c>
+      <c r="J694" t="n">
+        <v>32998445.8</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0</v>
+      </c>
+      <c r="G695" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0</v>
+      </c>
+      <c r="J695" t="n">
+        <v>45188997.86</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
           <t>DO-009482014/2025</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
         <is>
           <t>Prestação de Serviços</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr">
+      <c r="D696" t="inlineStr">
         <is>
           <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
-      <c r="E691" t="n">
-        <v>0</v>
-      </c>
-      <c r="F691" t="n">
-        <v>0</v>
-      </c>
-      <c r="G691" t="n">
-        <v>0</v>
-      </c>
-      <c r="H691" t="n">
-        <v>0</v>
-      </c>
-      <c r="I691" t="n">
-        <v>0</v>
-      </c>
-      <c r="J691" t="n">
-        <v>0</v>
+      <c r="E696" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0</v>
+      </c>
+      <c r="J696" t="n">
+        <v>77898894.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J691"/>
+  <autoFilter ref="A1:J696"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$696</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$707</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J696"/>
+  <dimension ref="A1:J707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11165,13 +11165,13 @@
         <v>24865514.03</v>
       </c>
       <c r="H268" t="n">
-        <v>19863600.32</v>
+        <v>20353151.07</v>
       </c>
       <c r="I268" t="n">
-        <v>1987435.56</v>
+        <v>2062875.33</v>
       </c>
       <c r="J268" t="n">
-        <v>5001913.71</v>
+        <v>4512362.96</v>
       </c>
     </row>
     <row r="269">
@@ -12965,13 +12965,13 @@
         <v>2923843.86</v>
       </c>
       <c r="H313" t="n">
-        <v>957623.3199999999</v>
+        <v>1056691.25</v>
       </c>
       <c r="I313" t="n">
-        <v>363466.8</v>
+        <v>405055.51</v>
       </c>
       <c r="J313" t="n">
-        <v>1966220.54</v>
+        <v>1867152.61</v>
       </c>
     </row>
     <row r="314">
@@ -15365,13 +15365,13 @@
         <v>36255903.57</v>
       </c>
       <c r="H373" t="n">
-        <v>29711129.82</v>
+        <v>29941304.59</v>
       </c>
       <c r="I373" t="n">
-        <v>1540999.36</v>
+        <v>1567645.61</v>
       </c>
       <c r="J373" t="n">
-        <v>6544773.75</v>
+        <v>6314598.98</v>
       </c>
     </row>
     <row r="374">
@@ -15405,13 +15405,13 @@
         <v>34335611.48</v>
       </c>
       <c r="H374" t="n">
-        <v>1356813.1</v>
+        <v>1770020.06</v>
       </c>
       <c r="I374" t="n">
-        <v>49985.28</v>
+        <v>64501.74</v>
       </c>
       <c r="J374" t="n">
-        <v>32978798.38</v>
+        <v>32565591.42</v>
       </c>
     </row>
     <row r="375">
@@ -15965,13 +15965,13 @@
         <v>3655796.23</v>
       </c>
       <c r="H388" t="n">
-        <v>2018694.35</v>
+        <v>2122647.3</v>
       </c>
       <c r="I388" t="n">
-        <v>288245.56</v>
+        <v>304264.7</v>
       </c>
       <c r="J388" t="n">
-        <v>1637101.88</v>
+        <v>1533148.93</v>
       </c>
     </row>
     <row r="389">
@@ -16845,13 +16845,13 @@
         <v>2600522.52</v>
       </c>
       <c r="H410" t="n">
-        <v>1507542.69</v>
+        <v>1603853.4</v>
       </c>
       <c r="I410" t="n">
-        <v>175162.04</v>
+        <v>190003.52</v>
       </c>
       <c r="J410" t="n">
-        <v>1092979.83</v>
+        <v>996669.12</v>
       </c>
     </row>
     <row r="411">
@@ -17085,13 +17085,13 @@
         <v>9807936.460000001</v>
       </c>
       <c r="H416" t="n">
-        <v>5043747.34</v>
+        <v>8514031.869999999</v>
       </c>
       <c r="I416" t="n">
-        <v>203448.59</v>
+        <v>552492.78</v>
       </c>
       <c r="J416" t="n">
-        <v>4764189.12</v>
+        <v>1293904.59</v>
       </c>
     </row>
     <row r="417">
@@ -17125,13 +17125,13 @@
         <v>7576922.1</v>
       </c>
       <c r="H417" t="n">
-        <v>4097169.68</v>
+        <v>4239229.08</v>
       </c>
       <c r="I417" t="n">
-        <v>403537.68</v>
+        <v>423752.72</v>
       </c>
       <c r="J417" t="n">
-        <v>3479752.42</v>
+        <v>3337693.02</v>
       </c>
     </row>
     <row r="418">
@@ -17765,13 +17765,13 @@
         <v>38819029.96</v>
       </c>
       <c r="H433" t="n">
-        <v>33638673.8</v>
+        <v>34740432.66</v>
       </c>
       <c r="I433" t="n">
-        <v>2021305.47</v>
+        <v>2122047.18</v>
       </c>
       <c r="J433" t="n">
-        <v>5180356.16</v>
+        <v>4078597.3</v>
       </c>
     </row>
     <row r="434">
@@ -18005,13 +18005,13 @@
         <v>1425000</v>
       </c>
       <c r="H439" t="n">
-        <v>1004477.76</v>
+        <v>1051152.96</v>
       </c>
       <c r="I439" t="n">
-        <v>56210.2</v>
+        <v>60859.04</v>
       </c>
       <c r="J439" t="n">
-        <v>420522.24</v>
+        <v>373847.04</v>
       </c>
     </row>
     <row r="440">
@@ -18165,13 +18165,13 @@
         <v>797999.85</v>
       </c>
       <c r="H443" t="n">
-        <v>391292.63</v>
+        <v>400277.37</v>
       </c>
       <c r="I443" t="n">
-        <v>26931.97</v>
+        <v>27793.59</v>
       </c>
       <c r="J443" t="n">
-        <v>406707.22</v>
+        <v>397722.48</v>
       </c>
     </row>
     <row r="444">
@@ -18205,13 +18205,13 @@
         <v>28096598.89</v>
       </c>
       <c r="H444" t="n">
-        <v>26154150.05</v>
+        <v>26999282.29</v>
       </c>
       <c r="I444" t="n">
-        <v>1298454.05</v>
+        <v>1385505.74</v>
       </c>
       <c r="J444" t="n">
-        <v>1942448.84</v>
+        <v>1097316.6</v>
       </c>
     </row>
     <row r="445">
@@ -18285,13 +18285,13 @@
         <v>31994041.87</v>
       </c>
       <c r="H446" t="n">
-        <v>28815897.11</v>
+        <v>29342447.39</v>
       </c>
       <c r="I446" t="n">
-        <v>1776195.35</v>
+        <v>1839385.71</v>
       </c>
       <c r="J446" t="n">
-        <v>3178144.76</v>
+        <v>2651594.48</v>
       </c>
     </row>
     <row r="447">
@@ -18325,13 +18325,13 @@
         <v>41801980.63</v>
       </c>
       <c r="H447" t="n">
-        <v>36859439.52</v>
+        <v>37778568.04</v>
       </c>
       <c r="I447" t="n">
-        <v>2588739.03</v>
+        <v>2690060.18</v>
       </c>
       <c r="J447" t="n">
-        <v>4942541.11</v>
+        <v>4023412.59</v>
       </c>
     </row>
     <row r="448">
@@ -18365,13 +18365,13 @@
         <v>30648355.12</v>
       </c>
       <c r="H448" t="n">
-        <v>16551136.84</v>
+        <v>17173368.49</v>
       </c>
       <c r="I448" t="n">
-        <v>1112171.11</v>
+        <v>1180122.02</v>
       </c>
       <c r="J448" t="n">
-        <v>14097218.28</v>
+        <v>13474986.63</v>
       </c>
     </row>
     <row r="449">
@@ -18405,13 +18405,13 @@
         <v>29715772.52</v>
       </c>
       <c r="H449" t="n">
-        <v>23090287.3</v>
+        <v>23439872.67</v>
       </c>
       <c r="I449" t="n">
-        <v>1177613.07</v>
+        <v>1224383.25</v>
       </c>
       <c r="J449" t="n">
-        <v>6625485.22</v>
+        <v>6275899.85</v>
       </c>
     </row>
     <row r="450">
@@ -18605,13 +18605,13 @@
         <v>33721624.27</v>
       </c>
       <c r="H454" t="n">
-        <v>17120516.56</v>
+        <v>17654827.84</v>
       </c>
       <c r="I454" t="n">
-        <v>972473.9</v>
+        <v>1026710.9</v>
       </c>
       <c r="J454" t="n">
-        <v>16601107.71</v>
+        <v>16066796.43</v>
       </c>
     </row>
     <row r="455">
@@ -18645,13 +18645,13 @@
         <v>32023158.45</v>
       </c>
       <c r="H455" t="n">
-        <v>26705330.6</v>
+        <v>27938707.57</v>
       </c>
       <c r="I455" t="n">
-        <v>1191342.54</v>
+        <v>1300896.83</v>
       </c>
       <c r="J455" t="n">
-        <v>5317827.85</v>
+        <v>4084450.88</v>
       </c>
     </row>
     <row r="456">
@@ -18765,13 +18765,13 @@
         <v>42788655.89</v>
       </c>
       <c r="H458" t="n">
-        <v>26817950.04</v>
+        <v>27461062.39</v>
       </c>
       <c r="I458" t="n">
-        <v>1413131.04</v>
+        <v>1481599.91</v>
       </c>
       <c r="J458" t="n">
-        <v>15970705.85</v>
+        <v>15327593.5</v>
       </c>
     </row>
     <row r="459">
@@ -18805,13 +18805,13 @@
         <v>34984519.25</v>
       </c>
       <c r="H459" t="n">
-        <v>29104302.64</v>
+        <v>30596587.45</v>
       </c>
       <c r="I459" t="n">
-        <v>1506627.07</v>
+        <v>1638048.83</v>
       </c>
       <c r="J459" t="n">
-        <v>5880216.61</v>
+        <v>4387931.8</v>
       </c>
     </row>
     <row r="460">
@@ -18925,13 +18925,13 @@
         <v>50256753.54</v>
       </c>
       <c r="H462" t="n">
-        <v>40609650.97</v>
+        <v>41981889.57</v>
       </c>
       <c r="I462" t="n">
-        <v>1467687.93</v>
+        <v>1522076.2</v>
       </c>
       <c r="J462" t="n">
-        <v>9647102.57</v>
+        <v>8274863.97</v>
       </c>
     </row>
     <row r="463">
@@ -19045,13 +19045,13 @@
         <v>47634588.04</v>
       </c>
       <c r="H465" t="n">
-        <v>25655505.35</v>
+        <v>26881215.87</v>
       </c>
       <c r="I465" t="n">
-        <v>1123267.81</v>
+        <v>1223574.14</v>
       </c>
       <c r="J465" t="n">
-        <v>21979082.69</v>
+        <v>20753372.17</v>
       </c>
     </row>
     <row r="466">
@@ -19125,13 +19125,13 @@
         <v>52604103.19</v>
       </c>
       <c r="H467" t="n">
-        <v>31955189.39</v>
+        <v>33806452.17</v>
       </c>
       <c r="I467" t="n">
-        <v>1394191.19</v>
+        <v>1522593.9</v>
       </c>
       <c r="J467" t="n">
-        <v>20648913.8</v>
+        <v>18797651.02</v>
       </c>
     </row>
     <row r="468">
@@ -19165,13 +19165,13 @@
         <v>45768946.45</v>
       </c>
       <c r="H468" t="n">
-        <v>18109441.46</v>
+        <v>20394072.15</v>
       </c>
       <c r="I468" t="n">
-        <v>822203.95</v>
+        <v>967683.63</v>
       </c>
       <c r="J468" t="n">
-        <v>27659504.99</v>
+        <v>25374874.3</v>
       </c>
     </row>
     <row r="469">
@@ -19205,13 +19205,13 @@
         <v>46337191.41</v>
       </c>
       <c r="H469" t="n">
-        <v>29530146.27</v>
+        <v>29856106.57</v>
       </c>
       <c r="I469" t="n">
-        <v>1334902.9</v>
+        <v>1357169.26</v>
       </c>
       <c r="J469" t="n">
-        <v>16807045.14</v>
+        <v>16481084.84</v>
       </c>
     </row>
     <row r="470">
@@ -19245,13 +19245,13 @@
         <v>859769.01</v>
       </c>
       <c r="H470" t="n">
-        <v>584820.63</v>
+        <v>688450.6899999999</v>
       </c>
       <c r="I470" t="n">
-        <v>18452.61</v>
+        <v>26141.96</v>
       </c>
       <c r="J470" t="n">
-        <v>274948.38</v>
+        <v>171318.32</v>
       </c>
     </row>
     <row r="471">
@@ -19405,13 +19405,13 @@
         <v>24309955.5</v>
       </c>
       <c r="H474" t="n">
-        <v>13284295.25</v>
+        <v>15133680.75</v>
       </c>
       <c r="I474" t="n">
-        <v>74469.48</v>
+        <v>170125.57</v>
       </c>
       <c r="J474" t="n">
-        <v>11025660.25</v>
+        <v>9176274.75</v>
       </c>
     </row>
     <row r="475">
@@ -19645,13 +19645,13 @@
         <v>2540551.02</v>
       </c>
       <c r="H480" t="n">
-        <v>117040.09</v>
+        <v>129788.89</v>
       </c>
       <c r="I480" t="n">
-        <v>5015.29</v>
+        <v>5961.25</v>
       </c>
       <c r="J480" t="n">
-        <v>2423510.93</v>
+        <v>2410762.13</v>
       </c>
     </row>
     <row r="481">
@@ -19685,13 +19685,13 @@
         <v>924684.42</v>
       </c>
       <c r="H481" t="n">
-        <v>647541.22</v>
+        <v>664376.46</v>
       </c>
       <c r="I481" t="n">
-        <v>28643.38</v>
+        <v>29892.55</v>
       </c>
       <c r="J481" t="n">
-        <v>277143.2</v>
+        <v>260307.96</v>
       </c>
     </row>
     <row r="482">
@@ -19725,13 +19725,13 @@
         <v>7109673.15</v>
       </c>
       <c r="H482" t="n">
-        <v>0</v>
+        <v>134831.17</v>
       </c>
       <c r="I482" t="n">
-        <v>0</v>
+        <v>4696.72</v>
       </c>
       <c r="J482" t="n">
-        <v>7109673.15</v>
+        <v>6974841.98</v>
       </c>
     </row>
     <row r="483">
@@ -19805,13 +19805,13 @@
         <v>28955069.4</v>
       </c>
       <c r="H484" t="n">
-        <v>14314001.61</v>
+        <v>14841369.03</v>
       </c>
       <c r="I484" t="n">
-        <v>337730.55</v>
+        <v>351155.7</v>
       </c>
       <c r="J484" t="n">
-        <v>14641067.79</v>
+        <v>14113700.37</v>
       </c>
     </row>
     <row r="485">
@@ -19845,13 +19845,13 @@
         <v>29576179.41</v>
       </c>
       <c r="H485" t="n">
-        <v>1039591.93</v>
+        <v>1373835.81</v>
       </c>
       <c r="I485" t="n">
-        <v>60971.02</v>
+        <v>73245.00999999999</v>
       </c>
       <c r="J485" t="n">
-        <v>28536587.48</v>
+        <v>28202343.6</v>
       </c>
     </row>
     <row r="486">
@@ -19925,13 +19925,13 @@
         <v>11569905.95</v>
       </c>
       <c r="H487" t="n">
-        <v>6145327.29</v>
+        <v>6271540.57</v>
       </c>
       <c r="I487" t="n">
-        <v>186278.45</v>
+        <v>190178.79</v>
       </c>
       <c r="J487" t="n">
-        <v>5424578.66</v>
+        <v>5298365.38</v>
       </c>
     </row>
     <row r="488">
@@ -20005,13 +20005,13 @@
         <v>30872072.3</v>
       </c>
       <c r="H489" t="n">
-        <v>3148412.06</v>
+        <v>3733445.15</v>
       </c>
       <c r="I489" t="n">
-        <v>69280.47</v>
+        <v>90400.14999999999</v>
       </c>
       <c r="J489" t="n">
-        <v>27723660.24</v>
+        <v>27138627.15</v>
       </c>
     </row>
     <row r="490">
@@ -20085,13 +20085,13 @@
         <v>3900717.4</v>
       </c>
       <c r="H491" t="n">
-        <v>1587630.07</v>
+        <v>1798925.05</v>
       </c>
       <c r="I491" t="n">
-        <v>810167.5699999999</v>
+        <v>917991.39</v>
       </c>
       <c r="J491" t="n">
-        <v>2313087.33</v>
+        <v>2101792.35</v>
       </c>
     </row>
     <row r="492">
@@ -20125,13 +20125,13 @@
         <v>9147934.25</v>
       </c>
       <c r="H492" t="n">
-        <v>1566140.15</v>
+        <v>1867887.53</v>
       </c>
       <c r="I492" t="n">
-        <v>34789.89</v>
+        <v>45682.96</v>
       </c>
       <c r="J492" t="n">
-        <v>7581794.1</v>
+        <v>7280046.72</v>
       </c>
     </row>
     <row r="493">
@@ -20165,13 +20165,13 @@
         <v>44573000</v>
       </c>
       <c r="H493" t="n">
-        <v>4087799.31</v>
+        <v>4670098.83</v>
       </c>
       <c r="I493" t="n">
-        <v>50292.73</v>
+        <v>66649.77</v>
       </c>
       <c r="J493" t="n">
-        <v>40485200.69</v>
+        <v>39902901.17</v>
       </c>
     </row>
     <row r="494">
@@ -20205,13 +20205,13 @@
         <v>22458906.7</v>
       </c>
       <c r="H494" t="n">
-        <v>1152827.26</v>
+        <v>1487538.65</v>
       </c>
       <c r="I494" t="n">
-        <v>23447.85</v>
+        <v>35530.91</v>
       </c>
       <c r="J494" t="n">
-        <v>21306079.44</v>
+        <v>20971368.05</v>
       </c>
     </row>
     <row r="495">
@@ -20285,13 +20285,13 @@
         <v>5978999.99</v>
       </c>
       <c r="H496" t="n">
-        <v>2550950.75</v>
+        <v>3278560.72</v>
       </c>
       <c r="I496" t="n">
-        <v>2027.55</v>
+        <v>1944.54</v>
       </c>
       <c r="J496" t="n">
-        <v>3428049.24</v>
+        <v>2700439.27</v>
       </c>
     </row>
     <row r="497">
@@ -20445,13 +20445,13 @@
         <v>9634126.24</v>
       </c>
       <c r="H500" t="n">
-        <v>3808666.66</v>
+        <v>4736694.87</v>
       </c>
       <c r="I500" t="n">
-        <v>68016.03999999999</v>
+        <v>90981.28999999999</v>
       </c>
       <c r="J500" t="n">
-        <v>5825459.58</v>
+        <v>4897431.37</v>
       </c>
     </row>
     <row r="501">
@@ -20485,13 +20485,13 @@
         <v>21429526.4</v>
       </c>
       <c r="H501" t="n">
-        <v>2490585.68</v>
+        <v>2750527.43</v>
       </c>
       <c r="I501" t="n">
         <v>0</v>
       </c>
       <c r="J501" t="n">
-        <v>18938940.72</v>
+        <v>18678998.97</v>
       </c>
     </row>
     <row r="502">
@@ -20525,13 +20525,13 @@
         <v>5903947.49</v>
       </c>
       <c r="H502" t="n">
-        <v>327634.99</v>
+        <v>344480.73</v>
       </c>
       <c r="I502" t="n">
-        <v>8666.059999999999</v>
+        <v>9274.190000000001</v>
       </c>
       <c r="J502" t="n">
-        <v>5576312.5</v>
+        <v>5559466.76</v>
       </c>
     </row>
     <row r="503">
@@ -20605,13 +20605,13 @@
         <v>2401689.3</v>
       </c>
       <c r="H504" t="n">
-        <v>764724.91</v>
+        <v>1355674.86</v>
       </c>
       <c r="I504" t="n">
         <v>0</v>
       </c>
       <c r="J504" t="n">
-        <v>1636964.39</v>
+        <v>1046014.44</v>
       </c>
     </row>
     <row r="505">
@@ -20645,13 +20645,13 @@
         <v>14619000</v>
       </c>
       <c r="H505" t="n">
-        <v>2398334.49</v>
+        <v>4429527.64</v>
       </c>
       <c r="I505" t="n">
-        <v>8420.889999999999</v>
+        <v>20772.43</v>
       </c>
       <c r="J505" t="n">
-        <v>12220665.51</v>
+        <v>10189472.36</v>
       </c>
     </row>
     <row r="506">
@@ -20685,13 +20685,13 @@
         <v>21860486.4</v>
       </c>
       <c r="H506" t="n">
-        <v>2841863.22</v>
+        <v>3570546.1</v>
       </c>
       <c r="I506" t="n">
-        <v>23244.98</v>
+        <v>46489.96</v>
       </c>
       <c r="J506" t="n">
-        <v>19018623.18</v>
+        <v>18289940.3</v>
       </c>
     </row>
     <row r="507">
@@ -20725,13 +20725,13 @@
         <v>9410345.890000001</v>
       </c>
       <c r="H507" t="n">
-        <v>816218.0699999999</v>
+        <v>1006178.54</v>
       </c>
       <c r="I507" t="n">
-        <v>22458.58</v>
+        <v>29316.14</v>
       </c>
       <c r="J507" t="n">
-        <v>8594127.82</v>
+        <v>8404167.35</v>
       </c>
     </row>
     <row r="508">
@@ -20765,13 +20765,13 @@
         <v>9200787.869999999</v>
       </c>
       <c r="H508" t="n">
-        <v>1133906.65</v>
+        <v>1400596.05</v>
       </c>
       <c r="I508" t="n">
-        <v>31496.39</v>
+        <v>41123.86</v>
       </c>
       <c r="J508" t="n">
-        <v>8066881.22</v>
+        <v>7800191.82</v>
       </c>
     </row>
     <row r="509">
@@ -20845,13 +20845,13 @@
         <v>2086583.52</v>
       </c>
       <c r="H510" t="n">
-        <v>120945.94</v>
+        <v>152799.08</v>
       </c>
       <c r="I510" t="n">
-        <v>7631.67</v>
+        <v>9641.6</v>
       </c>
       <c r="J510" t="n">
-        <v>1965637.58</v>
+        <v>1933784.44</v>
       </c>
     </row>
     <row r="511">
@@ -20885,13 +20885,13 @@
         <v>1361070.69</v>
       </c>
       <c r="H511" t="n">
-        <v>250889.08</v>
+        <v>262527.9</v>
       </c>
       <c r="I511" t="n">
-        <v>26889.6</v>
+        <v>28683.14</v>
       </c>
       <c r="J511" t="n">
-        <v>1110181.61</v>
+        <v>1098542.79</v>
       </c>
     </row>
     <row r="512">
@@ -21045,13 +21045,13 @@
         <v>864235.72</v>
       </c>
       <c r="H515" t="n">
-        <v>212331.48</v>
+        <v>217419.54</v>
       </c>
       <c r="I515" t="n">
-        <v>21206.44</v>
+        <v>21990.51</v>
       </c>
       <c r="J515" t="n">
-        <v>651904.24</v>
+        <v>646816.1800000001</v>
       </c>
     </row>
     <row r="516">
@@ -21085,13 +21085,13 @@
         <v>634467.04</v>
       </c>
       <c r="H516" t="n">
-        <v>156039.26</v>
+        <v>157025.26</v>
       </c>
       <c r="I516" t="n">
-        <v>16322.6</v>
+        <v>16474.54</v>
       </c>
       <c r="J516" t="n">
-        <v>478427.78</v>
+        <v>477441.78</v>
       </c>
     </row>
     <row r="517">
@@ -21405,13 +21405,13 @@
         <v>1792375.62</v>
       </c>
       <c r="H524" t="n">
-        <v>602790.09</v>
+        <v>629697.1800000001</v>
       </c>
       <c r="I524" t="n">
-        <v>73971.58</v>
+        <v>78117.96000000001</v>
       </c>
       <c r="J524" t="n">
-        <v>1189585.53</v>
+        <v>1162678.44</v>
       </c>
     </row>
     <row r="525">
@@ -21485,13 +21485,13 @@
         <v>3721286.23</v>
       </c>
       <c r="H526" t="n">
-        <v>1763047.69</v>
+        <v>1776371.55</v>
       </c>
       <c r="I526" t="n">
-        <v>201189.08</v>
+        <v>203242.28</v>
       </c>
       <c r="J526" t="n">
-        <v>1958238.54</v>
+        <v>1944914.68</v>
       </c>
     </row>
     <row r="527">
@@ -21525,13 +21525,13 @@
         <v>2451612.34</v>
       </c>
       <c r="H527" t="n">
-        <v>1561028.2</v>
+        <v>1748367.35</v>
       </c>
       <c r="I527" t="n">
-        <v>194555.8</v>
+        <v>223424.76</v>
       </c>
       <c r="J527" t="n">
-        <v>890584.14</v>
+        <v>703244.99</v>
       </c>
     </row>
     <row r="528">
@@ -21565,13 +21565,13 @@
         <v>1750107.91</v>
       </c>
       <c r="H528" t="n">
-        <v>178536.39</v>
+        <v>226431.45</v>
       </c>
       <c r="I528" t="n">
-        <v>27512.43</v>
+        <v>34893.05</v>
       </c>
       <c r="J528" t="n">
-        <v>1571571.52</v>
+        <v>1523676.46</v>
       </c>
     </row>
     <row r="529">
@@ -21605,13 +21605,13 @@
         <v>1584639.21</v>
       </c>
       <c r="H529" t="n">
-        <v>999355.53</v>
+        <v>1036278.58</v>
       </c>
       <c r="I529" t="n">
-        <v>129460.11</v>
+        <v>135149.95</v>
       </c>
       <c r="J529" t="n">
-        <v>585283.6800000001</v>
+        <v>548360.63</v>
       </c>
     </row>
     <row r="530">
@@ -21725,13 +21725,13 @@
         <v>2363126.32</v>
       </c>
       <c r="H532" t="n">
-        <v>787663.08</v>
+        <v>795161.12</v>
       </c>
       <c r="I532" t="n">
-        <v>75322.98</v>
+        <v>76478.42</v>
       </c>
       <c r="J532" t="n">
-        <v>1575463.24</v>
+        <v>1567965.2</v>
       </c>
     </row>
     <row r="533">
@@ -21885,13 +21885,13 @@
         <v>891896.45</v>
       </c>
       <c r="H536" t="n">
-        <v>475525.93</v>
+        <v>542488.23</v>
       </c>
       <c r="I536" t="n">
-        <v>52344.82</v>
+        <v>62663.71</v>
       </c>
       <c r="J536" t="n">
-        <v>416370.52</v>
+        <v>349408.22</v>
       </c>
     </row>
     <row r="537">
@@ -22205,13 +22205,13 @@
         <v>583263.13</v>
       </c>
       <c r="H544" t="n">
-        <v>214660.85</v>
+        <v>240213.31</v>
       </c>
       <c r="I544" t="n">
-        <v>24681.64</v>
+        <v>28619.27</v>
       </c>
       <c r="J544" t="n">
-        <v>368602.28</v>
+        <v>343049.82</v>
       </c>
     </row>
     <row r="545">
@@ -22325,13 +22325,13 @@
         <v>1040213.01</v>
       </c>
       <c r="H547" t="n">
-        <v>331496.98</v>
+        <v>358875.1</v>
       </c>
       <c r="I547" t="n">
-        <v>39155.67</v>
+        <v>43374.63</v>
       </c>
       <c r="J547" t="n">
-        <v>708716.03</v>
+        <v>681337.91</v>
       </c>
     </row>
     <row r="548">
@@ -23165,13 +23165,13 @@
         <v>33128884.09</v>
       </c>
       <c r="H568" t="n">
-        <v>29938521.01</v>
+        <v>30703508.45</v>
       </c>
       <c r="I568" t="n">
-        <v>1905593.01</v>
+        <v>1985017.74</v>
       </c>
       <c r="J568" t="n">
-        <v>3190363.08</v>
+        <v>2425375.64</v>
       </c>
     </row>
     <row r="569">
@@ -23245,13 +23245,13 @@
         <v>33826877.05</v>
       </c>
       <c r="H570" t="n">
-        <v>28979164.65</v>
+        <v>29210734.29</v>
       </c>
       <c r="I570" t="n">
-        <v>1329854.23</v>
+        <v>1346526.87</v>
       </c>
       <c r="J570" t="n">
-        <v>4847712.4</v>
+        <v>4616142.76</v>
       </c>
     </row>
     <row r="571">
@@ -23285,13 +23285,13 @@
         <v>75282924.23</v>
       </c>
       <c r="H571" t="n">
-        <v>49530165.98</v>
+        <v>50964371.23</v>
       </c>
       <c r="I571" t="n">
-        <v>2871590.78</v>
+        <v>2994474.72</v>
       </c>
       <c r="J571" t="n">
-        <v>25752758.25</v>
+        <v>24318553</v>
       </c>
     </row>
     <row r="572">
@@ -24165,13 +24165,13 @@
         <v>37310856.76</v>
       </c>
       <c r="H593" t="n">
-        <v>29934224.39</v>
+        <v>30828416.26</v>
       </c>
       <c r="I593" t="n">
-        <v>1561880.22</v>
+        <v>1645889.91</v>
       </c>
       <c r="J593" t="n">
-        <v>7376632.37</v>
+        <v>6482440.5</v>
       </c>
     </row>
     <row r="594">
@@ -24285,13 +24285,13 @@
         <v>47005570.55</v>
       </c>
       <c r="H596" t="n">
-        <v>23005707.02</v>
+        <v>23528643.71</v>
       </c>
       <c r="I596" t="n">
-        <v>1065585.4</v>
+        <v>1104146.56</v>
       </c>
       <c r="J596" t="n">
-        <v>23999863.53</v>
+        <v>23476926.84</v>
       </c>
     </row>
     <row r="597">
@@ -24325,13 +24325,13 @@
         <v>51333755.33</v>
       </c>
       <c r="H597" t="n">
-        <v>21600091.6</v>
+        <v>23304932.85</v>
       </c>
       <c r="I597" t="n">
-        <v>1130458.87</v>
+        <v>1252057.26</v>
       </c>
       <c r="J597" t="n">
-        <v>29733663.73</v>
+        <v>28028822.48</v>
       </c>
     </row>
     <row r="598">
@@ -24365,13 +24365,13 @@
         <v>50062054.28</v>
       </c>
       <c r="H598" t="n">
-        <v>24152609.14</v>
+        <v>26145936.44</v>
       </c>
       <c r="I598" t="n">
-        <v>1146491.71</v>
+        <v>1281115.95</v>
       </c>
       <c r="J598" t="n">
-        <v>25909445.14</v>
+        <v>23916117.84</v>
       </c>
     </row>
     <row r="599">
@@ -24405,13 +24405,13 @@
         <v>49131721.25</v>
       </c>
       <c r="H599" t="n">
-        <v>24194469.19</v>
+        <v>25075761.49</v>
       </c>
       <c r="I599" t="n">
-        <v>919247.1</v>
+        <v>984837.09</v>
       </c>
       <c r="J599" t="n">
-        <v>24937252.06</v>
+        <v>24055959.76</v>
       </c>
     </row>
     <row r="600">
@@ -24485,13 +24485,13 @@
         <v>47758833.23</v>
       </c>
       <c r="H601" t="n">
-        <v>27758013.78</v>
+        <v>29365376.04</v>
       </c>
       <c r="I601" t="n">
-        <v>1159437.88</v>
+        <v>1263434.93</v>
       </c>
       <c r="J601" t="n">
-        <v>20000819.45</v>
+        <v>18393457.19</v>
       </c>
     </row>
     <row r="602">
@@ -24565,13 +24565,13 @@
         <v>13735008.46</v>
       </c>
       <c r="H603" t="n">
-        <v>12277111.63</v>
+        <v>12437651.25</v>
       </c>
       <c r="I603" t="n">
-        <v>827898.05</v>
+        <v>845771.1899999999</v>
       </c>
       <c r="J603" t="n">
-        <v>1457896.83</v>
+        <v>1297357.21</v>
       </c>
     </row>
     <row r="604">
@@ -24605,13 +24605,13 @@
         <v>1484780.82</v>
       </c>
       <c r="H604" t="n">
-        <v>759251.79</v>
+        <v>923251.2</v>
       </c>
       <c r="I604" t="n">
-        <v>26700.76</v>
+        <v>38869.51</v>
       </c>
       <c r="J604" t="n">
-        <v>725529.03</v>
+        <v>561529.62</v>
       </c>
     </row>
     <row r="605">
@@ -24725,13 +24725,13 @@
         <v>9885230.82</v>
       </c>
       <c r="H607" t="n">
-        <v>4675593.17</v>
+        <v>4953180.67</v>
       </c>
       <c r="I607" t="n">
         <v>0</v>
       </c>
       <c r="J607" t="n">
-        <v>5209637.65</v>
+        <v>4932050.15</v>
       </c>
     </row>
     <row r="608">
@@ -25205,13 +25205,13 @@
         <v>4917800.43</v>
       </c>
       <c r="H619" t="n">
-        <v>0</v>
+        <v>208430.57</v>
       </c>
       <c r="I619" t="n">
-        <v>0</v>
+        <v>10175.13</v>
       </c>
       <c r="J619" t="n">
-        <v>4917800.43</v>
+        <v>4709369.86</v>
       </c>
     </row>
     <row r="620">
@@ -25325,13 +25325,13 @@
         <v>39334571.99</v>
       </c>
       <c r="H622" t="n">
-        <v>8620630.609999999</v>
+        <v>10734557.59</v>
       </c>
       <c r="I622" t="n">
-        <v>251344.61</v>
+        <v>315285.64</v>
       </c>
       <c r="J622" t="n">
-        <v>30713941.38</v>
+        <v>28600014.4</v>
       </c>
     </row>
     <row r="623">
@@ -25405,13 +25405,13 @@
         <v>31648004.35</v>
       </c>
       <c r="H624" t="n">
-        <v>27179395.08</v>
+        <v>27221408.52</v>
       </c>
       <c r="I624" t="n">
-        <v>334304.68</v>
+        <v>335837.84</v>
       </c>
       <c r="J624" t="n">
-        <v>4468609.27</v>
+        <v>4426595.83</v>
       </c>
     </row>
     <row r="625">
@@ -25445,13 +25445,13 @@
         <v>9659997.08</v>
       </c>
       <c r="H625" t="n">
-        <v>153335</v>
+        <v>206968.35</v>
       </c>
       <c r="I625" t="n">
-        <v>14183.47</v>
+        <v>19144.55</v>
       </c>
       <c r="J625" t="n">
-        <v>9506662.08</v>
+        <v>9453028.73</v>
       </c>
     </row>
     <row r="626">
@@ -25525,13 +25525,13 @@
         <v>5774752.44</v>
       </c>
       <c r="H627" t="n">
-        <v>1744569.6</v>
+        <v>1912436.46</v>
       </c>
       <c r="I627" t="n">
-        <v>66890.25999999999</v>
+        <v>77533.00999999999</v>
       </c>
       <c r="J627" t="n">
-        <v>4030182.84</v>
+        <v>3862315.98</v>
       </c>
     </row>
     <row r="628">
@@ -25565,13 +25565,13 @@
         <v>8415499.810000001</v>
       </c>
       <c r="H628" t="n">
-        <v>2407110.85</v>
+        <v>2984135.57</v>
       </c>
       <c r="I628" t="n">
-        <v>82826.58</v>
+        <v>105011.73</v>
       </c>
       <c r="J628" t="n">
-        <v>6008388.96</v>
+        <v>5431364.24</v>
       </c>
     </row>
     <row r="629">
@@ -25765,13 +25765,13 @@
         <v>803371.39</v>
       </c>
       <c r="H633" t="n">
-        <v>263096.11</v>
+        <v>307553.14</v>
       </c>
       <c r="I633" t="n">
-        <v>10984.67</v>
+        <v>13149.72</v>
       </c>
       <c r="J633" t="n">
-        <v>540275.28</v>
+        <v>495818.25</v>
       </c>
     </row>
     <row r="634">
@@ -25965,13 +25965,13 @@
         <v>49093539.45</v>
       </c>
       <c r="H638" t="n">
-        <v>4634384.99</v>
+        <v>5181810.35</v>
       </c>
       <c r="I638" t="n">
-        <v>33669.31</v>
+        <v>41982.04</v>
       </c>
       <c r="J638" t="n">
-        <v>44459154.46</v>
+        <v>43911729.1</v>
       </c>
     </row>
     <row r="639">
@@ -26085,13 +26085,13 @@
         <v>9522992.289999999</v>
       </c>
       <c r="H641" t="n">
-        <v>2703721.53</v>
+        <v>2955353.01</v>
       </c>
       <c r="I641" t="n">
-        <v>43602.39</v>
+        <v>51034.6</v>
       </c>
       <c r="J641" t="n">
-        <v>6819270.76</v>
+        <v>6567639.28</v>
       </c>
     </row>
     <row r="642">
@@ -26125,13 +26125,13 @@
         <v>51814575.44</v>
       </c>
       <c r="H642" t="n">
-        <v>5982264.67</v>
+        <v>6832001.61</v>
       </c>
       <c r="I642" t="n">
-        <v>74117.67999999999</v>
+        <v>97809.87</v>
       </c>
       <c r="J642" t="n">
-        <v>45832310.77</v>
+        <v>44982573.83</v>
       </c>
     </row>
     <row r="643">
@@ -26165,13 +26165,13 @@
         <v>50960749.38</v>
       </c>
       <c r="H643" t="n">
-        <v>5226168.65</v>
+        <v>5881370.48</v>
       </c>
       <c r="I643" t="n">
-        <v>39243.01</v>
+        <v>49202.31</v>
       </c>
       <c r="J643" t="n">
-        <v>45734580.73</v>
+        <v>45079378.9</v>
       </c>
     </row>
     <row r="644">
@@ -26205,13 +26205,13 @@
         <v>53356791.72</v>
       </c>
       <c r="H644" t="n">
-        <v>8108338.48</v>
+        <v>9603132.49</v>
       </c>
       <c r="I644" t="n">
-        <v>107589.5</v>
+        <v>146432.54</v>
       </c>
       <c r="J644" t="n">
-        <v>45248453.24</v>
+        <v>43753659.23</v>
       </c>
     </row>
     <row r="645">
@@ -26245,13 +26245,13 @@
         <v>53241874.38</v>
       </c>
       <c r="H645" t="n">
-        <v>10278516.91</v>
+        <v>11593843.28</v>
       </c>
       <c r="I645" t="n">
-        <v>103589.31</v>
+        <v>129819.98</v>
       </c>
       <c r="J645" t="n">
-        <v>42963357.47</v>
+        <v>41648031.1</v>
       </c>
     </row>
     <row r="646">
@@ -26285,13 +26285,13 @@
         <v>59299394.97</v>
       </c>
       <c r="H646" t="n">
-        <v>22747695.41</v>
+        <v>24082394.71</v>
       </c>
       <c r="I646" t="n">
-        <v>197398.65</v>
+        <v>225294.14</v>
       </c>
       <c r="J646" t="n">
-        <v>36551699.56</v>
+        <v>35217000.26</v>
       </c>
     </row>
     <row r="647">
@@ -26365,13 +26365,13 @@
         <v>1655673.22</v>
       </c>
       <c r="H648" t="n">
-        <v>261385</v>
+        <v>375709.28</v>
       </c>
       <c r="I648" t="n">
-        <v>4014.01</v>
+        <v>8141.11</v>
       </c>
       <c r="J648" t="n">
-        <v>1394288.22</v>
+        <v>1279963.94</v>
       </c>
     </row>
     <row r="649">
@@ -26405,13 +26405,13 @@
         <v>9284408.859999999</v>
       </c>
       <c r="H649" t="n">
-        <v>1295218.13</v>
+        <v>1544810.85</v>
       </c>
       <c r="I649" t="n">
-        <v>32866.19</v>
+        <v>41876.47</v>
       </c>
       <c r="J649" t="n">
-        <v>7989190.73</v>
+        <v>7739598.01</v>
       </c>
     </row>
     <row r="650">
@@ -26445,13 +26445,13 @@
         <v>9218472.49</v>
       </c>
       <c r="H650" t="n">
-        <v>829896.92</v>
+        <v>1041486.75</v>
       </c>
       <c r="I650" t="n">
-        <v>25417.53</v>
+        <v>33055.91</v>
       </c>
       <c r="J650" t="n">
-        <v>8388575.57</v>
+        <v>8176985.74</v>
       </c>
     </row>
     <row r="651">
@@ -26485,13 +26485,13 @@
         <v>64984305.34</v>
       </c>
       <c r="H651" t="n">
-        <v>1000383.75</v>
+        <v>2647093.02</v>
       </c>
       <c r="I651" t="n">
-        <v>34560.42</v>
+        <v>76958.82000000001</v>
       </c>
       <c r="J651" t="n">
-        <v>63983921.59</v>
+        <v>62337212.32</v>
       </c>
     </row>
     <row r="652">
@@ -26525,13 +26525,13 @@
         <v>14704896.91</v>
       </c>
       <c r="H652" t="n">
-        <v>805855.4399999999</v>
+        <v>1937021.67</v>
       </c>
       <c r="I652" t="n">
-        <v>73274.23</v>
+        <v>213905.91</v>
       </c>
       <c r="J652" t="n">
-        <v>13899041.47</v>
+        <v>12767875.24</v>
       </c>
     </row>
     <row r="653">
@@ -26565,13 +26565,13 @@
         <v>12403029.87</v>
       </c>
       <c r="H653" t="n">
-        <v>896838.3100000001</v>
+        <v>1614142.18</v>
       </c>
       <c r="I653" t="n">
-        <v>69963.45</v>
+        <v>134082.77</v>
       </c>
       <c r="J653" t="n">
-        <v>11506191.56</v>
+        <v>10788887.69</v>
       </c>
     </row>
     <row r="654">
@@ -26605,13 +26605,13 @@
         <v>2624909.09</v>
       </c>
       <c r="H654" t="n">
-        <v>155585.6</v>
+        <v>258309.25</v>
       </c>
       <c r="I654" t="n">
-        <v>3067.68</v>
+        <v>6344.56</v>
       </c>
       <c r="J654" t="n">
-        <v>2469323.49</v>
+        <v>2366599.84</v>
       </c>
     </row>
     <row r="655">
@@ -26685,13 +26685,13 @@
         <v>12585961.98</v>
       </c>
       <c r="H656" t="n">
-        <v>792234.27</v>
+        <v>1511276.19</v>
       </c>
       <c r="I656" t="n">
-        <v>71680.64</v>
+        <v>138325.23</v>
       </c>
       <c r="J656" t="n">
-        <v>11793727.71</v>
+        <v>11074685.79</v>
       </c>
     </row>
     <row r="657">
@@ -26725,13 +26725,13 @@
         <v>27994383.03</v>
       </c>
       <c r="H657" t="n">
-        <v>1555732.35</v>
+        <v>2365248.99</v>
       </c>
       <c r="I657" t="n">
-        <v>331506.92</v>
+        <v>504016.44</v>
       </c>
       <c r="J657" t="n">
-        <v>26438650.68</v>
+        <v>25629134.04</v>
       </c>
     </row>
     <row r="658">
@@ -26765,13 +26765,13 @@
         <v>12159273.83</v>
       </c>
       <c r="H658" t="n">
-        <v>2524796.62</v>
+        <v>3823205.97</v>
       </c>
       <c r="I658" t="n">
-        <v>189478.08</v>
+        <v>313522.25</v>
       </c>
       <c r="J658" t="n">
-        <v>9634477.210000001</v>
+        <v>8336067.86</v>
       </c>
     </row>
     <row r="659">
@@ -26885,13 +26885,13 @@
         <v>14929346.95</v>
       </c>
       <c r="H661" t="n">
-        <v>551298.7</v>
+        <v>833120.1899999999</v>
       </c>
       <c r="I661" t="n">
-        <v>118361.5</v>
+        <v>178892.04</v>
       </c>
       <c r="J661" t="n">
-        <v>14378048.25</v>
+        <v>14096226.76</v>
       </c>
     </row>
     <row r="662">
@@ -26965,13 +26965,13 @@
         <v>15304996.19</v>
       </c>
       <c r="H663" t="n">
-        <v>593834.61</v>
+        <v>1636050.93</v>
       </c>
       <c r="I663" t="n">
-        <v>72067.83</v>
+        <v>184473.31</v>
       </c>
       <c r="J663" t="n">
-        <v>14711161.58</v>
+        <v>13668945.26</v>
       </c>
     </row>
     <row r="664">
@@ -27005,13 +27005,13 @@
         <v>6199729.76</v>
       </c>
       <c r="H664" t="n">
-        <v>0</v>
+        <v>289152.96</v>
       </c>
       <c r="I664" t="n">
         <v>0</v>
       </c>
       <c r="J664" t="n">
-        <v>6199729.76</v>
+        <v>5910576.8</v>
       </c>
     </row>
     <row r="665">
@@ -27045,13 +27045,13 @@
         <v>10929975.56</v>
       </c>
       <c r="H665" t="n">
-        <v>0</v>
+        <v>405673.71</v>
       </c>
       <c r="I665" t="n">
         <v>0</v>
       </c>
       <c r="J665" t="n">
-        <v>10929975.56</v>
+        <v>10524301.85</v>
       </c>
     </row>
     <row r="666">
@@ -27125,13 +27125,13 @@
         <v>41984578.11</v>
       </c>
       <c r="H667" t="n">
-        <v>0</v>
+        <v>3794113.75</v>
       </c>
       <c r="I667" t="n">
         <v>0</v>
       </c>
       <c r="J667" t="n">
-        <v>41984578.11</v>
+        <v>38190464.36</v>
       </c>
     </row>
     <row r="668">
@@ -27285,13 +27285,13 @@
         <v>20125000</v>
       </c>
       <c r="H671" t="n">
-        <v>0</v>
+        <v>865117.08</v>
       </c>
       <c r="I671" t="n">
-        <v>0</v>
+        <v>36023.22</v>
       </c>
       <c r="J671" t="n">
-        <v>20125000</v>
+        <v>19259882.92</v>
       </c>
     </row>
     <row r="672">
@@ -27325,13 +27325,13 @@
         <v>59889999.58</v>
       </c>
       <c r="H672" t="n">
-        <v>0</v>
+        <v>897085.83</v>
       </c>
       <c r="I672" t="n">
-        <v>0</v>
+        <v>47341.54</v>
       </c>
       <c r="J672" t="n">
-        <v>59889999.58</v>
+        <v>58992913.75</v>
       </c>
     </row>
     <row r="673">
@@ -27485,13 +27485,13 @@
         <v>13190992.89</v>
       </c>
       <c r="H676" t="n">
-        <v>592401.33</v>
+        <v>1124617.17</v>
       </c>
       <c r="I676" t="n">
-        <v>71211.28999999999</v>
+        <v>126675.2</v>
       </c>
       <c r="J676" t="n">
-        <v>12598591.56</v>
+        <v>12066375.72</v>
       </c>
     </row>
     <row r="677">
@@ -27525,13 +27525,13 @@
         <v>14398046.07</v>
       </c>
       <c r="H677" t="n">
-        <v>318583.52</v>
+        <v>647838.1</v>
       </c>
       <c r="I677" t="n">
-        <v>30598.96</v>
+        <v>75894.34</v>
       </c>
       <c r="J677" t="n">
-        <v>14079462.55</v>
+        <v>13750207.97</v>
       </c>
     </row>
     <row r="678">
@@ -27857,7 +27857,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -27867,22 +27867,22 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>37600000</v>
+        <v>29302939.12</v>
       </c>
       <c r="F686" t="n">
         <v>0</v>
       </c>
       <c r="G686" t="n">
-        <v>37600000</v>
+        <v>29302939.12</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -27891,38 +27891,38 @@
         <v>0</v>
       </c>
       <c r="J686" t="n">
-        <v>37600000</v>
+        <v>29302939.12</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>1099724.43</v>
+        <v>36954174.97</v>
       </c>
       <c r="F687" t="n">
         <v>0</v>
       </c>
       <c r="G687" t="n">
-        <v>1099724.43</v>
+        <v>36954174.97</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -27931,13 +27931,13 @@
         <v>0</v>
       </c>
       <c r="J687" t="n">
-        <v>1099724.43</v>
+        <v>36954174.97</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DO-009482017/2025</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -27947,22 +27947,22 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>47349998.43</v>
+        <v>5342582.88</v>
       </c>
       <c r="F688" t="n">
         <v>0</v>
       </c>
       <c r="G688" t="n">
-        <v>47349998.43</v>
+        <v>5342582.88</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -27971,13 +27971,13 @@
         <v>0</v>
       </c>
       <c r="J688" t="n">
-        <v>47349998.43</v>
+        <v>5342582.88</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DO-9493205/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -27987,22 +27987,22 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>31699998.96</v>
+        <v>33205062.4</v>
       </c>
       <c r="F689" t="n">
         <v>0</v>
       </c>
       <c r="G689" t="n">
-        <v>31699998.96</v>
+        <v>33205062.4</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -28011,38 +28011,38 @@
         <v>0</v>
       </c>
       <c r="J689" t="n">
-        <v>31699998.96</v>
+        <v>33205062.4</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>D0-009482032/2025</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00)</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>35989998.13</v>
+        <v>4005503.13</v>
       </c>
       <c r="F690" t="n">
         <v>0</v>
       </c>
       <c r="G690" t="n">
-        <v>35989998.13</v>
+        <v>4005503.13</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -28051,13 +28051,13 @@
         <v>0</v>
       </c>
       <c r="J690" t="n">
-        <v>35989998.13</v>
+        <v>4005503.13</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DO-9481987/2025</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -28067,22 +28067,22 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00)</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>23434999.8</v>
+        <v>2520936.14</v>
       </c>
       <c r="F691" t="n">
         <v>0</v>
       </c>
       <c r="G691" t="n">
-        <v>23434999.8</v>
+        <v>2520936.14</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -28091,38 +28091,38 @@
         <v>0</v>
       </c>
       <c r="J691" t="n">
-        <v>23434999.8</v>
+        <v>2520936.14</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>DO-009482055/2025</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>32097999.96</v>
+        <v>3287560.73</v>
       </c>
       <c r="F692" t="n">
         <v>0</v>
       </c>
       <c r="G692" t="n">
-        <v>32097999.96</v>
+        <v>3287560.73</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -28131,13 +28131,13 @@
         <v>0</v>
       </c>
       <c r="J692" t="n">
-        <v>32097999.96</v>
+        <v>3287560.73</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -28147,22 +28147,22 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>14264750.82</v>
+        <v>37600000</v>
       </c>
       <c r="F693" t="n">
         <v>0</v>
       </c>
       <c r="G693" t="n">
-        <v>14264750.82</v>
+        <v>37600000</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -28171,38 +28171,38 @@
         <v>0</v>
       </c>
       <c r="J693" t="n">
-        <v>14264750.82</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>32998445.8</v>
+        <v>1099724.43</v>
       </c>
       <c r="F694" t="n">
         <v>0</v>
       </c>
       <c r="G694" t="n">
-        <v>32998445.8</v>
+        <v>1099724.43</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -28211,13 +28211,13 @@
         <v>0</v>
       </c>
       <c r="J694" t="n">
-        <v>32998445.8</v>
+        <v>1099724.43</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>DO-009482017/2025</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -28232,17 +28232,17 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>45188997.86</v>
+        <v>47349998.43</v>
       </c>
       <c r="F695" t="n">
         <v>0</v>
       </c>
       <c r="G695" t="n">
-        <v>45188997.86</v>
+        <v>47349998.43</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -28251,51 +28251,491 @@
         <v>0</v>
       </c>
       <c r="J695" t="n">
-        <v>45188997.86</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
+          <t>DO-9493205/2026</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>31699998.96</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" t="n">
+        <v>31699998.96</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0</v>
+      </c>
+      <c r="J696" t="n">
+        <v>31699998.96</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>D0-009482032/2025</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>35989998.13</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0</v>
+      </c>
+      <c r="G697" t="n">
+        <v>35989998.13</v>
+      </c>
+      <c r="H697" t="n">
+        <v>0</v>
+      </c>
+      <c r="I697" t="n">
+        <v>0</v>
+      </c>
+      <c r="J697" t="n">
+        <v>35989998.13</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>DO-9481987/2025</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0</v>
+      </c>
+      <c r="G698" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="H698" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0</v>
+      </c>
+      <c r="J698" t="n">
+        <v>23434999.8</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>DO-009482055/2025</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="H699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0</v>
+      </c>
+      <c r="J699" t="n">
+        <v>32097999.96</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="H700" t="n">
+        <v>0</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J700" t="n">
+        <v>14264750.82</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0</v>
+      </c>
+      <c r="G701" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="H701" t="n">
+        <v>604883.63</v>
+      </c>
+      <c r="I701" t="n">
+        <v>62432.08</v>
+      </c>
+      <c r="J701" t="n">
+        <v>32393562.17</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0</v>
+      </c>
+      <c r="G702" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="H702" t="n">
+        <v>0</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0</v>
+      </c>
+      <c r="J702" t="n">
+        <v>45188997.86</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
           <t>DO-009482014/2025</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
         <is>
           <t>Prestação de Serviços</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr">
+      <c r="D703" t="inlineStr">
         <is>
           <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
-      <c r="E696" t="n">
+      <c r="E703" t="n">
         <v>77898894.3</v>
       </c>
-      <c r="F696" t="n">
-        <v>0</v>
-      </c>
-      <c r="G696" t="n">
+      <c r="F703" t="n">
+        <v>0</v>
+      </c>
+      <c r="G703" t="n">
         <v>77898894.3</v>
       </c>
-      <c r="H696" t="n">
-        <v>0</v>
-      </c>
-      <c r="I696" t="n">
-        <v>0</v>
-      </c>
-      <c r="J696" t="n">
+      <c r="H703" t="n">
+        <v>0</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0</v>
+      </c>
+      <c r="J703" t="n">
         <v>77898894.3</v>
       </c>
     </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0</v>
+      </c>
+      <c r="G704" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="H704" t="n">
+        <v>0</v>
+      </c>
+      <c r="I704" t="n">
+        <v>0</v>
+      </c>
+      <c r="J704" t="n">
+        <v>24832463.21</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0</v>
+      </c>
+      <c r="G705" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="H705" t="n">
+        <v>0</v>
+      </c>
+      <c r="I705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J705" t="n">
+        <v>34422078.35</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0</v>
+      </c>
+      <c r="G706" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="H706" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J706" t="n">
+        <v>30603197.87</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>31172534.58</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0</v>
+      </c>
+      <c r="G707" t="n">
+        <v>31172534.58</v>
+      </c>
+      <c r="H707" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J707" t="n">
+        <v>31172534.58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J696"/>
+  <autoFilter ref="A1:J707"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$707</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$711</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J707"/>
+  <dimension ref="A1:J711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3845,13 +3845,13 @@
         <v>2814906.8</v>
       </c>
       <c r="H85" t="n">
-        <v>2733037.82</v>
+        <v>2738058.77</v>
       </c>
       <c r="I85" t="n">
-        <v>290615.2</v>
+        <v>291460.72</v>
       </c>
       <c r="J85" t="n">
-        <v>81868.98</v>
+        <v>76848.03</v>
       </c>
     </row>
     <row r="86">
@@ -5445,13 +5445,13 @@
         <v>7485474.87</v>
       </c>
       <c r="H125" t="n">
-        <v>6555969.19</v>
+        <v>6572398.61</v>
       </c>
       <c r="I125" t="n">
-        <v>7594736.43</v>
+        <v>7612144.85</v>
       </c>
       <c r="J125" t="n">
-        <v>929505.6800000001</v>
+        <v>913076.26</v>
       </c>
     </row>
     <row r="126">
@@ -18205,13 +18205,13 @@
         <v>28096598.89</v>
       </c>
       <c r="H444" t="n">
-        <v>26999282.29</v>
+        <v>27634042.2</v>
       </c>
       <c r="I444" t="n">
-        <v>1385505.74</v>
+        <v>1443844.31</v>
       </c>
       <c r="J444" t="n">
-        <v>1097316.6</v>
+        <v>462556.69</v>
       </c>
     </row>
     <row r="445">
@@ -18365,13 +18365,13 @@
         <v>30648355.12</v>
       </c>
       <c r="H448" t="n">
-        <v>17173368.49</v>
+        <v>18729510.86</v>
       </c>
       <c r="I448" t="n">
-        <v>1180122.02</v>
+        <v>1331166.75</v>
       </c>
       <c r="J448" t="n">
-        <v>13474986.63</v>
+        <v>11918844.26</v>
       </c>
     </row>
     <row r="449">
@@ -18845,13 +18845,13 @@
         <v>3345699.13</v>
       </c>
       <c r="H460" t="n">
-        <v>2283579.27</v>
+        <v>2386069.14</v>
       </c>
       <c r="I460" t="n">
-        <v>183253.44</v>
+        <v>196495.13</v>
       </c>
       <c r="J460" t="n">
-        <v>1062119.86</v>
+        <v>959629.99</v>
       </c>
     </row>
     <row r="461">
@@ -19199,10 +19199,10 @@
         <v>46337191.41</v>
       </c>
       <c r="F469" t="n">
-        <v>0</v>
+        <v>1821413.8</v>
       </c>
       <c r="G469" t="n">
-        <v>46337191.41</v>
+        <v>48158605.21</v>
       </c>
       <c r="H469" t="n">
         <v>29856106.57</v>
@@ -19211,7 +19211,7 @@
         <v>1357169.26</v>
       </c>
       <c r="J469" t="n">
-        <v>16481084.84</v>
+        <v>18302498.64</v>
       </c>
     </row>
     <row r="470">
@@ -19759,10 +19759,10 @@
         <v>44482154.94</v>
       </c>
       <c r="F483" t="n">
-        <v>0</v>
+        <v>7757492.99</v>
       </c>
       <c r="G483" t="n">
-        <v>44482154.94</v>
+        <v>52239647.93</v>
       </c>
       <c r="H483" t="n">
         <v>17027419.71</v>
@@ -19771,7 +19771,7 @@
         <v>515574.38</v>
       </c>
       <c r="J483" t="n">
-        <v>27454735.23</v>
+        <v>35212228.22</v>
       </c>
     </row>
     <row r="484">
@@ -19885,13 +19885,13 @@
         <v>95661672.93000001</v>
       </c>
       <c r="H486" t="n">
-        <v>12480224.9</v>
+        <v>15151232.48</v>
       </c>
       <c r="I486" t="n">
-        <v>540755.11</v>
+        <v>646825.62</v>
       </c>
       <c r="J486" t="n">
-        <v>83181448.03</v>
+        <v>80510440.45</v>
       </c>
     </row>
     <row r="487">
@@ -20325,13 +20325,13 @@
         <v>181409015</v>
       </c>
       <c r="H497" t="n">
-        <v>22060526.99</v>
+        <v>29660203.15</v>
       </c>
       <c r="I497" t="n">
-        <v>310021.94</v>
+        <v>442407.81</v>
       </c>
       <c r="J497" t="n">
-        <v>159348488.01</v>
+        <v>151748811.85</v>
       </c>
     </row>
     <row r="498">
@@ -20405,13 +20405,13 @@
         <v>45918998.95</v>
       </c>
       <c r="H499" t="n">
-        <v>1575614.78</v>
+        <v>2216386.72</v>
       </c>
       <c r="I499" t="n">
-        <v>26742.86</v>
+        <v>42264.81</v>
       </c>
       <c r="J499" t="n">
-        <v>44343384.17</v>
+        <v>43702612.23</v>
       </c>
     </row>
     <row r="500">
@@ -23925,13 +23925,13 @@
         <v>24582835.86</v>
       </c>
       <c r="H587" t="n">
-        <v>11273665.11</v>
+        <v>11441711.93</v>
       </c>
       <c r="I587" t="n">
-        <v>1842969.56</v>
+        <v>1878810.4</v>
       </c>
       <c r="J587" t="n">
-        <v>13309170.75</v>
+        <v>13141123.93</v>
       </c>
     </row>
     <row r="588">
@@ -23965,13 +23965,13 @@
         <v>9488185</v>
       </c>
       <c r="H588" t="n">
-        <v>4585196.15</v>
+        <v>4657695.76</v>
       </c>
       <c r="I588" t="n">
-        <v>751841.25</v>
+        <v>767211.13</v>
       </c>
       <c r="J588" t="n">
-        <v>4902988.85</v>
+        <v>4830489.24</v>
       </c>
     </row>
     <row r="589">
@@ -24205,13 +24205,13 @@
         <v>37153801.63</v>
       </c>
       <c r="H594" t="n">
-        <v>30132401.34</v>
+        <v>31480840.39</v>
       </c>
       <c r="I594" t="n">
-        <v>1413980.61</v>
+        <v>1560103.92</v>
       </c>
       <c r="J594" t="n">
-        <v>7021400.29</v>
+        <v>5672961.24</v>
       </c>
     </row>
     <row r="595">
@@ -24245,13 +24245,13 @@
         <v>47556790.26</v>
       </c>
       <c r="H595" t="n">
-        <v>31001351.31</v>
+        <v>32145995.87</v>
       </c>
       <c r="I595" t="n">
-        <v>1306191.62</v>
+        <v>1389956.58</v>
       </c>
       <c r="J595" t="n">
-        <v>16555438.95</v>
+        <v>15410794.39</v>
       </c>
     </row>
     <row r="596">
@@ -25605,13 +25605,13 @@
         <v>4776981.58</v>
       </c>
       <c r="H629" t="n">
-        <v>2916164.28</v>
+        <v>3155692.55</v>
       </c>
       <c r="I629" t="n">
-        <v>93313.14999999999</v>
+        <v>101679.28</v>
       </c>
       <c r="J629" t="n">
-        <v>1860817.3</v>
+        <v>1621289.03</v>
       </c>
     </row>
     <row r="630">
@@ -26045,13 +26045,13 @@
         <v>2876761.94</v>
       </c>
       <c r="H640" t="n">
-        <v>2383339.88</v>
+        <v>2421023.53</v>
       </c>
       <c r="I640" t="n">
-        <v>99049.57000000001</v>
+        <v>102143.91</v>
       </c>
       <c r="J640" t="n">
-        <v>493422.06</v>
+        <v>455738.41</v>
       </c>
     </row>
     <row r="641">
@@ -26925,13 +26925,13 @@
         <v>3028048.96</v>
       </c>
       <c r="H662" t="n">
-        <v>151508.22</v>
+        <v>317502.27</v>
       </c>
       <c r="I662" t="n">
-        <v>4833.11</v>
+        <v>10128.32</v>
       </c>
       <c r="J662" t="n">
-        <v>2876540.74</v>
+        <v>2710546.69</v>
       </c>
     </row>
     <row r="663">
@@ -27085,13 +27085,13 @@
         <v>24492723.16</v>
       </c>
       <c r="H666" t="n">
-        <v>0</v>
+        <v>471547.81</v>
       </c>
       <c r="I666" t="n">
-        <v>0</v>
+        <v>100551.66</v>
       </c>
       <c r="J666" t="n">
-        <v>24492723.16</v>
+        <v>24021175.35</v>
       </c>
     </row>
     <row r="667">
@@ -27165,13 +27165,13 @@
         <v>9306630.199999999</v>
       </c>
       <c r="H668" t="n">
-        <v>0</v>
+        <v>202141.46</v>
       </c>
       <c r="I668" t="n">
-        <v>0</v>
+        <v>42853.93</v>
       </c>
       <c r="J668" t="n">
-        <v>9306630.199999999</v>
+        <v>9104488.74</v>
       </c>
     </row>
     <row r="669">
@@ -27205,13 +27205,13 @@
         <v>3187539.16</v>
       </c>
       <c r="H669" t="n">
-        <v>82179.63</v>
+        <v>191808.12</v>
       </c>
       <c r="I669" t="n">
-        <v>2621.53</v>
+        <v>6118.67</v>
       </c>
       <c r="J669" t="n">
-        <v>3105359.53</v>
+        <v>2995731.04</v>
       </c>
     </row>
     <row r="670">
@@ -27245,13 +27245,13 @@
         <v>4324285.68</v>
       </c>
       <c r="H670" t="n">
-        <v>70934.85000000001</v>
+        <v>170016.64</v>
       </c>
       <c r="I670" t="n">
-        <v>2262.82</v>
+        <v>5423.52</v>
       </c>
       <c r="J670" t="n">
-        <v>4253350.83</v>
+        <v>4154269.04</v>
       </c>
     </row>
     <row r="671">
@@ -27365,13 +27365,13 @@
         <v>6677404.33</v>
       </c>
       <c r="H673" t="n">
-        <v>119550.83</v>
+        <v>295085.15</v>
       </c>
       <c r="I673" t="n">
-        <v>3813.67</v>
+        <v>9413.209999999999</v>
       </c>
       <c r="J673" t="n">
-        <v>6557853.5</v>
+        <v>6382319.18</v>
       </c>
     </row>
     <row r="674">
@@ -28137,7 +28137,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -28147,22 +28147,22 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>37600000</v>
+        <v>31813334.15</v>
       </c>
       <c r="F693" t="n">
         <v>0</v>
       </c>
       <c r="G693" t="n">
-        <v>37600000</v>
+        <v>31813334.15</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -28171,38 +28171,38 @@
         <v>0</v>
       </c>
       <c r="J693" t="n">
-        <v>37600000</v>
+        <v>31813334.15</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>1099724.43</v>
+        <v>4506718.06</v>
       </c>
       <c r="F694" t="n">
         <v>0</v>
       </c>
       <c r="G694" t="n">
-        <v>1099724.43</v>
+        <v>4506718.06</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -28211,13 +28211,13 @@
         <v>0</v>
       </c>
       <c r="J694" t="n">
-        <v>1099724.43</v>
+        <v>4506718.06</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DO-009482017/2025</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -28227,22 +28227,22 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>47349998.43</v>
+        <v>36950516.6</v>
       </c>
       <c r="F695" t="n">
         <v>0</v>
       </c>
       <c r="G695" t="n">
-        <v>47349998.43</v>
+        <v>36950516.6</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -28251,13 +28251,13 @@
         <v>0</v>
       </c>
       <c r="J695" t="n">
-        <v>47349998.43</v>
+        <v>36950516.6</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>DO-9493205/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -28267,22 +28267,22 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>31699998.96</v>
+        <v>37600000</v>
       </c>
       <c r="F696" t="n">
         <v>0</v>
       </c>
       <c r="G696" t="n">
-        <v>31699998.96</v>
+        <v>37600000</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -28291,18 +28291,18 @@
         <v>0</v>
       </c>
       <c r="J696" t="n">
-        <v>31699998.96</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>D0-009482032/2025</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -28312,17 +28312,17 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>35989998.13</v>
+        <v>1099724.43</v>
       </c>
       <c r="F697" t="n">
         <v>0</v>
       </c>
       <c r="G697" t="n">
-        <v>35989998.13</v>
+        <v>1099724.43</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -28331,13 +28331,13 @@
         <v>0</v>
       </c>
       <c r="J697" t="n">
-        <v>35989998.13</v>
+        <v>1099724.43</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DO-9481987/2025</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -28352,17 +28352,17 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>23434999.8</v>
+        <v>47349998.43</v>
       </c>
       <c r="F698" t="n">
         <v>0</v>
       </c>
       <c r="G698" t="n">
-        <v>23434999.8</v>
+        <v>47349998.43</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -28371,13 +28371,13 @@
         <v>0</v>
       </c>
       <c r="J698" t="n">
-        <v>23434999.8</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DO-009482055/2025</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -28392,17 +28392,17 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>32097999.96</v>
+        <v>31699998.96</v>
       </c>
       <c r="F699" t="n">
         <v>0</v>
       </c>
       <c r="G699" t="n">
-        <v>32097999.96</v>
+        <v>31699998.96</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -28411,13 +28411,13 @@
         <v>0</v>
       </c>
       <c r="J699" t="n">
-        <v>32097999.96</v>
+        <v>31699998.96</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -28427,22 +28427,22 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>14264750.82</v>
+        <v>35989998.13</v>
       </c>
       <c r="F700" t="n">
         <v>0</v>
       </c>
       <c r="G700" t="n">
-        <v>14264750.82</v>
+        <v>35989998.13</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -28451,13 +28451,13 @@
         <v>0</v>
       </c>
       <c r="J700" t="n">
-        <v>14264750.82</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -28467,37 +28467,37 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>32998445.8</v>
+        <v>23434999.8</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
       </c>
       <c r="G701" t="n">
-        <v>32998445.8</v>
+        <v>23434999.8</v>
       </c>
       <c r="H701" t="n">
-        <v>604883.63</v>
+        <v>0</v>
       </c>
       <c r="I701" t="n">
-        <v>62432.08</v>
+        <v>0</v>
       </c>
       <c r="J701" t="n">
-        <v>32393562.17</v>
+        <v>23434999.8</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -28512,17 +28512,17 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>45188997.86</v>
+        <v>32097999.96</v>
       </c>
       <c r="F702" t="n">
         <v>0</v>
       </c>
       <c r="G702" t="n">
-        <v>45188997.86</v>
+        <v>32097999.96</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -28531,13 +28531,13 @@
         <v>0</v>
       </c>
       <c r="J702" t="n">
-        <v>45188997.86</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>DO-009482014/2025</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -28547,22 +28547,22 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>77898894.3</v>
+        <v>0</v>
       </c>
       <c r="F703" t="n">
         <v>0</v>
       </c>
       <c r="G703" t="n">
-        <v>77898894.3</v>
+        <v>0</v>
       </c>
       <c r="H703" t="n">
         <v>0</v>
@@ -28571,13 +28571,13 @@
         <v>0</v>
       </c>
       <c r="J703" t="n">
-        <v>77898894.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -28587,22 +28587,22 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>24832463.21</v>
+        <v>14264750.82</v>
       </c>
       <c r="F704" t="n">
         <v>0</v>
       </c>
       <c r="G704" t="n">
-        <v>24832463.21</v>
+        <v>14264750.82</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -28611,13 +28611,13 @@
         <v>0</v>
       </c>
       <c r="J704" t="n">
-        <v>24832463.21</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -28632,32 +28632,32 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>34422078.35</v>
+        <v>32998445.8</v>
       </c>
       <c r="F705" t="n">
         <v>0</v>
       </c>
       <c r="G705" t="n">
-        <v>34422078.35</v>
+        <v>32998445.8</v>
       </c>
       <c r="H705" t="n">
-        <v>0</v>
+        <v>604883.63</v>
       </c>
       <c r="I705" t="n">
-        <v>0</v>
+        <v>62432.08</v>
       </c>
       <c r="J705" t="n">
-        <v>34422078.35</v>
+        <v>32393562.17</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -28667,22 +28667,22 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>30603197.87</v>
+        <v>45188997.86</v>
       </c>
       <c r="F706" t="n">
         <v>0</v>
       </c>
       <c r="G706" t="n">
-        <v>30603197.87</v>
+        <v>45188997.86</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -28691,51 +28691,211 @@
         <v>0</v>
       </c>
       <c r="J706" t="n">
-        <v>30603197.87</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0</v>
+      </c>
+      <c r="G707" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="H707" t="n">
+        <v>0</v>
+      </c>
+      <c r="I707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J707" t="n">
+        <v>77898894.3</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0</v>
+      </c>
+      <c r="G708" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="H708" t="n">
+        <v>0</v>
+      </c>
+      <c r="I708" t="n">
+        <v>0</v>
+      </c>
+      <c r="J708" t="n">
+        <v>24832463.21</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0</v>
+      </c>
+      <c r="G709" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="H709" t="n">
+        <v>0</v>
+      </c>
+      <c r="I709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J709" t="n">
+        <v>34422078.35</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0</v>
+      </c>
+      <c r="G710" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="H710" t="n">
+        <v>0</v>
+      </c>
+      <c r="I710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J710" t="n">
+        <v>30603197.87</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C707" t="inlineStr">
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr">
+      <c r="D711" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="E707" t="n">
+      <c r="E711" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="F707" t="n">
-        <v>0</v>
-      </c>
-      <c r="G707" t="n">
+      <c r="F711" t="n">
+        <v>0</v>
+      </c>
+      <c r="G711" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="H707" t="n">
-        <v>0</v>
-      </c>
-      <c r="I707" t="n">
-        <v>0</v>
-      </c>
-      <c r="J707" t="n">
+      <c r="H711" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" t="n">
+        <v>0</v>
+      </c>
+      <c r="J711" t="n">
         <v>31172534.58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J707"/>
+  <autoFilter ref="A1:J711"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$711</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$714</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J711"/>
+  <dimension ref="A1:J714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17765,13 +17765,13 @@
         <v>38819029.96</v>
       </c>
       <c r="H433" t="n">
-        <v>34740432.66</v>
+        <v>35394992.2</v>
       </c>
       <c r="I433" t="n">
-        <v>2122047.18</v>
+        <v>2174619.26</v>
       </c>
       <c r="J433" t="n">
-        <v>4078597.3</v>
+        <v>3424037.76</v>
       </c>
     </row>
     <row r="434">
@@ -17999,10 +17999,10 @@
         <v>1425000</v>
       </c>
       <c r="F439" t="n">
-        <v>0</v>
+        <v>-11585.2</v>
       </c>
       <c r="G439" t="n">
-        <v>1425000</v>
+        <v>1413414.8</v>
       </c>
       <c r="H439" t="n">
         <v>1051152.96</v>
@@ -18011,7 +18011,7 @@
         <v>60859.04</v>
       </c>
       <c r="J439" t="n">
-        <v>373847.04</v>
+        <v>362261.84</v>
       </c>
     </row>
     <row r="440">
@@ -18325,13 +18325,13 @@
         <v>41801980.63</v>
       </c>
       <c r="H447" t="n">
-        <v>37778568.04</v>
+        <v>38850140.53</v>
       </c>
       <c r="I447" t="n">
-        <v>2690060.18</v>
+        <v>2809692.02</v>
       </c>
       <c r="J447" t="n">
-        <v>4023412.59</v>
+        <v>2951840.1</v>
       </c>
     </row>
     <row r="448">
@@ -19125,13 +19125,13 @@
         <v>52604103.19</v>
       </c>
       <c r="H467" t="n">
-        <v>33806452.17</v>
+        <v>35353156.02</v>
       </c>
       <c r="I467" t="n">
-        <v>1522593.9</v>
+        <v>1631513.09</v>
       </c>
       <c r="J467" t="n">
-        <v>18797651.02</v>
+        <v>17250947.17</v>
       </c>
     </row>
     <row r="468">
@@ -19365,13 +19365,13 @@
         <v>10982401.77</v>
       </c>
       <c r="H473" t="n">
-        <v>2486659.38</v>
+        <v>2659709.31</v>
       </c>
       <c r="I473" t="n">
-        <v>101795.87</v>
+        <v>110914.7</v>
       </c>
       <c r="J473" t="n">
-        <v>8495742.390000001</v>
+        <v>8322692.46</v>
       </c>
     </row>
     <row r="474">
@@ -19485,13 +19485,13 @@
         <v>152176229.73</v>
       </c>
       <c r="H476" t="n">
-        <v>61434407.65</v>
+        <v>70201621.12</v>
       </c>
       <c r="I476" t="n">
-        <v>2379545.29</v>
+        <v>2927446.71</v>
       </c>
       <c r="J476" t="n">
-        <v>90741822.08</v>
+        <v>81974608.61</v>
       </c>
     </row>
     <row r="477">
@@ -19645,13 +19645,13 @@
         <v>2540551.02</v>
       </c>
       <c r="H480" t="n">
-        <v>129788.89</v>
+        <v>143989.05</v>
       </c>
       <c r="I480" t="n">
-        <v>5961.25</v>
+        <v>7014.9</v>
       </c>
       <c r="J480" t="n">
-        <v>2410762.13</v>
+        <v>2396561.97</v>
       </c>
     </row>
     <row r="481">
@@ -20005,13 +20005,13 @@
         <v>30872072.3</v>
       </c>
       <c r="H489" t="n">
-        <v>3733445.15</v>
+        <v>4321961.53</v>
       </c>
       <c r="I489" t="n">
-        <v>90400.14999999999</v>
+        <v>111645.58</v>
       </c>
       <c r="J489" t="n">
-        <v>27138627.15</v>
+        <v>26550110.77</v>
       </c>
     </row>
     <row r="490">
@@ -20085,13 +20085,13 @@
         <v>3900717.4</v>
       </c>
       <c r="H491" t="n">
-        <v>1798925.05</v>
+        <v>2016899.4</v>
       </c>
       <c r="I491" t="n">
-        <v>917991.39</v>
+        <v>1029223.7</v>
       </c>
       <c r="J491" t="n">
-        <v>2101792.35</v>
+        <v>1883818</v>
       </c>
     </row>
     <row r="492">
@@ -20165,13 +20165,13 @@
         <v>44573000</v>
       </c>
       <c r="H493" t="n">
-        <v>4670098.83</v>
+        <v>5120476.8</v>
       </c>
       <c r="I493" t="n">
-        <v>66649.77</v>
+        <v>77902.28999999999</v>
       </c>
       <c r="J493" t="n">
-        <v>39902901.17</v>
+        <v>39452523.2</v>
       </c>
     </row>
     <row r="494">
@@ -20205,13 +20205,13 @@
         <v>22458906.7</v>
       </c>
       <c r="H494" t="n">
-        <v>1487538.65</v>
+        <v>1773004.43</v>
       </c>
       <c r="I494" t="n">
-        <v>35530.91</v>
+        <v>45836.21</v>
       </c>
       <c r="J494" t="n">
-        <v>20971368.05</v>
+        <v>20685902.27</v>
       </c>
     </row>
     <row r="495">
@@ -20445,13 +20445,13 @@
         <v>9634126.24</v>
       </c>
       <c r="H500" t="n">
-        <v>4736694.87</v>
+        <v>5546633.76</v>
       </c>
       <c r="I500" t="n">
-        <v>90981.28999999999</v>
+        <v>110994.77</v>
       </c>
       <c r="J500" t="n">
-        <v>4897431.37</v>
+        <v>4087492.48</v>
       </c>
     </row>
     <row r="501">
@@ -24725,13 +24725,13 @@
         <v>9885230.82</v>
       </c>
       <c r="H607" t="n">
-        <v>4953180.67</v>
+        <v>4994918.17</v>
       </c>
       <c r="I607" t="n">
         <v>0</v>
       </c>
       <c r="J607" t="n">
-        <v>4932050.15</v>
+        <v>4890312.65</v>
       </c>
     </row>
     <row r="608">
@@ -25685,13 +25685,13 @@
         <v>1346346.46</v>
       </c>
       <c r="H631" t="n">
-        <v>131945.13</v>
+        <v>172156.59</v>
       </c>
       <c r="I631" t="n">
-        <v>5409.74</v>
+        <v>8393.43</v>
       </c>
       <c r="J631" t="n">
-        <v>1214401.33</v>
+        <v>1174189.87</v>
       </c>
     </row>
     <row r="632">
@@ -26765,13 +26765,13 @@
         <v>12159273.83</v>
       </c>
       <c r="H658" t="n">
-        <v>3823205.97</v>
+        <v>4563869.02</v>
       </c>
       <c r="I658" t="n">
-        <v>313522.25</v>
+        <v>399359.72</v>
       </c>
       <c r="J658" t="n">
-        <v>8336067.86</v>
+        <v>7595404.81</v>
       </c>
     </row>
     <row r="659">
@@ -26805,13 +26805,13 @@
         <v>18749931.77</v>
       </c>
       <c r="H659" t="n">
-        <v>2160121.29</v>
+        <v>2951267.99</v>
       </c>
       <c r="I659" t="n">
-        <v>458510.34</v>
+        <v>626313.58</v>
       </c>
       <c r="J659" t="n">
-        <v>16589810.48</v>
+        <v>15798663.78</v>
       </c>
     </row>
     <row r="660">
@@ -26965,13 +26965,13 @@
         <v>15304996.19</v>
       </c>
       <c r="H663" t="n">
-        <v>1636050.93</v>
+        <v>3776564.13</v>
       </c>
       <c r="I663" t="n">
-        <v>184473.31</v>
+        <v>359723.53</v>
       </c>
       <c r="J663" t="n">
-        <v>13668945.26</v>
+        <v>11528432.06</v>
       </c>
     </row>
     <row r="664">
@@ -27657,32 +27657,32 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
+          <t>Manutenção Linha Verde e complexo viário da Cidade Administrativa</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>79488.85000000001</v>
+        <v>19798000</v>
       </c>
       <c r="F681" t="n">
         <v>0</v>
       </c>
       <c r="G681" t="n">
-        <v>79488.85000000001</v>
+        <v>19798000</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -27691,13 +27691,13 @@
         <v>0</v>
       </c>
       <c r="J681" t="n">
-        <v>79488.85000000001</v>
+        <v>19798000</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -27712,17 +27712,17 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
+          <t>Construção da Ponte sobre o Rio Corrente, no trecho de Munhoz - Toledo, rodovia MG-460, com 34,00m de extensão</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>5579340.09</v>
+        <v>2961858.84</v>
       </c>
       <c r="F682" t="n">
         <v>0</v>
       </c>
       <c r="G682" t="n">
-        <v>5579340.09</v>
+        <v>2961858.84</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -27731,38 +27731,38 @@
         <v>0</v>
       </c>
       <c r="J682" t="n">
-        <v>5579340.09</v>
+        <v>2961858.84</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Prestação de serviços especiais de apoio à coordenação e apoio técnico na Diretoria de Construção - Lote 1 - Supervisão de Projetos</t>
+          <t xml:space="preserve"> Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>23052682.68</v>
+        <v>79488.85000000001</v>
       </c>
       <c r="F683" t="n">
         <v>0</v>
       </c>
       <c r="G683" t="n">
-        <v>23052682.68</v>
+        <v>79488.85000000001</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -27771,13 +27771,13 @@
         <v>0</v>
       </c>
       <c r="J683" t="n">
-        <v>23052682.68</v>
+        <v>79488.85000000001</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -27787,22 +27787,22 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Trevo de Acesso</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação da interseção de acesso ao Presídio de Iturama, na via Municipal - Extensão 2,000km</t>
+          <t>Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>3700000</v>
+        <v>5579340.09</v>
       </c>
       <c r="F684" t="n">
         <v>0</v>
       </c>
       <c r="G684" t="n">
-        <v>3700000</v>
+        <v>5579340.09</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -27811,13 +27811,13 @@
         <v>0</v>
       </c>
       <c r="J684" t="n">
-        <v>3700000</v>
+        <v>5579340.09</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -27827,37 +27827,37 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
+          <t>Prestação de serviços especiais de apoio à coordenação e apoio técnico na Diretoria de Construção - Lote 1 - Supervisão de Projetos</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>12246076.65</v>
+        <v>23052682.68</v>
       </c>
       <c r="F685" t="n">
         <v>0</v>
       </c>
       <c r="G685" t="n">
-        <v>12246076.65</v>
+        <v>23052682.68</v>
       </c>
       <c r="H685" t="n">
-        <v>0</v>
+        <v>544858.86</v>
       </c>
       <c r="I685" t="n">
         <v>0</v>
       </c>
       <c r="J685" t="n">
-        <v>12246076.65</v>
+        <v>22507823.82</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -27867,22 +27867,22 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Trevo de Acesso</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
+          <t>Melhoramento e Pavimentação da interseção de acesso ao Presídio de Iturama, na via Municipal - Extensão 2,000km</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>29302939.12</v>
+        <v>3700000</v>
       </c>
       <c r="F686" t="n">
         <v>0</v>
       </c>
       <c r="G686" t="n">
-        <v>29302939.12</v>
+        <v>3700000</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -27891,13 +27891,13 @@
         <v>0</v>
       </c>
       <c r="J686" t="n">
-        <v>29302939.12</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -27907,22 +27907,22 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
+          <t>Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>36954174.97</v>
+        <v>12246076.65</v>
       </c>
       <c r="F687" t="n">
         <v>0</v>
       </c>
       <c r="G687" t="n">
-        <v>36954174.97</v>
+        <v>12246076.65</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -27931,13 +27931,13 @@
         <v>0</v>
       </c>
       <c r="J687" t="n">
-        <v>36954174.97</v>
+        <v>12246076.65</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -27947,22 +27947,22 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>5342582.88</v>
+        <v>29302939.12</v>
       </c>
       <c r="F688" t="n">
         <v>0</v>
       </c>
       <c r="G688" t="n">
-        <v>5342582.88</v>
+        <v>29302939.12</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -27971,13 +27971,13 @@
         <v>0</v>
       </c>
       <c r="J688" t="n">
-        <v>5342582.88</v>
+        <v>29302939.12</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -27992,72 +27992,72 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>33205062.4</v>
+        <v>36954174.97</v>
       </c>
       <c r="F689" t="n">
         <v>0</v>
       </c>
       <c r="G689" t="n">
-        <v>33205062.4</v>
+        <v>36954174.97</v>
       </c>
       <c r="H689" t="n">
-        <v>0</v>
+        <v>1155443.59</v>
       </c>
       <c r="I689" t="n">
-        <v>0</v>
+        <v>124341.92</v>
       </c>
       <c r="J689" t="n">
-        <v>33205062.4</v>
+        <v>35798731.38</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00)</t>
+          <t>Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>4005503.13</v>
+        <v>5342582.88</v>
       </c>
       <c r="F690" t="n">
         <v>0</v>
       </c>
       <c r="G690" t="n">
-        <v>4005503.13</v>
+        <v>5342582.88</v>
       </c>
       <c r="H690" t="n">
-        <v>0</v>
+        <v>1552.5</v>
       </c>
       <c r="I690" t="n">
         <v>0</v>
       </c>
       <c r="J690" t="n">
-        <v>4005503.13</v>
+        <v>5341030.38</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -28067,22 +28067,22 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00)</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2520936.14</v>
+        <v>33205062.4</v>
       </c>
       <c r="F691" t="n">
         <v>0</v>
       </c>
       <c r="G691" t="n">
-        <v>2520936.14</v>
+        <v>33205062.4</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -28091,7 +28091,7 @@
         <v>0</v>
       </c>
       <c r="J691" t="n">
-        <v>2520936.14</v>
+        <v>33205062.4</v>
       </c>
     </row>
     <row r="692">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -28112,17 +28112,17 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
+          <t>Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00)</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>3287560.73</v>
+        <v>4005503.13</v>
       </c>
       <c r="F692" t="n">
         <v>0</v>
       </c>
       <c r="G692" t="n">
-        <v>3287560.73</v>
+        <v>4005503.13</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -28131,13 +28131,13 @@
         <v>0</v>
       </c>
       <c r="J692" t="n">
-        <v>3287560.73</v>
+        <v>4005503.13</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -28147,22 +28147,22 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
+          <t>Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00)</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>31813334.15</v>
+        <v>2520936.14</v>
       </c>
       <c r="F693" t="n">
         <v>0</v>
       </c>
       <c r="G693" t="n">
-        <v>31813334.15</v>
+        <v>2520936.14</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -28171,38 +28171,38 @@
         <v>0</v>
       </c>
       <c r="J693" t="n">
-        <v>31813334.15</v>
+        <v>2520936.14</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
+          <t>Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>4506718.06</v>
+        <v>3287560.73</v>
       </c>
       <c r="F694" t="n">
         <v>0</v>
       </c>
       <c r="G694" t="n">
-        <v>4506718.06</v>
+        <v>3287560.73</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -28211,13 +28211,13 @@
         <v>0</v>
       </c>
       <c r="J694" t="n">
-        <v>4506718.06</v>
+        <v>3287560.73</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -28232,17 +28232,17 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>36950516.6</v>
+        <v>31813334.15</v>
       </c>
       <c r="F695" t="n">
         <v>0</v>
       </c>
       <c r="G695" t="n">
-        <v>36950516.6</v>
+        <v>31813334.15</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -28251,13 +28251,13 @@
         <v>0</v>
       </c>
       <c r="J695" t="n">
-        <v>36950516.6</v>
+        <v>31813334.15</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -28267,22 +28267,22 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>37600000</v>
+        <v>4506718.06</v>
       </c>
       <c r="F696" t="n">
         <v>0</v>
       </c>
       <c r="G696" t="n">
-        <v>37600000</v>
+        <v>4506718.06</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -28291,38 +28291,38 @@
         <v>0</v>
       </c>
       <c r="J696" t="n">
-        <v>37600000</v>
+        <v>4506718.06</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>1099724.43</v>
+        <v>36950516.6</v>
       </c>
       <c r="F697" t="n">
         <v>0</v>
       </c>
       <c r="G697" t="n">
-        <v>1099724.43</v>
+        <v>36950516.6</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -28331,13 +28331,13 @@
         <v>0</v>
       </c>
       <c r="J697" t="n">
-        <v>1099724.43</v>
+        <v>36950516.6</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -28347,22 +28347,22 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>47349998.43</v>
+        <v>37600000</v>
       </c>
       <c r="F698" t="n">
         <v>0</v>
       </c>
       <c r="G698" t="n">
-        <v>47349998.43</v>
+        <v>37600000</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -28371,18 +28371,18 @@
         <v>0</v>
       </c>
       <c r="J698" t="n">
-        <v>47349998.43</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -28392,17 +28392,17 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>31699998.96</v>
+        <v>1099724.43</v>
       </c>
       <c r="F699" t="n">
         <v>0</v>
       </c>
       <c r="G699" t="n">
-        <v>31699998.96</v>
+        <v>1099724.43</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -28411,13 +28411,13 @@
         <v>0</v>
       </c>
       <c r="J699" t="n">
-        <v>31699998.96</v>
+        <v>1099724.43</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -28432,17 +28432,17 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
       <c r="F700" t="n">
         <v>0</v>
       </c>
       <c r="G700" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -28451,13 +28451,13 @@
         <v>0</v>
       </c>
       <c r="J700" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -28472,17 +28472,17 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>23434999.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
       </c>
       <c r="G701" t="n">
-        <v>23434999.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -28491,13 +28491,13 @@
         <v>0</v>
       </c>
       <c r="J701" t="n">
-        <v>23434999.8</v>
+        <v>31699998.96</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -28512,17 +28512,17 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
       <c r="F702" t="n">
         <v>0</v>
       </c>
       <c r="G702" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -28531,13 +28531,13 @@
         <v>0</v>
       </c>
       <c r="J702" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -28547,22 +28547,22 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>0</v>
+        <v>23434999.8</v>
       </c>
       <c r="F703" t="n">
         <v>0</v>
       </c>
       <c r="G703" t="n">
-        <v>0</v>
+        <v>23434999.8</v>
       </c>
       <c r="H703" t="n">
         <v>0</v>
@@ -28571,13 +28571,13 @@
         <v>0</v>
       </c>
       <c r="J703" t="n">
-        <v>0</v>
+        <v>23434999.8</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -28587,22 +28587,22 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>14264750.82</v>
+        <v>32097999.96</v>
       </c>
       <c r="F704" t="n">
         <v>0</v>
       </c>
       <c r="G704" t="n">
-        <v>14264750.82</v>
+        <v>32097999.96</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -28611,13 +28611,13 @@
         <v>0</v>
       </c>
       <c r="J704" t="n">
-        <v>14264750.82</v>
+        <v>32097999.96</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -28627,37 +28627,37 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>32998445.8</v>
+        <v>0</v>
       </c>
       <c r="F705" t="n">
         <v>0</v>
       </c>
       <c r="G705" t="n">
-        <v>32998445.8</v>
+        <v>0</v>
       </c>
       <c r="H705" t="n">
-        <v>604883.63</v>
+        <v>0</v>
       </c>
       <c r="I705" t="n">
-        <v>62432.08</v>
+        <v>0</v>
       </c>
       <c r="J705" t="n">
-        <v>32393562.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -28667,22 +28667,22 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>45188997.86</v>
+        <v>14264750.82</v>
       </c>
       <c r="F706" t="n">
         <v>0</v>
       </c>
       <c r="G706" t="n">
-        <v>45188997.86</v>
+        <v>14264750.82</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -28691,13 +28691,13 @@
         <v>0</v>
       </c>
       <c r="J706" t="n">
-        <v>45188997.86</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -28707,37 +28707,37 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>77898894.3</v>
+        <v>32998445.8</v>
       </c>
       <c r="F707" t="n">
         <v>0</v>
       </c>
       <c r="G707" t="n">
-        <v>77898894.3</v>
+        <v>32998445.8</v>
       </c>
       <c r="H707" t="n">
-        <v>0</v>
+        <v>604883.63</v>
       </c>
       <c r="I707" t="n">
-        <v>0</v>
+        <v>62432.08</v>
       </c>
       <c r="J707" t="n">
-        <v>77898894.3</v>
+        <v>32393562.17</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -28747,22 +28747,22 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>24832463.21</v>
+        <v>36033198.22</v>
       </c>
       <c r="F708" t="n">
         <v>0</v>
       </c>
       <c r="G708" t="n">
-        <v>24832463.21</v>
+        <v>36033198.22</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -28771,13 +28771,13 @@
         <v>0</v>
       </c>
       <c r="J708" t="n">
-        <v>24832463.21</v>
+        <v>36033198.22</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -28787,22 +28787,22 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>34422078.35</v>
+        <v>45188997.86</v>
       </c>
       <c r="F709" t="n">
         <v>0</v>
       </c>
       <c r="G709" t="n">
-        <v>34422078.35</v>
+        <v>45188997.86</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -28811,13 +28811,13 @@
         <v>0</v>
       </c>
       <c r="J709" t="n">
-        <v>34422078.35</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -28827,22 +28827,22 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>30603197.87</v>
+        <v>77898894.3</v>
       </c>
       <c r="F710" t="n">
         <v>0</v>
       </c>
       <c r="G710" t="n">
-        <v>30603197.87</v>
+        <v>77898894.3</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -28851,51 +28851,171 @@
         <v>0</v>
       </c>
       <c r="J710" t="n">
-        <v>30603197.87</v>
+        <v>77898894.3</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="F711" t="n">
+        <v>0</v>
+      </c>
+      <c r="G711" t="n">
+        <v>24832463.21</v>
+      </c>
+      <c r="H711" t="n">
+        <v>0</v>
+      </c>
+      <c r="I711" t="n">
+        <v>0</v>
+      </c>
+      <c r="J711" t="n">
+        <v>24832463.21</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="H712" t="n">
+        <v>0</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0</v>
+      </c>
+      <c r="J712" t="n">
+        <v>34422078.35</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="H713" t="n">
+        <v>0</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0</v>
+      </c>
+      <c r="J713" t="n">
+        <v>30603197.87</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr">
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr">
+      <c r="D714" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="E711" t="n">
+      <c r="E714" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="F711" t="n">
-        <v>0</v>
-      </c>
-      <c r="G711" t="n">
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="H711" t="n">
-        <v>0</v>
-      </c>
-      <c r="I711" t="n">
-        <v>0</v>
-      </c>
-      <c r="J711" t="n">
+      <c r="H714" t="n">
+        <v>0</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J714" t="n">
         <v>31172534.58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J711"/>
+  <autoFilter ref="A1:J714"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -16645,13 +16645,13 @@
         <v>2867205</v>
       </c>
       <c r="H405" t="n">
-        <v>2586657.84</v>
+        <v>2677159.38</v>
       </c>
       <c r="I405" t="n">
-        <v>612009.77</v>
+        <v>641902.42</v>
       </c>
       <c r="J405" t="n">
-        <v>280547.16</v>
+        <v>190045.62</v>
       </c>
     </row>
     <row r="406">
@@ -17125,13 +17125,13 @@
         <v>7576922.1</v>
       </c>
       <c r="H417" t="n">
-        <v>4239229.08</v>
+        <v>4365171.24</v>
       </c>
       <c r="I417" t="n">
-        <v>423752.72</v>
+        <v>441674.27</v>
       </c>
       <c r="J417" t="n">
-        <v>3337693.02</v>
+        <v>3211750.86</v>
       </c>
     </row>
     <row r="418">
@@ -18005,13 +18005,13 @@
         <v>1413414.8</v>
       </c>
       <c r="H439" t="n">
-        <v>1051152.96</v>
+        <v>1105927.68</v>
       </c>
       <c r="I439" t="n">
-        <v>60859.04</v>
+        <v>66314.60000000001</v>
       </c>
       <c r="J439" t="n">
-        <v>362261.84</v>
+        <v>307487.12</v>
       </c>
     </row>
     <row r="440">
@@ -18485,13 +18485,13 @@
         <v>33479427.94</v>
       </c>
       <c r="H451" t="n">
-        <v>19221395.57</v>
+        <v>21822548.03</v>
       </c>
       <c r="I451" t="n">
-        <v>1019396.32</v>
+        <v>1302114.23</v>
       </c>
       <c r="J451" t="n">
-        <v>14258032.37</v>
+        <v>11656879.91</v>
       </c>
     </row>
     <row r="452">
@@ -18605,13 +18605,13 @@
         <v>33721624.27</v>
       </c>
       <c r="H454" t="n">
-        <v>17654827.84</v>
+        <v>18950254.07</v>
       </c>
       <c r="I454" t="n">
-        <v>1026710.9</v>
+        <v>1139200.92</v>
       </c>
       <c r="J454" t="n">
-        <v>16066796.43</v>
+        <v>14771370.2</v>
       </c>
     </row>
     <row r="455">
@@ -18765,13 +18765,13 @@
         <v>42788655.89</v>
       </c>
       <c r="H458" t="n">
-        <v>27461062.39</v>
+        <v>28236307.03</v>
       </c>
       <c r="I458" t="n">
-        <v>1481599.91</v>
+        <v>1562283.98</v>
       </c>
       <c r="J458" t="n">
-        <v>15327593.5</v>
+        <v>14552348.86</v>
       </c>
     </row>
     <row r="459">
@@ -19165,13 +19165,13 @@
         <v>45768946.45</v>
       </c>
       <c r="H468" t="n">
-        <v>20394072.15</v>
+        <v>21326695.49</v>
       </c>
       <c r="I468" t="n">
-        <v>967683.63</v>
+        <v>1049157.66</v>
       </c>
       <c r="J468" t="n">
-        <v>25374874.3</v>
+        <v>24442250.96</v>
       </c>
     </row>
     <row r="469">
@@ -19885,13 +19885,13 @@
         <v>95661672.93000001</v>
       </c>
       <c r="H486" t="n">
-        <v>15151232.48</v>
+        <v>19433859.66</v>
       </c>
       <c r="I486" t="n">
-        <v>646825.62</v>
+        <v>817663.8100000001</v>
       </c>
       <c r="J486" t="n">
-        <v>80510440.45</v>
+        <v>76227813.27</v>
       </c>
     </row>
     <row r="487">
@@ -20045,13 +20045,13 @@
         <v>10364111.47</v>
       </c>
       <c r="H490" t="n">
-        <v>2579642.02</v>
+        <v>2904800.14</v>
       </c>
       <c r="I490" t="n">
-        <v>713477.2</v>
+        <v>821885.87</v>
       </c>
       <c r="J490" t="n">
-        <v>7784469.45</v>
+        <v>7459311.33</v>
       </c>
     </row>
     <row r="491">
@@ -20485,13 +20485,13 @@
         <v>21429526.4</v>
       </c>
       <c r="H501" t="n">
-        <v>2750527.43</v>
+        <v>3127943.52</v>
       </c>
       <c r="I501" t="n">
         <v>0</v>
       </c>
       <c r="J501" t="n">
-        <v>18678998.97</v>
+        <v>18301582.88</v>
       </c>
     </row>
     <row r="502">
@@ -20685,13 +20685,13 @@
         <v>21860486.4</v>
       </c>
       <c r="H506" t="n">
-        <v>3570546.1</v>
+        <v>4299228.98</v>
       </c>
       <c r="I506" t="n">
-        <v>46489.96</v>
+        <v>69734.94</v>
       </c>
       <c r="J506" t="n">
-        <v>18289940.3</v>
+        <v>17561257.42</v>
       </c>
     </row>
     <row r="507">
@@ -20725,13 +20725,13 @@
         <v>9410345.890000001</v>
       </c>
       <c r="H507" t="n">
-        <v>1006178.54</v>
+        <v>1228299.11</v>
       </c>
       <c r="I507" t="n">
-        <v>29316.14</v>
+        <v>37334.68</v>
       </c>
       <c r="J507" t="n">
-        <v>8404167.35</v>
+        <v>8182046.78</v>
       </c>
     </row>
     <row r="508">
@@ -23245,13 +23245,13 @@
         <v>33826877.05</v>
       </c>
       <c r="H570" t="n">
-        <v>29210734.29</v>
+        <v>29468214.18</v>
       </c>
       <c r="I570" t="n">
-        <v>1346526.87</v>
+        <v>1364900.9</v>
       </c>
       <c r="J570" t="n">
-        <v>4616142.76</v>
+        <v>4358662.87</v>
       </c>
     </row>
     <row r="571">
@@ -23285,13 +23285,13 @@
         <v>75282924.23</v>
       </c>
       <c r="H571" t="n">
-        <v>50964371.23</v>
+        <v>53680846</v>
       </c>
       <c r="I571" t="n">
-        <v>2994474.72</v>
+        <v>3211937.05</v>
       </c>
       <c r="J571" t="n">
-        <v>24318553</v>
+        <v>21602078.23</v>
       </c>
     </row>
     <row r="572">
@@ -24285,13 +24285,13 @@
         <v>47005570.55</v>
       </c>
       <c r="H596" t="n">
-        <v>23528643.71</v>
+        <v>24832214.04</v>
       </c>
       <c r="I596" t="n">
-        <v>1104146.56</v>
+        <v>1179693.19</v>
       </c>
       <c r="J596" t="n">
-        <v>23476926.84</v>
+        <v>22173356.51</v>
       </c>
     </row>
     <row r="597">
@@ -24685,13 +24685,13 @@
         <v>61821473.21</v>
       </c>
       <c r="H606" t="n">
-        <v>46257291.3</v>
+        <v>46331106.15</v>
       </c>
       <c r="I606" t="n">
-        <v>1387864.19</v>
+        <v>1389985.11</v>
       </c>
       <c r="J606" t="n">
-        <v>15564181.91</v>
+        <v>15490367.06</v>
       </c>
     </row>
     <row r="607">
@@ -25325,13 +25325,13 @@
         <v>39334571.99</v>
       </c>
       <c r="H622" t="n">
-        <v>10734557.59</v>
+        <v>17178308.35</v>
       </c>
       <c r="I622" t="n">
-        <v>315285.64</v>
+        <v>492175.03</v>
       </c>
       <c r="J622" t="n">
-        <v>28600014.4</v>
+        <v>22156263.64</v>
       </c>
     </row>
     <row r="623">
@@ -25365,13 +25365,13 @@
         <v>2246097.6</v>
       </c>
       <c r="H623" t="n">
-        <v>164119.62</v>
+        <v>171424.7</v>
       </c>
       <c r="I623" t="n">
-        <v>6728.85</v>
+        <v>7270.88</v>
       </c>
       <c r="J623" t="n">
-        <v>2081977.98</v>
+        <v>2074672.9</v>
       </c>
     </row>
     <row r="624">
@@ -25525,13 +25525,13 @@
         <v>5774752.44</v>
       </c>
       <c r="H627" t="n">
-        <v>1912436.46</v>
+        <v>2080303.32</v>
       </c>
       <c r="I627" t="n">
-        <v>77533.00999999999</v>
+        <v>88175.75999999999</v>
       </c>
       <c r="J627" t="n">
-        <v>3862315.98</v>
+        <v>3694449.12</v>
       </c>
     </row>
     <row r="628">
@@ -25565,13 +25565,13 @@
         <v>8415499.810000001</v>
       </c>
       <c r="H628" t="n">
-        <v>2984135.57</v>
+        <v>3668445.77</v>
       </c>
       <c r="I628" t="n">
-        <v>105011.73</v>
+        <v>133016.83</v>
       </c>
       <c r="J628" t="n">
-        <v>5431364.24</v>
+        <v>4747054.04</v>
       </c>
     </row>
     <row r="629">
@@ -25605,13 +25605,13 @@
         <v>4776981.58</v>
       </c>
       <c r="H629" t="n">
-        <v>3155692.55</v>
+        <v>3811147.4</v>
       </c>
       <c r="I629" t="n">
-        <v>101679.28</v>
+        <v>125510.2</v>
       </c>
       <c r="J629" t="n">
-        <v>1621289.03</v>
+        <v>965834.1800000001</v>
       </c>
     </row>
     <row r="630">
@@ -25805,13 +25805,13 @@
         <v>13934048.38</v>
       </c>
       <c r="H634" t="n">
-        <v>4685070</v>
+        <v>5255390.3</v>
       </c>
       <c r="I634" t="n">
-        <v>1294868.36</v>
+        <v>1484860.68</v>
       </c>
       <c r="J634" t="n">
-        <v>9248978.380000001</v>
+        <v>8678658.08</v>
       </c>
     </row>
     <row r="635">
@@ -25845,13 +25845,13 @@
         <v>9104897.41</v>
       </c>
       <c r="H635" t="n">
-        <v>2625143.15</v>
+        <v>2984078.68</v>
       </c>
       <c r="I635" t="n">
-        <v>726351.11</v>
+        <v>846058.74</v>
       </c>
       <c r="J635" t="n">
-        <v>6479754.26</v>
+        <v>6120818.73</v>
       </c>
     </row>
     <row r="636">
@@ -25885,13 +25885,13 @@
         <v>15276741.09</v>
       </c>
       <c r="H636" t="n">
-        <v>4187262.13</v>
+        <v>4700012.81</v>
       </c>
       <c r="I636" t="n">
-        <v>1157069.81</v>
+        <v>1327844.46</v>
       </c>
       <c r="J636" t="n">
-        <v>11089478.96</v>
+        <v>10576728.28</v>
       </c>
     </row>
     <row r="637">
@@ -26325,13 +26325,13 @@
         <v>53573999.99</v>
       </c>
       <c r="H647" t="n">
-        <v>6093202.3</v>
+        <v>7700082.26</v>
       </c>
       <c r="I647" t="n">
-        <v>63545.71</v>
+        <v>95028.74000000001</v>
       </c>
       <c r="J647" t="n">
-        <v>47480797.69</v>
+        <v>45873917.73</v>
       </c>
     </row>
     <row r="648">
@@ -26365,13 +26365,13 @@
         <v>1655673.22</v>
       </c>
       <c r="H648" t="n">
-        <v>375709.28</v>
+        <v>485335.3</v>
       </c>
       <c r="I648" t="n">
-        <v>8141.11</v>
+        <v>12098.6</v>
       </c>
       <c r="J648" t="n">
-        <v>1279963.94</v>
+        <v>1170337.92</v>
       </c>
     </row>
     <row r="649">
@@ -26405,13 +26405,13 @@
         <v>9284408.859999999</v>
       </c>
       <c r="H649" t="n">
-        <v>1544810.85</v>
+        <v>1879558.63</v>
       </c>
       <c r="I649" t="n">
-        <v>41876.47</v>
+        <v>53960.85</v>
       </c>
       <c r="J649" t="n">
-        <v>7739598.01</v>
+        <v>7404850.23</v>
       </c>
     </row>
     <row r="650">
@@ -26485,13 +26485,13 @@
         <v>64984305.34</v>
       </c>
       <c r="H651" t="n">
-        <v>2647093.02</v>
+        <v>4375479.93</v>
       </c>
       <c r="I651" t="n">
-        <v>76958.82000000001</v>
+        <v>117451.13</v>
       </c>
       <c r="J651" t="n">
-        <v>62337212.32</v>
+        <v>60608825.41</v>
       </c>
     </row>
     <row r="652">
@@ -26565,13 +26565,13 @@
         <v>12403029.87</v>
       </c>
       <c r="H653" t="n">
-        <v>1614142.18</v>
+        <v>2671611.78</v>
       </c>
       <c r="I653" t="n">
-        <v>134082.77</v>
+        <v>207169.47</v>
       </c>
       <c r="J653" t="n">
-        <v>10788887.69</v>
+        <v>9731418.09</v>
       </c>
     </row>
     <row r="654">
@@ -26645,13 +26645,13 @@
         <v>22167830.47</v>
       </c>
       <c r="H655" t="n">
-        <v>2304211.64</v>
+        <v>3149597.47</v>
       </c>
       <c r="I655" t="n">
-        <v>491722.4</v>
+        <v>672167.05</v>
       </c>
       <c r="J655" t="n">
-        <v>19863618.83</v>
+        <v>19018233</v>
       </c>
     </row>
     <row r="656">
@@ -26685,13 +26685,13 @@
         <v>12585961.98</v>
       </c>
       <c r="H656" t="n">
-        <v>1511276.19</v>
+        <v>2076298.69</v>
       </c>
       <c r="I656" t="n">
-        <v>138325.23</v>
+        <v>192219.5</v>
       </c>
       <c r="J656" t="n">
-        <v>11074685.79</v>
+        <v>10509663.29</v>
       </c>
     </row>
     <row r="657">
@@ -27125,13 +27125,13 @@
         <v>41984578.11</v>
       </c>
       <c r="H667" t="n">
-        <v>3794113.75</v>
+        <v>15624439.46</v>
       </c>
       <c r="I667" t="n">
         <v>0</v>
       </c>
       <c r="J667" t="n">
-        <v>38190464.36</v>
+        <v>26360138.65</v>
       </c>
     </row>
     <row r="668">
@@ -27325,13 +27325,13 @@
         <v>59889999.58</v>
       </c>
       <c r="H672" t="n">
-        <v>897085.83</v>
+        <v>1361505.52</v>
       </c>
       <c r="I672" t="n">
-        <v>47341.54</v>
+        <v>60143.35</v>
       </c>
       <c r="J672" t="n">
-        <v>58992913.75</v>
+        <v>58528494.06</v>
       </c>
     </row>
     <row r="673">
@@ -27485,13 +27485,13 @@
         <v>13190992.89</v>
       </c>
       <c r="H676" t="n">
-        <v>1124617.17</v>
+        <v>2020033.16</v>
       </c>
       <c r="I676" t="n">
-        <v>126675.2</v>
+        <v>254120.31</v>
       </c>
       <c r="J676" t="n">
-        <v>12066375.72</v>
+        <v>11170959.73</v>
       </c>
     </row>
     <row r="677">
@@ -27525,13 +27525,13 @@
         <v>14398046.07</v>
       </c>
       <c r="H677" t="n">
-        <v>647838.1</v>
+        <v>1555371.56</v>
       </c>
       <c r="I677" t="n">
-        <v>75894.34</v>
+        <v>190823.62</v>
       </c>
       <c r="J677" t="n">
-        <v>13750207.97</v>
+        <v>12842674.51</v>
       </c>
     </row>
     <row r="678">
@@ -28965,13 +28965,13 @@
         <v>30603197.87</v>
       </c>
       <c r="H713" t="n">
-        <v>0</v>
+        <v>1284027.29</v>
       </c>
       <c r="I713" t="n">
-        <v>0</v>
+        <v>108112.79</v>
       </c>
       <c r="J713" t="n">
-        <v>30603197.87</v>
+        <v>29319170.58</v>
       </c>
     </row>
     <row r="714">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -9285,13 +9285,13 @@
         <v>32501203.78</v>
       </c>
       <c r="H221" t="n">
-        <v>28835459.69</v>
+        <v>29542276.22</v>
       </c>
       <c r="I221" t="n">
-        <v>5158403.67</v>
+        <v>5286993.24</v>
       </c>
       <c r="J221" t="n">
-        <v>3665744.09</v>
+        <v>2958927.56</v>
       </c>
     </row>
     <row r="222">
@@ -11165,13 +11165,13 @@
         <v>24865514.03</v>
       </c>
       <c r="H268" t="n">
-        <v>20353151.07</v>
+        <v>20427521.85</v>
       </c>
       <c r="I268" t="n">
-        <v>2062875.33</v>
+        <v>2074335.86</v>
       </c>
       <c r="J268" t="n">
-        <v>4512362.96</v>
+        <v>4437992.18</v>
       </c>
     </row>
     <row r="269">
@@ -15365,13 +15365,13 @@
         <v>36255903.57</v>
       </c>
       <c r="H373" t="n">
-        <v>29941304.59</v>
+        <v>30099564.8</v>
       </c>
       <c r="I373" t="n">
-        <v>1567645.61</v>
+        <v>1590840.45</v>
       </c>
       <c r="J373" t="n">
-        <v>6314598.98</v>
+        <v>6156338.77</v>
       </c>
     </row>
     <row r="374">
@@ -15405,13 +15405,13 @@
         <v>34335611.48</v>
       </c>
       <c r="H374" t="n">
-        <v>1770020.06</v>
+        <v>3323873.3</v>
       </c>
       <c r="I374" t="n">
-        <v>64501.74</v>
+        <v>180663.59</v>
       </c>
       <c r="J374" t="n">
-        <v>32565591.42</v>
+        <v>31011738.18</v>
       </c>
     </row>
     <row r="375">
@@ -16845,13 +16845,13 @@
         <v>2600522.52</v>
       </c>
       <c r="H410" t="n">
-        <v>1603853.4</v>
+        <v>1635689.86</v>
       </c>
       <c r="I410" t="n">
-        <v>190003.52</v>
+        <v>194909.51</v>
       </c>
       <c r="J410" t="n">
-        <v>996669.12</v>
+        <v>964832.66</v>
       </c>
     </row>
     <row r="411">
@@ -17845,13 +17845,13 @@
         <v>1259081.21</v>
       </c>
       <c r="H435" t="n">
-        <v>459255.79</v>
+        <v>478612.49</v>
       </c>
       <c r="I435" t="n">
-        <v>57694.97</v>
+        <v>60677.83</v>
       </c>
       <c r="J435" t="n">
-        <v>799825.42</v>
+        <v>780468.72</v>
       </c>
     </row>
     <row r="436">
@@ -18125,13 +18125,13 @@
         <v>1394910.17</v>
       </c>
       <c r="H442" t="n">
-        <v>332644.45</v>
+        <v>371349.63</v>
       </c>
       <c r="I442" t="n">
-        <v>41896.01</v>
+        <v>47860.47</v>
       </c>
       <c r="J442" t="n">
-        <v>1062265.72</v>
+        <v>1023560.54</v>
       </c>
     </row>
     <row r="443">
@@ -18405,13 +18405,13 @@
         <v>29715772.52</v>
       </c>
       <c r="H449" t="n">
-        <v>23439872.67</v>
+        <v>24431837.74</v>
       </c>
       <c r="I449" t="n">
-        <v>1224383.25</v>
+        <v>1332520.78</v>
       </c>
       <c r="J449" t="n">
-        <v>6275899.85</v>
+        <v>5283934.78</v>
       </c>
     </row>
     <row r="450">
@@ -18645,13 +18645,13 @@
         <v>32023158.45</v>
       </c>
       <c r="H455" t="n">
-        <v>27938707.57</v>
+        <v>29811640.98</v>
       </c>
       <c r="I455" t="n">
-        <v>1300896.83</v>
+        <v>1478242.43</v>
       </c>
       <c r="J455" t="n">
-        <v>4084450.88</v>
+        <v>2211517.47</v>
       </c>
     </row>
     <row r="456">
@@ -18805,13 +18805,13 @@
         <v>34984519.25</v>
       </c>
       <c r="H459" t="n">
-        <v>30596587.45</v>
+        <v>32487325.6</v>
       </c>
       <c r="I459" t="n">
-        <v>1638048.83</v>
+        <v>1803563.04</v>
       </c>
       <c r="J459" t="n">
-        <v>4387931.8</v>
+        <v>2497193.65</v>
       </c>
     </row>
     <row r="460">
@@ -18845,13 +18845,13 @@
         <v>3345699.13</v>
       </c>
       <c r="H460" t="n">
-        <v>2386069.14</v>
+        <v>2485734.75</v>
       </c>
       <c r="I460" t="n">
-        <v>196495.13</v>
+        <v>209371.92</v>
       </c>
       <c r="J460" t="n">
-        <v>959629.99</v>
+        <v>859964.38</v>
       </c>
     </row>
     <row r="461">
@@ -18925,13 +18925,13 @@
         <v>50256753.54</v>
       </c>
       <c r="H462" t="n">
-        <v>41981889.57</v>
+        <v>42740546.57</v>
       </c>
       <c r="I462" t="n">
-        <v>1522076.2</v>
+        <v>1576940.53</v>
       </c>
       <c r="J462" t="n">
-        <v>8274863.97</v>
+        <v>7516206.97</v>
       </c>
     </row>
     <row r="463">
@@ -19045,13 +19045,13 @@
         <v>47634588.04</v>
       </c>
       <c r="H465" t="n">
-        <v>26881215.87</v>
+        <v>31846402.08</v>
       </c>
       <c r="I465" t="n">
-        <v>1223574.14</v>
+        <v>1523518.61</v>
       </c>
       <c r="J465" t="n">
-        <v>20753372.17</v>
+        <v>15788185.96</v>
       </c>
     </row>
     <row r="466">
@@ -19205,13 +19205,13 @@
         <v>48158605.21</v>
       </c>
       <c r="H469" t="n">
-        <v>29856106.57</v>
+        <v>30474934.34</v>
       </c>
       <c r="I469" t="n">
-        <v>1357169.26</v>
+        <v>1407677.98</v>
       </c>
       <c r="J469" t="n">
-        <v>18302498.64</v>
+        <v>17683670.87</v>
       </c>
     </row>
     <row r="470">
@@ -19245,13 +19245,13 @@
         <v>859769.01</v>
       </c>
       <c r="H470" t="n">
-        <v>688450.6899999999</v>
+        <v>694073.51</v>
       </c>
       <c r="I470" t="n">
-        <v>26141.96</v>
+        <v>26559.17</v>
       </c>
       <c r="J470" t="n">
-        <v>171318.32</v>
+        <v>165695.5</v>
       </c>
     </row>
     <row r="471">
@@ -19399,19 +19399,19 @@
         <v>24309955.5</v>
       </c>
       <c r="F474" t="n">
-        <v>0</v>
+        <v>97125</v>
       </c>
       <c r="G474" t="n">
-        <v>24309955.5</v>
+        <v>24407080.5</v>
       </c>
       <c r="H474" t="n">
-        <v>15133680.75</v>
+        <v>16100052.36</v>
       </c>
       <c r="I474" t="n">
-        <v>170125.57</v>
+        <v>220109.24</v>
       </c>
       <c r="J474" t="n">
-        <v>9176274.75</v>
+        <v>8307028.14</v>
       </c>
     </row>
     <row r="475">
@@ -19605,13 +19605,13 @@
         <v>8742912.960000001</v>
       </c>
       <c r="H479" t="n">
-        <v>0</v>
+        <v>365496.06</v>
       </c>
       <c r="I479" t="n">
-        <v>0</v>
+        <v>21299.64</v>
       </c>
       <c r="J479" t="n">
-        <v>8742912.960000001</v>
+        <v>8377416.9</v>
       </c>
     </row>
     <row r="480">
@@ -19685,13 +19685,13 @@
         <v>924684.42</v>
       </c>
       <c r="H481" t="n">
-        <v>664376.46</v>
+        <v>674271.65</v>
       </c>
       <c r="I481" t="n">
-        <v>29892.55</v>
+        <v>30626.77</v>
       </c>
       <c r="J481" t="n">
-        <v>260307.96</v>
+        <v>250412.77</v>
       </c>
     </row>
     <row r="482">
@@ -19765,13 +19765,13 @@
         <v>52239647.93</v>
       </c>
       <c r="H483" t="n">
-        <v>17027419.71</v>
+        <v>30269209.55</v>
       </c>
       <c r="I483" t="n">
-        <v>515574.38</v>
+        <v>919112.24</v>
       </c>
       <c r="J483" t="n">
-        <v>35212228.22</v>
+        <v>21970438.38</v>
       </c>
     </row>
     <row r="484">
@@ -19805,13 +19805,13 @@
         <v>28955069.4</v>
       </c>
       <c r="H484" t="n">
-        <v>14841369.03</v>
+        <v>15678020.81</v>
       </c>
       <c r="I484" t="n">
-        <v>351155.7</v>
+        <v>371802.99</v>
       </c>
       <c r="J484" t="n">
-        <v>14113700.37</v>
+        <v>13277048.59</v>
       </c>
     </row>
     <row r="485">
@@ -20125,13 +20125,13 @@
         <v>9147934.25</v>
       </c>
       <c r="H492" t="n">
-        <v>1867887.53</v>
+        <v>2217399.59</v>
       </c>
       <c r="I492" t="n">
-        <v>45682.96</v>
+        <v>58300.33</v>
       </c>
       <c r="J492" t="n">
-        <v>7280046.72</v>
+        <v>6930534.66</v>
       </c>
     </row>
     <row r="493">
@@ -20285,13 +20285,13 @@
         <v>5978999.99</v>
       </c>
       <c r="H496" t="n">
-        <v>3278560.72</v>
+        <v>4021883.98</v>
       </c>
       <c r="I496" t="n">
-        <v>1944.54</v>
+        <v>2366.45</v>
       </c>
       <c r="J496" t="n">
-        <v>2700439.27</v>
+        <v>1957116.01</v>
       </c>
     </row>
     <row r="497">
@@ -20405,13 +20405,13 @@
         <v>45918998.95</v>
       </c>
       <c r="H499" t="n">
-        <v>2216386.72</v>
+        <v>3889704.5</v>
       </c>
       <c r="I499" t="n">
-        <v>42264.81</v>
+        <v>80510.37</v>
       </c>
       <c r="J499" t="n">
-        <v>43702612.23</v>
+        <v>42029294.45</v>
       </c>
     </row>
     <row r="500">
@@ -20525,13 +20525,13 @@
         <v>5903947.49</v>
       </c>
       <c r="H502" t="n">
-        <v>344480.73</v>
+        <v>377721.68</v>
       </c>
       <c r="I502" t="n">
-        <v>9274.190000000001</v>
+        <v>10474.18</v>
       </c>
       <c r="J502" t="n">
-        <v>5559466.76</v>
+        <v>5526225.81</v>
       </c>
     </row>
     <row r="503">
@@ -20565,13 +20565,13 @@
         <v>1152374.25</v>
       </c>
       <c r="H503" t="n">
-        <v>130152.94</v>
+        <v>152236.05</v>
       </c>
       <c r="I503" t="n">
-        <v>3781.96</v>
+        <v>4579.16</v>
       </c>
       <c r="J503" t="n">
-        <v>1022221.31</v>
+        <v>1000138.2</v>
       </c>
     </row>
     <row r="504">
@@ -20645,13 +20645,13 @@
         <v>14619000</v>
       </c>
       <c r="H505" t="n">
-        <v>4429527.64</v>
+        <v>7635030.52</v>
       </c>
       <c r="I505" t="n">
-        <v>20772.43</v>
+        <v>29661.44</v>
       </c>
       <c r="J505" t="n">
-        <v>10189472.36</v>
+        <v>6983969.48</v>
       </c>
     </row>
     <row r="506">
@@ -20765,13 +20765,13 @@
         <v>9200787.869999999</v>
       </c>
       <c r="H508" t="n">
-        <v>1400596.05</v>
+        <v>1671073.29</v>
       </c>
       <c r="I508" t="n">
-        <v>41123.86</v>
+        <v>50888.07</v>
       </c>
       <c r="J508" t="n">
-        <v>7800191.82</v>
+        <v>7529714.58</v>
       </c>
     </row>
     <row r="509">
@@ -20845,13 +20845,13 @@
         <v>2086583.52</v>
       </c>
       <c r="H510" t="n">
-        <v>152799.08</v>
+        <v>172556.71</v>
       </c>
       <c r="I510" t="n">
-        <v>9641.6</v>
+        <v>10888.3</v>
       </c>
       <c r="J510" t="n">
-        <v>1933784.44</v>
+        <v>1914026.81</v>
       </c>
     </row>
     <row r="511">
@@ -21085,13 +21085,13 @@
         <v>634467.04</v>
       </c>
       <c r="H516" t="n">
-        <v>157025.26</v>
+        <v>161485.84</v>
       </c>
       <c r="I516" t="n">
-        <v>16474.54</v>
+        <v>17161.91</v>
       </c>
       <c r="J516" t="n">
-        <v>477441.78</v>
+        <v>472981.2</v>
       </c>
     </row>
     <row r="517">
@@ -21285,13 +21285,13 @@
         <v>410983.4</v>
       </c>
       <c r="H521" t="n">
-        <v>106722.12</v>
+        <v>111989.41</v>
       </c>
       <c r="I521" t="n">
-        <v>10749.95</v>
+        <v>11561.63</v>
       </c>
       <c r="J521" t="n">
-        <v>304261.28</v>
+        <v>298993.99</v>
       </c>
     </row>
     <row r="522">
@@ -21405,13 +21405,13 @@
         <v>1792375.62</v>
       </c>
       <c r="H524" t="n">
-        <v>629697.1800000001</v>
+        <v>636725.02</v>
       </c>
       <c r="I524" t="n">
-        <v>78117.96000000001</v>
+        <v>79200.95</v>
       </c>
       <c r="J524" t="n">
-        <v>1162678.44</v>
+        <v>1155650.6</v>
       </c>
     </row>
     <row r="525">
@@ -21485,13 +21485,13 @@
         <v>3721286.23</v>
       </c>
       <c r="H526" t="n">
-        <v>1776371.55</v>
+        <v>1779576.31</v>
       </c>
       <c r="I526" t="n">
-        <v>203242.28</v>
+        <v>203736.13</v>
       </c>
       <c r="J526" t="n">
-        <v>1944914.68</v>
+        <v>1941709.92</v>
       </c>
     </row>
     <row r="527">
@@ -21525,13 +21525,13 @@
         <v>2451612.34</v>
       </c>
       <c r="H527" t="n">
-        <v>1748367.35</v>
+        <v>1826197.75</v>
       </c>
       <c r="I527" t="n">
-        <v>223424.76</v>
+        <v>235418.42</v>
       </c>
       <c r="J527" t="n">
-        <v>703244.99</v>
+        <v>625414.59</v>
       </c>
     </row>
     <row r="528">
@@ -21605,13 +21605,13 @@
         <v>1584639.21</v>
       </c>
       <c r="H529" t="n">
-        <v>1036278.58</v>
+        <v>1042554.68</v>
       </c>
       <c r="I529" t="n">
-        <v>135149.95</v>
+        <v>136117.09</v>
       </c>
       <c r="J529" t="n">
-        <v>548360.63</v>
+        <v>542084.53</v>
       </c>
     </row>
     <row r="530">
@@ -21725,13 +21725,13 @@
         <v>2363126.32</v>
       </c>
       <c r="H532" t="n">
-        <v>795161.12</v>
+        <v>812459.77</v>
       </c>
       <c r="I532" t="n">
-        <v>76478.42</v>
+        <v>79144.14</v>
       </c>
       <c r="J532" t="n">
-        <v>1567965.2</v>
+        <v>1550666.55</v>
       </c>
     </row>
     <row r="533">
@@ -21885,13 +21885,13 @@
         <v>891896.45</v>
       </c>
       <c r="H536" t="n">
-        <v>542488.23</v>
+        <v>547052.05</v>
       </c>
       <c r="I536" t="n">
-        <v>62663.71</v>
+        <v>63366.99</v>
       </c>
       <c r="J536" t="n">
-        <v>349408.22</v>
+        <v>344844.4</v>
       </c>
     </row>
     <row r="537">
@@ -24165,13 +24165,13 @@
         <v>37310856.76</v>
       </c>
       <c r="H593" t="n">
-        <v>30828416.26</v>
+        <v>33571627.42</v>
       </c>
       <c r="I593" t="n">
-        <v>1645889.91</v>
+        <v>1885811.92</v>
       </c>
       <c r="J593" t="n">
-        <v>6482440.5</v>
+        <v>3739229.34</v>
       </c>
     </row>
     <row r="594">
@@ -24325,13 +24325,13 @@
         <v>51333755.33</v>
       </c>
       <c r="H597" t="n">
-        <v>23304932.85</v>
+        <v>25738126.27</v>
       </c>
       <c r="I597" t="n">
-        <v>1252057.26</v>
+        <v>1396822.53</v>
       </c>
       <c r="J597" t="n">
-        <v>28028822.48</v>
+        <v>25595629.06</v>
       </c>
     </row>
     <row r="598">
@@ -24405,13 +24405,13 @@
         <v>49131721.25</v>
       </c>
       <c r="H599" t="n">
-        <v>25075761.49</v>
+        <v>27091255.57</v>
       </c>
       <c r="I599" t="n">
-        <v>984837.09</v>
+        <v>1108710.91</v>
       </c>
       <c r="J599" t="n">
-        <v>24055959.76</v>
+        <v>22040465.68</v>
       </c>
     </row>
     <row r="600">
@@ -24485,13 +24485,13 @@
         <v>47758833.23</v>
       </c>
       <c r="H601" t="n">
-        <v>29365376.04</v>
+        <v>30685601.38</v>
       </c>
       <c r="I601" t="n">
-        <v>1263434.93</v>
+        <v>1357081.56</v>
       </c>
       <c r="J601" t="n">
-        <v>18393457.19</v>
+        <v>17073231.85</v>
       </c>
     </row>
     <row r="602">
@@ -24605,13 +24605,13 @@
         <v>1484780.82</v>
       </c>
       <c r="H604" t="n">
-        <v>923251.2</v>
+        <v>955292.0699999999</v>
       </c>
       <c r="I604" t="n">
-        <v>38869.51</v>
+        <v>41246.94</v>
       </c>
       <c r="J604" t="n">
-        <v>561529.62</v>
+        <v>529488.75</v>
       </c>
     </row>
     <row r="605">
@@ -24685,13 +24685,13 @@
         <v>61821473.21</v>
       </c>
       <c r="H606" t="n">
-        <v>46331106.15</v>
+        <v>46516423.88</v>
       </c>
       <c r="I606" t="n">
-        <v>1389985.11</v>
+        <v>1395457.53</v>
       </c>
       <c r="J606" t="n">
-        <v>15490367.06</v>
+        <v>15305049.33</v>
       </c>
     </row>
     <row r="607">
@@ -25205,13 +25205,13 @@
         <v>4917800.43</v>
       </c>
       <c r="H619" t="n">
-        <v>208430.57</v>
+        <v>966914.63</v>
       </c>
       <c r="I619" t="n">
-        <v>10175.13</v>
+        <v>43684.1</v>
       </c>
       <c r="J619" t="n">
-        <v>4709369.86</v>
+        <v>3950885.8</v>
       </c>
     </row>
     <row r="620">
@@ -25445,13 +25445,13 @@
         <v>9659997.08</v>
       </c>
       <c r="H625" t="n">
-        <v>206968.35</v>
+        <v>264833.81</v>
       </c>
       <c r="I625" t="n">
-        <v>19144.55</v>
+        <v>24497.1</v>
       </c>
       <c r="J625" t="n">
-        <v>9453028.73</v>
+        <v>9395163.27</v>
       </c>
     </row>
     <row r="626">
@@ -25765,13 +25765,13 @@
         <v>803371.39</v>
       </c>
       <c r="H633" t="n">
-        <v>307553.14</v>
+        <v>352010.15</v>
       </c>
       <c r="I633" t="n">
-        <v>13149.72</v>
+        <v>15314.77</v>
       </c>
       <c r="J633" t="n">
-        <v>495818.25</v>
+        <v>451361.24</v>
       </c>
     </row>
     <row r="634">
@@ -25965,13 +25965,13 @@
         <v>49093539.45</v>
       </c>
       <c r="H638" t="n">
-        <v>5181810.35</v>
+        <v>5724611.63</v>
       </c>
       <c r="I638" t="n">
-        <v>41982.04</v>
+        <v>49661.35</v>
       </c>
       <c r="J638" t="n">
-        <v>43911729.1</v>
+        <v>43368927.82</v>
       </c>
     </row>
     <row r="639">
@@ -26085,13 +26085,13 @@
         <v>9522992.289999999</v>
       </c>
       <c r="H641" t="n">
-        <v>2955353.01</v>
+        <v>3299582.84</v>
       </c>
       <c r="I641" t="n">
-        <v>51034.6</v>
+        <v>60442.41</v>
       </c>
       <c r="J641" t="n">
-        <v>6567639.28</v>
+        <v>6223409.45</v>
       </c>
     </row>
     <row r="642">
@@ -26125,13 +26125,13 @@
         <v>51814575.44</v>
       </c>
       <c r="H642" t="n">
-        <v>6832001.61</v>
+        <v>8776447.58</v>
       </c>
       <c r="I642" t="n">
-        <v>97809.87</v>
+        <v>157370.32</v>
       </c>
       <c r="J642" t="n">
-        <v>44982573.83</v>
+        <v>43038127.86</v>
       </c>
     </row>
     <row r="643">
@@ -26165,13 +26165,13 @@
         <v>50960749.38</v>
       </c>
       <c r="H643" t="n">
-        <v>5881370.48</v>
+        <v>6563149.56</v>
       </c>
       <c r="I643" t="n">
-        <v>49202.31</v>
+        <v>60601.39</v>
       </c>
       <c r="J643" t="n">
-        <v>45079378.9</v>
+        <v>44397599.82</v>
       </c>
     </row>
     <row r="644">
@@ -26205,13 +26205,13 @@
         <v>53356791.72</v>
       </c>
       <c r="H644" t="n">
-        <v>9603132.49</v>
+        <v>11440004.49</v>
       </c>
       <c r="I644" t="n">
-        <v>146432.54</v>
+        <v>195949.38</v>
       </c>
       <c r="J644" t="n">
-        <v>43753659.23</v>
+        <v>41916787.23</v>
       </c>
     </row>
     <row r="645">
@@ -26245,13 +26245,13 @@
         <v>53241874.38</v>
       </c>
       <c r="H645" t="n">
-        <v>11593843.28</v>
+        <v>13376312.96</v>
       </c>
       <c r="I645" t="n">
-        <v>129819.98</v>
+        <v>189993.16</v>
       </c>
       <c r="J645" t="n">
-        <v>41648031.1</v>
+        <v>39865561.42</v>
       </c>
     </row>
     <row r="646">
@@ -26285,13 +26285,13 @@
         <v>59299394.97</v>
       </c>
       <c r="H646" t="n">
-        <v>24082394.71</v>
+        <v>25780749.1</v>
       </c>
       <c r="I646" t="n">
-        <v>225294.14</v>
+        <v>259048.22</v>
       </c>
       <c r="J646" t="n">
-        <v>35217000.26</v>
+        <v>33518645.87</v>
       </c>
     </row>
     <row r="647">
@@ -26445,13 +26445,13 @@
         <v>9218472.49</v>
       </c>
       <c r="H650" t="n">
-        <v>1041486.75</v>
+        <v>1253158.75</v>
       </c>
       <c r="I650" t="n">
-        <v>33055.91</v>
+        <v>40697.25</v>
       </c>
       <c r="J650" t="n">
-        <v>8176985.74</v>
+        <v>7965313.74</v>
       </c>
     </row>
     <row r="651">
@@ -26525,13 +26525,13 @@
         <v>14704896.91</v>
       </c>
       <c r="H652" t="n">
-        <v>1937021.67</v>
+        <v>3334781.36</v>
       </c>
       <c r="I652" t="n">
-        <v>213905.91</v>
+        <v>357089.45</v>
       </c>
       <c r="J652" t="n">
-        <v>12767875.24</v>
+        <v>11370115.55</v>
       </c>
     </row>
     <row r="653">
@@ -26805,13 +26805,13 @@
         <v>18749931.77</v>
       </c>
       <c r="H659" t="n">
-        <v>2951267.99</v>
+        <v>3731967.69</v>
       </c>
       <c r="I659" t="n">
         <v>626313.58</v>
       </c>
       <c r="J659" t="n">
-        <v>15798663.78</v>
+        <v>15017964.08</v>
       </c>
     </row>
     <row r="660">
@@ -26845,13 +26845,13 @@
         <v>57467603.75</v>
       </c>
       <c r="H660" t="n">
-        <v>0</v>
+        <v>1225033.21</v>
       </c>
       <c r="I660" t="n">
-        <v>0</v>
+        <v>54549.02</v>
       </c>
       <c r="J660" t="n">
-        <v>57467603.75</v>
+        <v>56242570.54</v>
       </c>
     </row>
     <row r="661">
@@ -26885,13 +26885,13 @@
         <v>14929346.95</v>
       </c>
       <c r="H661" t="n">
-        <v>833120.1899999999</v>
+        <v>1095630.47</v>
       </c>
       <c r="I661" t="n">
-        <v>178892.04</v>
+        <v>235452.45</v>
       </c>
       <c r="J661" t="n">
-        <v>14096226.76</v>
+        <v>13833716.48</v>
       </c>
     </row>
     <row r="662">
@@ -26925,13 +26925,13 @@
         <v>3028048.96</v>
       </c>
       <c r="H662" t="n">
-        <v>317502.27</v>
+        <v>484650.83</v>
       </c>
       <c r="I662" t="n">
-        <v>10128.32</v>
+        <v>15460.35</v>
       </c>
       <c r="J662" t="n">
-        <v>2710546.69</v>
+        <v>2543398.13</v>
       </c>
     </row>
     <row r="663">
@@ -27005,13 +27005,13 @@
         <v>6199729.76</v>
       </c>
       <c r="H664" t="n">
-        <v>289152.96</v>
+        <v>2369404.54</v>
       </c>
       <c r="I664" t="n">
         <v>0</v>
       </c>
       <c r="J664" t="n">
-        <v>5910576.8</v>
+        <v>3830325.22</v>
       </c>
     </row>
     <row r="665">
@@ -27205,13 +27205,13 @@
         <v>3187539.16</v>
       </c>
       <c r="H669" t="n">
-        <v>191808.12</v>
+        <v>333054.32</v>
       </c>
       <c r="I669" t="n">
-        <v>6118.67</v>
+        <v>10624.42</v>
       </c>
       <c r="J669" t="n">
-        <v>2995731.04</v>
+        <v>2854484.84</v>
       </c>
     </row>
     <row r="670">
@@ -27245,13 +27245,13 @@
         <v>4324285.68</v>
       </c>
       <c r="H670" t="n">
-        <v>170016.64</v>
+        <v>269098.43</v>
       </c>
       <c r="I670" t="n">
-        <v>5423.52</v>
+        <v>8584.219999999999</v>
       </c>
       <c r="J670" t="n">
-        <v>4154269.04</v>
+        <v>4055187.25</v>
       </c>
     </row>
     <row r="671">
@@ -27965,13 +27965,13 @@
         <v>29302939.12</v>
       </c>
       <c r="H688" t="n">
-        <v>0</v>
+        <v>430460.69</v>
       </c>
       <c r="I688" t="n">
-        <v>0</v>
+        <v>45845.08</v>
       </c>
       <c r="J688" t="n">
-        <v>29302939.12</v>
+        <v>28872478.43</v>
       </c>
     </row>
     <row r="689">
@@ -28085,13 +28085,13 @@
         <v>33205062.4</v>
       </c>
       <c r="H691" t="n">
-        <v>0</v>
+        <v>598527.91</v>
       </c>
       <c r="I691" t="n">
-        <v>0</v>
+        <v>66572.00999999999</v>
       </c>
       <c r="J691" t="n">
-        <v>33205062.4</v>
+        <v>32606534.49</v>
       </c>
     </row>
     <row r="692">
@@ -28445,13 +28445,13 @@
         <v>47349998.43</v>
       </c>
       <c r="H700" t="n">
-        <v>0</v>
+        <v>98942.17999999999</v>
       </c>
       <c r="I700" t="n">
-        <v>0</v>
+        <v>3156.24</v>
       </c>
       <c r="J700" t="n">
-        <v>47349998.43</v>
+        <v>47251056.25</v>
       </c>
     </row>
     <row r="701">
@@ -28485,13 +28485,13 @@
         <v>31699998.96</v>
       </c>
       <c r="H701" t="n">
-        <v>0</v>
+        <v>29454.44</v>
       </c>
       <c r="I701" t="n">
-        <v>0</v>
+        <v>939.59</v>
       </c>
       <c r="J701" t="n">
-        <v>31699998.96</v>
+        <v>31670544.52</v>
       </c>
     </row>
     <row r="702">
@@ -28525,13 +28525,13 @@
         <v>35989998.13</v>
       </c>
       <c r="H702" t="n">
-        <v>0</v>
+        <v>99429.13</v>
       </c>
       <c r="I702" t="n">
-        <v>0</v>
+        <v>3171.78</v>
       </c>
       <c r="J702" t="n">
-        <v>35989998.13</v>
+        <v>35890569</v>
       </c>
     </row>
     <row r="703">
@@ -28565,13 +28565,13 @@
         <v>23434999.8</v>
       </c>
       <c r="H703" t="n">
-        <v>0</v>
+        <v>49098.49</v>
       </c>
       <c r="I703" t="n">
-        <v>0</v>
+        <v>1566.24</v>
       </c>
       <c r="J703" t="n">
-        <v>23434999.8</v>
+        <v>23385901.31</v>
       </c>
     </row>
     <row r="704">
@@ -28605,13 +28605,13 @@
         <v>32097999.96</v>
       </c>
       <c r="H704" t="n">
-        <v>0</v>
+        <v>100813.18</v>
       </c>
       <c r="I704" t="n">
-        <v>0</v>
+        <v>3215.93</v>
       </c>
       <c r="J704" t="n">
-        <v>32097999.96</v>
+        <v>31997186.78</v>
       </c>
     </row>
     <row r="705">
@@ -28725,13 +28725,13 @@
         <v>32998445.8</v>
       </c>
       <c r="H707" t="n">
-        <v>604883.63</v>
+        <v>1085396</v>
       </c>
       <c r="I707" t="n">
-        <v>62432.08</v>
+        <v>123110.02</v>
       </c>
       <c r="J707" t="n">
-        <v>32393562.17</v>
+        <v>31913049.8</v>
       </c>
     </row>
     <row r="708">
@@ -28765,13 +28765,13 @@
         <v>36033198.22</v>
       </c>
       <c r="H708" t="n">
-        <v>0</v>
+        <v>204666.13</v>
       </c>
       <c r="I708" t="n">
-        <v>0</v>
+        <v>6528.84</v>
       </c>
       <c r="J708" t="n">
-        <v>36033198.22</v>
+        <v>35828532.09</v>
       </c>
     </row>
     <row r="709">
@@ -28845,13 +28845,13 @@
         <v>77898894.3</v>
       </c>
       <c r="H710" t="n">
-        <v>0</v>
+        <v>84001.16</v>
       </c>
       <c r="I710" t="n">
-        <v>0</v>
+        <v>2679.63</v>
       </c>
       <c r="J710" t="n">
-        <v>77898894.3</v>
+        <v>77814893.14</v>
       </c>
     </row>
     <row r="711">
@@ -28885,13 +28885,13 @@
         <v>24832463.21</v>
       </c>
       <c r="H711" t="n">
-        <v>0</v>
+        <v>706164.05</v>
       </c>
       <c r="I711" t="n">
-        <v>0</v>
+        <v>69286.32000000001</v>
       </c>
       <c r="J711" t="n">
-        <v>24832463.21</v>
+        <v>24126299.16</v>
       </c>
     </row>
     <row r="712">
@@ -28925,13 +28925,13 @@
         <v>34422078.35</v>
       </c>
       <c r="H712" t="n">
-        <v>0</v>
+        <v>442302.76</v>
       </c>
       <c r="I712" t="n">
-        <v>0</v>
+        <v>51291.02</v>
       </c>
       <c r="J712" t="n">
-        <v>34422078.35</v>
+        <v>33979775.59</v>
       </c>
     </row>
     <row r="713">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$714</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$716</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J714"/>
+  <dimension ref="A1:J716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -19285,13 +19285,13 @@
         <v>28277547.59</v>
       </c>
       <c r="H471" t="n">
-        <v>24320830.23</v>
+        <v>25098078.47</v>
       </c>
       <c r="I471" t="n">
-        <v>970501.73</v>
+        <v>1046950.04</v>
       </c>
       <c r="J471" t="n">
-        <v>3956717.36</v>
+        <v>3179469.12</v>
       </c>
     </row>
     <row r="472">
@@ -19725,13 +19725,13 @@
         <v>7109673.15</v>
       </c>
       <c r="H482" t="n">
-        <v>134831.17</v>
+        <v>2179552.55</v>
       </c>
       <c r="I482" t="n">
-        <v>4696.72</v>
+        <v>60976.47</v>
       </c>
       <c r="J482" t="n">
-        <v>6974841.98</v>
+        <v>4930120.6</v>
       </c>
     </row>
     <row r="483">
@@ -19845,13 +19845,13 @@
         <v>29576179.41</v>
       </c>
       <c r="H485" t="n">
-        <v>1373835.81</v>
+        <v>2282985.62</v>
       </c>
       <c r="I485" t="n">
-        <v>73245.00999999999</v>
+        <v>102303.87</v>
       </c>
       <c r="J485" t="n">
-        <v>28202343.6</v>
+        <v>27293193.79</v>
       </c>
     </row>
     <row r="486">
@@ -19965,13 +19965,13 @@
         <v>43789355.88</v>
       </c>
       <c r="H488" t="n">
-        <v>34319619.39</v>
+        <v>36978458.24</v>
       </c>
       <c r="I488" t="n">
-        <v>452643.71</v>
+        <v>521464.11</v>
       </c>
       <c r="J488" t="n">
-        <v>9469736.49</v>
+        <v>6810897.64</v>
       </c>
     </row>
     <row r="489">
@@ -20125,13 +20125,13 @@
         <v>9147934.25</v>
       </c>
       <c r="H492" t="n">
-        <v>2217399.59</v>
+        <v>2228969.36</v>
       </c>
       <c r="I492" t="n">
-        <v>58300.33</v>
+        <v>58718</v>
       </c>
       <c r="J492" t="n">
-        <v>6930534.66</v>
+        <v>6918964.89</v>
       </c>
     </row>
     <row r="493">
@@ -20325,13 +20325,13 @@
         <v>181409015</v>
       </c>
       <c r="H497" t="n">
-        <v>29660203.15</v>
+        <v>35442897.44</v>
       </c>
       <c r="I497" t="n">
-        <v>442407.81</v>
+        <v>553588.77</v>
       </c>
       <c r="J497" t="n">
-        <v>151748811.85</v>
+        <v>145966117.56</v>
       </c>
     </row>
     <row r="498">
@@ -20365,13 +20365,13 @@
         <v>26080985</v>
       </c>
       <c r="H498" t="n">
-        <v>107185.1</v>
+        <v>133001.2</v>
       </c>
       <c r="I498" t="n">
-        <v>1792.3</v>
+        <v>2724.26</v>
       </c>
       <c r="J498" t="n">
-        <v>25973799.9</v>
+        <v>25947983.8</v>
       </c>
     </row>
     <row r="499">
@@ -24365,13 +24365,13 @@
         <v>50062054.28</v>
       </c>
       <c r="H598" t="n">
-        <v>26145936.44</v>
+        <v>27333370.56</v>
       </c>
       <c r="I598" t="n">
-        <v>1281115.95</v>
+        <v>1363482.96</v>
       </c>
       <c r="J598" t="n">
-        <v>23916117.84</v>
+        <v>22728683.72</v>
       </c>
     </row>
     <row r="599">
@@ -25405,13 +25405,13 @@
         <v>31648004.35</v>
       </c>
       <c r="H624" t="n">
-        <v>27221408.52</v>
+        <v>27438666.59</v>
       </c>
       <c r="I624" t="n">
-        <v>335837.84</v>
+        <v>343426.89</v>
       </c>
       <c r="J624" t="n">
-        <v>4426595.83</v>
+        <v>4209337.76</v>
       </c>
     </row>
     <row r="625">
@@ -26605,13 +26605,13 @@
         <v>2624909.09</v>
       </c>
       <c r="H654" t="n">
-        <v>258309.25</v>
+        <v>366122.67</v>
       </c>
       <c r="I654" t="n">
-        <v>6344.56</v>
+        <v>9783.799999999999</v>
       </c>
       <c r="J654" t="n">
-        <v>2366599.84</v>
+        <v>2258786.42</v>
       </c>
     </row>
     <row r="655">
@@ -26808,7 +26808,7 @@
         <v>3731967.69</v>
       </c>
       <c r="I659" t="n">
-        <v>626313.58</v>
+        <v>792028.13</v>
       </c>
       <c r="J659" t="n">
         <v>15017964.08</v>
@@ -28337,7 +28337,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -28347,22 +28347,22 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 16ª URG</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>37600000</v>
+        <v>42542200.39</v>
       </c>
       <c r="F698" t="n">
         <v>0</v>
       </c>
       <c r="G698" t="n">
-        <v>37600000</v>
+        <v>42542200.39</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -28371,38 +28371,38 @@
         <v>0</v>
       </c>
       <c r="J698" t="n">
-        <v>37600000</v>
+        <v>42542200.39</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 28ª URG</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>1099724.43</v>
+        <v>34497775.12</v>
       </c>
       <c r="F699" t="n">
         <v>0</v>
       </c>
       <c r="G699" t="n">
-        <v>1099724.43</v>
+        <v>34497775.12</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -28411,13 +28411,13 @@
         <v>0</v>
       </c>
       <c r="J699" t="n">
-        <v>1099724.43</v>
+        <v>34497775.12</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -28427,42 +28427,42 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>47349998.43</v>
+        <v>37600000</v>
       </c>
       <c r="F700" t="n">
         <v>0</v>
       </c>
       <c r="G700" t="n">
-        <v>47349998.43</v>
+        <v>37600000</v>
       </c>
       <c r="H700" t="n">
-        <v>98942.17999999999</v>
+        <v>0</v>
       </c>
       <c r="I700" t="n">
-        <v>3156.24</v>
+        <v>0</v>
       </c>
       <c r="J700" t="n">
-        <v>47251056.25</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -28472,32 +28472,32 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>31699998.96</v>
+        <v>1099724.43</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
       </c>
       <c r="G701" t="n">
-        <v>31699998.96</v>
+        <v>1099724.43</v>
       </c>
       <c r="H701" t="n">
-        <v>29454.44</v>
+        <v>0</v>
       </c>
       <c r="I701" t="n">
-        <v>939.59</v>
+        <v>0</v>
       </c>
       <c r="J701" t="n">
-        <v>31670544.52</v>
+        <v>1099724.43</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -28512,32 +28512,32 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
       <c r="F702" t="n">
         <v>0</v>
       </c>
       <c r="G702" t="n">
-        <v>35989998.13</v>
+        <v>47349998.43</v>
       </c>
       <c r="H702" t="n">
-        <v>99429.13</v>
+        <v>98942.17999999999</v>
       </c>
       <c r="I702" t="n">
-        <v>3171.78</v>
+        <v>3156.24</v>
       </c>
       <c r="J702" t="n">
-        <v>35890569</v>
+        <v>47251056.25</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -28552,32 +28552,32 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>23434999.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="F703" t="n">
         <v>0</v>
       </c>
       <c r="G703" t="n">
-        <v>23434999.8</v>
+        <v>31699998.96</v>
       </c>
       <c r="H703" t="n">
-        <v>49098.49</v>
+        <v>29454.44</v>
       </c>
       <c r="I703" t="n">
-        <v>1566.24</v>
+        <v>939.59</v>
       </c>
       <c r="J703" t="n">
-        <v>23385901.31</v>
+        <v>31670544.52</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -28592,32 +28592,32 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
       <c r="F704" t="n">
         <v>0</v>
       </c>
       <c r="G704" t="n">
-        <v>32097999.96</v>
+        <v>35989998.13</v>
       </c>
       <c r="H704" t="n">
-        <v>100813.18</v>
+        <v>99429.13</v>
       </c>
       <c r="I704" t="n">
-        <v>3215.93</v>
+        <v>3171.78</v>
       </c>
       <c r="J704" t="n">
-        <v>31997186.78</v>
+        <v>35890569</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -28627,37 +28627,37 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>0</v>
+        <v>23434999.8</v>
       </c>
       <c r="F705" t="n">
         <v>0</v>
       </c>
       <c r="G705" t="n">
-        <v>0</v>
+        <v>23434999.8</v>
       </c>
       <c r="H705" t="n">
-        <v>0</v>
+        <v>49098.49</v>
       </c>
       <c r="I705" t="n">
-        <v>0</v>
+        <v>1566.24</v>
       </c>
       <c r="J705" t="n">
-        <v>0</v>
+        <v>23385901.31</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -28667,37 +28667,37 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>14264750.82</v>
+        <v>32097999.96</v>
       </c>
       <c r="F706" t="n">
         <v>0</v>
       </c>
       <c r="G706" t="n">
-        <v>14264750.82</v>
+        <v>32097999.96</v>
       </c>
       <c r="H706" t="n">
-        <v>0</v>
+        <v>100813.18</v>
       </c>
       <c r="I706" t="n">
-        <v>0</v>
+        <v>3215.93</v>
       </c>
       <c r="J706" t="n">
-        <v>14264750.82</v>
+        <v>31997186.78</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -28707,37 +28707,37 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>32998445.8</v>
+        <v>0</v>
       </c>
       <c r="F707" t="n">
         <v>0</v>
       </c>
       <c r="G707" t="n">
-        <v>32998445.8</v>
+        <v>0</v>
       </c>
       <c r="H707" t="n">
-        <v>1085396</v>
+        <v>0</v>
       </c>
       <c r="I707" t="n">
-        <v>123110.02</v>
+        <v>0</v>
       </c>
       <c r="J707" t="n">
-        <v>31913049.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -28747,37 +28747,37 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>36033198.22</v>
+        <v>14264750.82</v>
       </c>
       <c r="F708" t="n">
         <v>0</v>
       </c>
       <c r="G708" t="n">
-        <v>36033198.22</v>
+        <v>14264750.82</v>
       </c>
       <c r="H708" t="n">
-        <v>204666.13</v>
+        <v>0</v>
       </c>
       <c r="I708" t="n">
-        <v>6528.84</v>
+        <v>0</v>
       </c>
       <c r="J708" t="n">
-        <v>35828532.09</v>
+        <v>14264750.82</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -28787,37 +28787,37 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>45188997.86</v>
+        <v>32998445.8</v>
       </c>
       <c r="F709" t="n">
         <v>0</v>
       </c>
       <c r="G709" t="n">
-        <v>45188997.86</v>
+        <v>32998445.8</v>
       </c>
       <c r="H709" t="n">
-        <v>0</v>
+        <v>1085396</v>
       </c>
       <c r="I709" t="n">
-        <v>0</v>
+        <v>123110.02</v>
       </c>
       <c r="J709" t="n">
-        <v>45188997.86</v>
+        <v>31913049.8</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -28827,37 +28827,37 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>77898894.3</v>
+        <v>36033198.22</v>
       </c>
       <c r="F710" t="n">
         <v>0</v>
       </c>
       <c r="G710" t="n">
-        <v>77898894.3</v>
+        <v>36033198.22</v>
       </c>
       <c r="H710" t="n">
-        <v>84001.16</v>
+        <v>204666.13</v>
       </c>
       <c r="I710" t="n">
-        <v>2679.63</v>
+        <v>6528.84</v>
       </c>
       <c r="J710" t="n">
-        <v>77814893.14</v>
+        <v>35828532.09</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -28867,37 +28867,37 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>24832463.21</v>
+        <v>45188997.86</v>
       </c>
       <c r="F711" t="n">
         <v>0</v>
       </c>
       <c r="G711" t="n">
-        <v>24832463.21</v>
+        <v>45188997.86</v>
       </c>
       <c r="H711" t="n">
-        <v>706164.05</v>
+        <v>0</v>
       </c>
       <c r="I711" t="n">
-        <v>69286.32000000001</v>
+        <v>0</v>
       </c>
       <c r="J711" t="n">
-        <v>24126299.16</v>
+        <v>45188997.86</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -28907,37 +28907,37 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>34422078.35</v>
+        <v>77898894.3</v>
       </c>
       <c r="F712" t="n">
         <v>0</v>
       </c>
       <c r="G712" t="n">
-        <v>34422078.35</v>
+        <v>77898894.3</v>
       </c>
       <c r="H712" t="n">
-        <v>442302.76</v>
+        <v>84001.16</v>
       </c>
       <c r="I712" t="n">
-        <v>51291.02</v>
+        <v>2679.63</v>
       </c>
       <c r="J712" t="n">
-        <v>33979775.59</v>
+        <v>77814893.14</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -28952,70 +28952,150 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>30603197.87</v>
+        <v>24832463.21</v>
       </c>
       <c r="F713" t="n">
         <v>0</v>
       </c>
       <c r="G713" t="n">
-        <v>30603197.87</v>
+        <v>24832463.21</v>
       </c>
       <c r="H713" t="n">
-        <v>1284027.29</v>
+        <v>706164.05</v>
       </c>
       <c r="I713" t="n">
-        <v>108112.79</v>
+        <v>69286.32000000001</v>
       </c>
       <c r="J713" t="n">
-        <v>29319170.58</v>
+        <v>24126299.16</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="H714" t="n">
+        <v>442302.76</v>
+      </c>
+      <c r="I714" t="n">
+        <v>51291.02</v>
+      </c>
+      <c r="J714" t="n">
+        <v>33979775.59</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0</v>
+      </c>
+      <c r="G715" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="H715" t="n">
+        <v>1284027.29</v>
+      </c>
+      <c r="I715" t="n">
+        <v>108112.79</v>
+      </c>
+      <c r="J715" t="n">
+        <v>29319170.58</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr">
+      <c r="D716" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="E714" t="n">
+      <c r="E716" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="F714" t="n">
-        <v>0</v>
-      </c>
-      <c r="G714" t="n">
+      <c r="F716" t="n">
+        <v>0</v>
+      </c>
+      <c r="G716" t="n">
         <v>31172534.58</v>
       </c>
-      <c r="H714" t="n">
-        <v>0</v>
-      </c>
-      <c r="I714" t="n">
-        <v>0</v>
-      </c>
-      <c r="J714" t="n">
+      <c r="H716" t="n">
+        <v>0</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J716" t="n">
         <v>31172534.58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J714"/>
+  <autoFilter ref="A1:J716"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L722"/>
+  <dimension ref="A1:L746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44451,12 +44451,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -44466,17 +44466,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44501,24 +44501,24 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44528,17 +44528,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44548,27 +44548,27 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>31913049.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
@@ -44590,17 +44590,17 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44610,22 +44610,22 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -44652,17 +44652,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44672,22 +44672,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44714,17 +44714,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44734,22 +44734,22 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -44776,17 +44776,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44796,22 +44796,22 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
@@ -44823,12 +44823,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44838,17 +44838,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44858,7 +44858,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44873,24 +44873,24 @@
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44900,17 +44900,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44920,39 +44920,39 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44962,17 +44962,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44982,39 +44982,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>706164.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>69286.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>24126299.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -45024,17 +45024,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45044,39 +45044,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>442302.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>51291.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>33979775.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45086,17 +45086,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45106,87 +45106,1575 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>1284027.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>108112.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>29319170.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>9497685</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperação Funcional </t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>14264750.82</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>14264750.82</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>14264750.82</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>2301762 000023/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>9414460</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>32998445.8</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>32998445.8</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>1085396</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>123110.02</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>31913049.8</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>84001.16</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>2679.63</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>77814893.14</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>706164.05</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>69286.32</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>24126299.16</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>442302.76</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>51291.02</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>33979775.59</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>1284027.29</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>108112.79</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>29319170.58</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B746" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr">
+      <c r="E746" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F722" t="inlineStr">
+      <c r="F746" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="L722" t="inlineStr">
+      <c r="L746" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L746"/>
+  <dimension ref="A1:L721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6572398.61</t>
+          <t>6595470.42</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>7612144.85</t>
+          <t>7640597.15</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>913076.26</t>
+          <t>890004.45</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -28061,17 +28061,17 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>29342447.39</t>
+          <t>31150162.08</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>1839385.71</t>
+          <t>2038585.67</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>2651594.48</t>
+          <t>843879.79</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -29353,12 +29353,12 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>554685.66</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>52604103.19</t>
+          <t>53158788.85</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>17250947.17</t>
+          <t>17805632.83</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29636,11 +29636,7 @@
           <t xml:space="preserve">DC-9441355/2024 </t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>9441355</t>
-        </is>
-      </c>
+      <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -29686,11 +29682,7 @@
           <t>2808049.54</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>2301520 000014/2024</t>
-        </is>
-      </c>
+      <c r="L472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30665,17 +30657,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>36978458.24</t>
+          <t>37813731.11</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>521464.11</t>
+          <t>549433.12</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>6810897.64</t>
+          <t>5975624.77</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -32463,17 +32455,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>748993.38</t>
+          <t>806267.63</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>82329.13</t>
+          <t>91155.09</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>382123.68</t>
+          <t>324849.43</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -32649,17 +32641,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>1355967.86</t>
+          <t>1394881.54</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>146490.03</t>
+          <t>152486.62</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>364985.65</t>
+          <t>326071.97</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -37299,17 +37291,17 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>32145995.87</t>
+          <t>32992827.05</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>1389956.58</t>
+          <t>1452411.3</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>15410794.39</t>
+          <t>14563963.21</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -40610,11 +40602,7 @@
           <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>9469794</t>
-        </is>
-      </c>
+      <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -40660,11 +40648,7 @@
           <t>7404850.23</t>
         </is>
       </c>
-      <c r="L649" t="inlineStr">
-        <is>
-          <t>2301931 000002/2025</t>
-        </is>
-      </c>
+      <c r="L649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -41071,12 +41055,12 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2131240</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>12585961.98</t>
+          <t>14717201.98</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -41091,7 +41075,7 @@
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>10509663.29</t>
+          <t>12640903.29</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
@@ -43189,7 +43173,7 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>1552.5</t>
+          <t>112220.23</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
@@ -43199,7 +43183,7 @@
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>5341030.38</t>
+          <t>5230362.65</t>
         </is>
       </c>
       <c r="L690" t="inlineStr">
@@ -43893,14 +43877,10 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
-        </is>
-      </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>9482017</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr"/>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43908,17 +43888,17 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -43928,59 +43908,51 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>98942.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>3156.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>47251056.25</t>
-        </is>
-      </c>
-      <c r="L702" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>41648190.39</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
-        </is>
-      </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>9493205</t>
-        </is>
-      </c>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento  2 (835 a 1250), extensão 8,300 km.</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -43990,41 +43962,33 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>29454.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>939.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>31670544.52</t>
-        </is>
-      </c>
-      <c r="L703" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>9482032</t>
-        </is>
-      </c>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44032,17 +43996,17 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t xml:space="preserve">Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Segmento 1 (0 a 835), extensão: 16,700 km </t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -44052,39 +44016,35 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>99429.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>3171.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>35890569</t>
-        </is>
-      </c>
-      <c r="L704" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -44099,12 +44059,12 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -44114,22 +44074,22 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>49098.49</t>
+          <t>98942.18</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>1566.24</t>
+          <t>3156.24</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>23385901.31</t>
+          <t>47251056.25</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -44141,12 +44101,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -44161,12 +44121,12 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -44176,22 +44136,22 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>94619.15</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>3018.34</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>31997186.78</t>
+          <t>31605379.81</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
@@ -44203,12 +44163,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -44218,17 +44178,17 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -44238,39 +44198,39 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99429.13</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3171.78</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35890569</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -44280,17 +44240,17 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -44300,39 +44260,39 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236173.66</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7533.93</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23198826.14</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -44342,17 +44302,17 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44362,27 +44322,27 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100813.18</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3215.93</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31997186.78</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
@@ -44513,12 +44473,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44528,17 +44488,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44548,7 +44508,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44563,24 +44523,24 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44590,47 +44550,47 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1085396</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123110.02</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32018655.9</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
@@ -44652,17 +44612,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44672,22 +44632,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44714,17 +44674,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44734,22 +44694,22 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -44761,12 +44721,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44776,17 +44736,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44796,7 +44756,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44811,24 +44771,24 @@
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44838,17 +44798,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44858,39 +44818,39 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84001.16</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2679.63</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77814893.14</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44900,17 +44860,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44920,39 +44880,39 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>706164.05</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69286.32</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24126299.16</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44962,17 +44922,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44982,39 +44942,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442302.76</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51291.02</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33979775.59</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -45024,17 +44984,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45044,39 +45004,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1284027.29</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108112.79</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29319170.58</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45086,17 +45046,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45106,1575 +45066,25 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3122723.66</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>352855.67</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28049810.92</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>Rodovia</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>DM-9497685/2026</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>9497685</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>14264750.82</t>
-        </is>
-      </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>14264750.82</t>
-        </is>
-      </c>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K723" t="inlineStr">
-        <is>
-          <t>14264750.82</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>2301762 000023/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>DM-005/2024-A</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>9414460</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
-        </is>
-      </c>
-      <c r="F724" t="inlineStr">
-        <is>
-          <t>32998445.8</t>
-        </is>
-      </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>32998445.8</t>
-        </is>
-      </c>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>1085396</t>
-        </is>
-      </c>
-      <c r="J724" t="inlineStr">
-        <is>
-          <t>123110.02</t>
-        </is>
-      </c>
-      <c r="K724" t="inlineStr">
-        <is>
-          <t>31913049.8</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E725" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H725" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I725" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K725" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E726" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F726" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G726" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H726" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I726" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J726" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K726" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L726" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F727" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H727" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I727" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J727" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K727" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I728" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J728" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K728" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F729" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G729" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I729" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K729" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J730" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K730" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F731" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H731" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J731" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K731" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B732" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F732" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G732" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H732" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I732" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J732" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K732" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L732" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B733" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C733" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D733" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E733" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F733" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H733" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I733" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J733" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K733" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L733" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D734" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E734" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F734" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G734" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H734" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I734" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J734" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K734" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L734" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B735" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C735" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F735" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G735" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H735" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I735" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J735" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K735" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D736" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F736" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G736" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H736" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I736" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J736" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K736" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L736" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F737" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G737" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H737" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I737" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J737" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K737" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L737" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D738" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F738" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G738" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I738" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J738" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K738" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B739" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C739" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D739" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E739" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F739" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G739" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I739" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J739" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K739" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L739" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B740" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C740" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D740" t="inlineStr">
-        <is>
-          <t>Supervisão</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr">
-        <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
-        </is>
-      </c>
-      <c r="F740" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="G740" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H740" t="inlineStr">
-        <is>
-          <t>36033198.22</t>
-        </is>
-      </c>
-      <c r="I740" t="inlineStr">
-        <is>
-          <t>204666.13</t>
-        </is>
-      </c>
-      <c r="J740" t="inlineStr">
-        <is>
-          <t>6528.84</t>
-        </is>
-      </c>
-      <c r="K740" t="inlineStr">
-        <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L740" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
-        <is>
-          <t>DO-009482046/2025-L2</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr">
-        <is>
-          <t>9482046</t>
-        </is>
-      </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D741" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="E741" t="inlineStr">
-        <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
-        </is>
-      </c>
-      <c r="F741" t="inlineStr">
-        <is>
-          <t>45188997.86</t>
-        </is>
-      </c>
-      <c r="G741" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H741" t="inlineStr">
-        <is>
-          <t>45188997.86</t>
-        </is>
-      </c>
-      <c r="I741" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J741" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K741" t="inlineStr">
-        <is>
-          <t>45188997.86</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
-        <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B742" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
-      <c r="C742" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D742" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
-        </is>
-      </c>
-      <c r="F742" t="inlineStr">
-        <is>
-          <t>77898894.3</t>
-        </is>
-      </c>
-      <c r="G742" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H742" t="inlineStr">
-        <is>
-          <t>77898894.3</t>
-        </is>
-      </c>
-      <c r="I742" t="inlineStr">
-        <is>
-          <t>84001.16</t>
-        </is>
-      </c>
-      <c r="J742" t="inlineStr">
-        <is>
-          <t>2679.63</t>
-        </is>
-      </c>
-      <c r="K742" t="inlineStr">
-        <is>
-          <t>77814893.14</t>
-        </is>
-      </c>
-      <c r="L742" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
-        <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D743" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E743" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
-        </is>
-      </c>
-      <c r="F743" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="G743" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H743" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="I743" t="inlineStr">
-        <is>
-          <t>706164.05</t>
-        </is>
-      </c>
-      <c r="J743" t="inlineStr">
-        <is>
-          <t>69286.32</t>
-        </is>
-      </c>
-      <c r="K743" t="inlineStr">
-        <is>
-          <t>24126299.16</t>
-        </is>
-      </c>
-      <c r="L743" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
-        <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B744" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
-      <c r="C744" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D744" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E744" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
-        </is>
-      </c>
-      <c r="F744" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="G744" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H744" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="I744" t="inlineStr">
-        <is>
-          <t>442302.76</t>
-        </is>
-      </c>
-      <c r="J744" t="inlineStr">
-        <is>
-          <t>51291.02</t>
-        </is>
-      </c>
-      <c r="K744" t="inlineStr">
-        <is>
-          <t>33979775.59</t>
-        </is>
-      </c>
-      <c r="L744" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
-        <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B745" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D745" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E745" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
-        </is>
-      </c>
-      <c r="F745" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="G745" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="I745" t="inlineStr">
-        <is>
-          <t>1284027.29</t>
-        </is>
-      </c>
-      <c r="J745" t="inlineStr">
-        <is>
-          <t>108112.79</t>
-        </is>
-      </c>
-      <c r="K745" t="inlineStr">
-        <is>
-          <t>29319170.58</t>
-        </is>
-      </c>
-      <c r="L745" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
-        <is>
-          <t>DM-008/2024-A</t>
-        </is>
-      </c>
-      <c r="B746" t="inlineStr">
-        <is>
-          <t>9422064</t>
-        </is>
-      </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D746" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E746" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
-        </is>
-      </c>
-      <c r="F746" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="G746" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H746" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="I746" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J746" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K746" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="L746" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L721"/>
+  <dimension ref="A1:L725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44473,12 +44473,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44488,17 +44488,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44523,24 +44523,24 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44550,59 +44550,59 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>32018655.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44612,17 +44612,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44632,39 +44632,39 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44674,59 +44674,59 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>1085396</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>123110.02</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>32018655.9</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44736,17 +44736,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44756,39 +44756,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44798,17 +44798,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44818,39 +44818,39 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44860,17 +44860,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44880,39 +44880,39 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>706164.05</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>69286.32</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>24126299.16</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44922,17 +44922,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44942,39 +44942,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>442302.76</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>51291.02</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>33979775.59</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44984,17 +44984,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45004,87 +45004,335 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>1284027.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>108112.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>29319170.58</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>84001.16</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>2679.63</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>77814893.14</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>706164.05</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>69286.32</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>24126299.16</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>442302.76</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>51291.02</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>33979775.59</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>1284027.29</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>108112.79</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>29319170.58</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B725" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr">
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E721" t="inlineStr">
+      <c r="E725" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F721" t="inlineStr">
+      <c r="F725" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H721" t="inlineStr">
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I721" t="inlineStr">
+      <c r="I725" t="inlineStr">
         <is>
           <t>3122723.66</t>
         </is>
       </c>
-      <c r="J721" t="inlineStr">
+      <c r="J725" t="inlineStr">
         <is>
           <t>352855.67</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr">
+      <c r="K725" t="inlineStr">
         <is>
           <t>28049810.92</t>
         </is>
       </c>
-      <c r="L721" t="inlineStr">
+      <c r="L725" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L725"/>
+  <dimension ref="A1:L721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28805,17 +28805,17 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>28236307.03</t>
+          <t>30061702.59</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>1562283.98</t>
+          <t>1760462</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>14552348.86</t>
+          <t>12726953.3</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -38965,17 +38965,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>17178308.35</t>
+          <t>24578876.25</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>492175.03</t>
+          <t>683991.5</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>22156263.64</t>
+          <t>14755695.74</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -41375,17 +41375,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>1095630.47</t>
+          <t>1369796.14</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>235452.45</t>
+          <t>294153.53</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>13833716.48</t>
+          <t>13559550.81</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>471547.81</t>
+          <t>1110292.85</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>100551.66</t>
+          <t>236825.56</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>24021175.35</t>
+          <t>23382430.31</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41809,17 +41809,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>202141.46</t>
+          <t>478613.8</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>42853.93</t>
+          <t>101466.03</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>9104488.74</t>
+          <t>8828016.4</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -44473,12 +44473,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44488,17 +44488,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44523,24 +44523,24 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44550,59 +44550,59 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1085396</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123110.02</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32018655.9</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44612,17 +44612,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44632,39 +44632,39 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44674,59 +44674,59 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>32018655.9</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44736,17 +44736,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44756,39 +44756,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44798,17 +44798,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44818,39 +44818,39 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>84001.16</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>2679.63</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>77814893.14</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44860,17 +44860,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44880,39 +44880,39 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>706164.05</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>69286.32</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>24126299.16</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44922,17 +44922,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44942,39 +44942,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>442302.76</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>51291.02</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>33979775.59</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44984,17 +44984,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45004,39 +45004,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1284027.29</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108112.79</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>29319170.58</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45046,17 +45046,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45066,273 +45066,25 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>3122723.66</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>352855.67</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>28049810.92</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>706164.05</t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>69286.32</t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
-        <is>
-          <t>24126299.16</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
-        <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t>442302.76</t>
-        </is>
-      </c>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t>51291.02</t>
-        </is>
-      </c>
-      <c r="K723" t="inlineStr">
-        <is>
-          <t>33979775.59</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
-        <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E724" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
-        </is>
-      </c>
-      <c r="F724" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="G724" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="I724" t="inlineStr">
-        <is>
-          <t>1284027.29</t>
-        </is>
-      </c>
-      <c r="J724" t="inlineStr">
-        <is>
-          <t>108112.79</t>
-        </is>
-      </c>
-      <c r="K724" t="inlineStr">
-        <is>
-          <t>29319170.58</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
-        <is>
-          <t>DM-008/2024-A</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>9422064</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E725" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
-        </is>
-      </c>
-      <c r="F725" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H725" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="I725" t="inlineStr">
-        <is>
-          <t>3122723.66</t>
-        </is>
-      </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>352855.67</t>
-        </is>
-      </c>
-      <c r="K725" t="inlineStr">
-        <is>
-          <t>28049810.92</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L721"/>
+  <dimension ref="A1:L722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30719,17 +30719,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>4321961.53</t>
+          <t>4925478.97</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>111645.58</t>
+          <t>133432.55</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>26550110.77</t>
+          <t>25946593.33</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -30843,17 +30843,17 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>2016899.4</t>
+          <t>2098902.99</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>1029223.7</t>
+          <t>1071070.13</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>1883818</t>
+          <t>1801814.41</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -37415,17 +37415,17 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>25738126.27</t>
+          <t>26478243.14</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>1396822.53</t>
+          <t>1453592.1</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>25595629.06</t>
+          <t>24855512.19</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
@@ -41003,17 +41003,17 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>3149597.47</t>
+          <t>3995405.43</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>672167.05</t>
+          <t>852669.83</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>19018233</t>
+          <t>18172425.04</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -41499,17 +41499,17 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>3776564.13</t>
+          <t>4876229.77</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>359723.53</t>
+          <t>468624.36</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>11528432.06</t>
+          <t>10428766.42</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -42119,17 +42119,17 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>295085.15</t>
+          <t>470619.49</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>9413.21</t>
+          <t>15012.75</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>6382319.18</t>
+          <t>6206784.84</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
@@ -42305,17 +42305,17 @@
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>2020033.16</t>
+          <t>3730159.05</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>254120.31</t>
+          <t>489500.96</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>11170959.73</t>
+          <t>9460833.84</t>
         </is>
       </c>
       <c r="L676" t="inlineStr">
@@ -43111,17 +43111,17 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>1155443.59</t>
+          <t>2293831.31</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>124341.92</t>
+          <t>207512.68</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>35798731.38</t>
+          <t>34660343.66</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -43545,17 +43545,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123432.43</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62987.56</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>4506718.06</t>
+          <t>4383285.63</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -43947,7 +43947,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento  2 (835 a 1250), extensão 8,300 km.</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
@@ -44001,7 +44001,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Segmento 1 (0 a 835), extensão: 16,700 km </t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
@@ -44203,17 +44203,17 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>99429.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>3171.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>35890569</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
@@ -44597,14 +44597,10 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44612,17 +44608,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44632,29 +44628,25 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>35828532.09</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -44721,12 +44713,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44736,17 +44728,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44756,39 +44748,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44803,12 +44795,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44818,22 +44810,22 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
@@ -44845,12 +44837,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44860,17 +44852,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44880,39 +44872,39 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>706164.05</t>
+          <t>84001.16</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>69286.32</t>
+          <t>2679.63</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>24126299.16</t>
+          <t>77814893.14</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44927,12 +44919,12 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44942,22 +44934,22 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>442302.76</t>
+          <t>706164.05</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>51291.02</t>
+          <t>69286.32</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>33979775.59</t>
+          <t>24126299.16</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
@@ -44969,12 +44961,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44989,12 +44981,12 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45004,22 +44996,22 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>1284027.29</t>
+          <t>442302.76</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>108112.79</t>
+          <t>51291.02</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>29319170.58</t>
+          <t>33979775.59</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
@@ -45031,60 +45023,122 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>1284027.29</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>108112.79</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>29319170.58</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
+      <c r="B722" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr">
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E721" t="inlineStr">
+      <c r="E722" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F721" t="inlineStr">
+      <c r="F722" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H721" t="inlineStr">
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I721" t="inlineStr">
+      <c r="I722" t="inlineStr">
         <is>
           <t>3122723.66</t>
         </is>
       </c>
-      <c r="J721" t="inlineStr">
+      <c r="J722" t="inlineStr">
         <is>
           <t>352855.67</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr">
+      <c r="K722" t="inlineStr">
         <is>
           <t>28049810.92</t>
         </is>
       </c>
-      <c r="L721" t="inlineStr">
+      <c r="L722" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L722"/>
+  <dimension ref="A1:L728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43934,7 +43934,11 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -43988,10 +43992,14 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -44001,7 +44009,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
@@ -44039,12 +44047,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -44054,17 +44062,17 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -44074,39 +44082,35 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>98942.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>3156.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>47251056.25</t>
-        </is>
-      </c>
-      <c r="L705" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -44116,17 +44120,17 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -44136,39 +44140,35 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>94619.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>3018.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>31605379.81</t>
-        </is>
-      </c>
-      <c r="L706" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -44183,12 +44183,12 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -44198,22 +44198,22 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98942.18</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3156.24</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>47251056.25</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
@@ -44225,12 +44225,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -44245,12 +44245,12 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -44260,22 +44260,22 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>236173.66</t>
+          <t>94619.15</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>7533.93</t>
+          <t>3018.34</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>23198826.14</t>
+          <t>31605379.81</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
@@ -44287,12 +44287,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -44307,12 +44307,12 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44322,22 +44322,22 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>31997186.78</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
@@ -44349,12 +44349,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -44364,17 +44364,17 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44384,39 +44384,39 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236173.66</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7533.93</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23198826.14</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -44426,17 +44426,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44446,39 +44446,39 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100813.18</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3215.93</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31997186.78</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44488,17 +44488,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44523,24 +44523,24 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44550,57 +44550,61 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>32018655.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C714" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44613,12 +44617,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44628,7 +44632,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44643,10 +44647,14 @@
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>1768342.65</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -44666,17 +44674,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44686,22 +44694,22 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -44713,12 +44721,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44728,17 +44736,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44748,39 +44756,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44790,61 +44798,57 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1085396</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123110.02</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32018655.9</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44852,17 +44856,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44872,39 +44876,35 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>77814893.14</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44914,17 +44914,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44934,39 +44934,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>706164.05</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>69286.32</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>24126299.16</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44976,17 +44976,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44996,39 +44996,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>442302.76</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>51291.02</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>33979775.59</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45038,17 +45038,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45058,87 +45058,459 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>1284027.29</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>108112.79</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>29319170.58</t>
+          <t>35828532.09</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>204666.13</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>6528.84</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>84001.16</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2679.63</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>77814893.14</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>706164.05</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>69286.32</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>24126299.16</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>442302.76</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>51291.02</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>33979775.59</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>1284027.29</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>108112.79</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>29319170.58</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B728" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr">
+      <c r="E728" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F722" t="inlineStr">
+      <c r="F728" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I722" t="inlineStr">
+      <c r="I728" t="inlineStr">
         <is>
           <t>3122723.66</t>
         </is>
       </c>
-      <c r="J722" t="inlineStr">
+      <c r="J728" t="inlineStr">
         <is>
           <t>352855.67</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr">
+      <c r="K728" t="inlineStr">
         <is>
           <t>28049810.92</t>
         </is>
       </c>
-      <c r="L722" t="inlineStr">
+      <c r="L728" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L728"/>
+  <dimension ref="A1:L725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27627,17 +27627,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>1105927.68</t>
+          <t>1177999.68</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>66314.6</t>
+          <t>73492.97</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>307487.12</t>
+          <t>235415.12</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -28557,17 +28557,17 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>18950254.07</t>
+          <t>20357094.1</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>1139200.92</t>
+          <t>1296725.53</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>14771370.2</t>
+          <t>13364530.17</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -29053,17 +29053,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>42740546.57</t>
+          <t>43658709.16</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>1576940.53</t>
+          <t>1639945.68</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>7516206.97</t>
+          <t>6598044.38</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -29425,17 +29425,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>21326695.49</t>
+          <t>22583302.95</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>1049157.66</t>
+          <t>1151934.58</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>24442250.96</t>
+          <t>23185643.5</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29727,17 +29727,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>2659709.31</t>
+          <t>2789988.76</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>110914.7</t>
+          <t>117571.97</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>8322692.46</t>
+          <t>8192413.01</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -29913,17 +29913,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>70201621.12</t>
+          <t>76206166.6</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>2927446.71</t>
+          <t>3184891.93</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>81974608.61</t>
+          <t>75970063.13</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30161,17 +30161,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>143989.05</t>
+          <t>213949.8</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>7014.9</t>
+          <t>12205.98</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>2396561.97</t>
+          <t>2326601.22</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -30285,17 +30285,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>2179552.55</t>
+          <t>4059210.05</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>60976.47</t>
+          <t>108617.7</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4930120.6</t>
+          <t>3050463.1</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30347,17 +30347,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>30269209.55</t>
+          <t>41509825.74</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>919112.24</t>
+          <t>1230592.5</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>21970438.38</t>
+          <t>10729822.19</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -30533,17 +30533,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>19433859.66</t>
+          <t>32208027.4</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>817663.81</t>
+          <t>2039206.85</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>76227813.27</t>
+          <t>63453645.53</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -30967,17 +30967,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>5120476.8</t>
+          <t>5728167.91</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>77902.29</t>
+          <t>92366.17</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>39452523.2</t>
+          <t>38844832.09</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31029,17 +31029,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>1773004.43</t>
+          <t>2499057.24</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>45836.21</t>
+          <t>72046.7</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>20685902.27</t>
+          <t>19959849.46</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>3127943.52</t>
+          <t>3749064.97</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>18301582.88</t>
+          <t>17680461.43</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -35803,17 +35803,17 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>53680846</t>
+          <t>58732716.82</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>3211937.05</t>
+          <t>3614380.02</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>21602078.23</t>
+          <t>16550207.41</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
@@ -37353,17 +37353,17 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>24832214.04</t>
+          <t>26214961.73</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>1179693.19</t>
+          <t>1261297.08</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>22173356.51</t>
+          <t>20790608.82</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>4994918.17</t>
+          <t>5041293.17</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>4890312.65</t>
+          <t>4843937.65</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -39027,17 +39027,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>171424.7</t>
+          <t>254883.93</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>7270.88</t>
+          <t>13463.55</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>2074672.9</t>
+          <t>1991213.67</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -39523,17 +39523,17 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>172156.59</t>
+          <t>198591.25</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>8393.43</t>
+          <t>10354.88</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1174189.87</t>
+          <t>1147755.21</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -40205,17 +40205,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>8776447.58</t>
+          <t>10061390.16</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>157370.32</t>
+          <t>191977.36</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>43038127.86</t>
+          <t>41753185.28</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -40453,17 +40453,17 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>25780749.1</t>
+          <t>27755030.86</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>259048.22</t>
+          <t>297185.39</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>33518645.87</t>
+          <t>31544364.11</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -41127,17 +41127,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>2365248.99</t>
+          <t>3178378.52</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>504016.44</t>
+          <t>677291.89</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>25629134.04</t>
+          <t>24816004.51</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -41189,17 +41189,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>4563869.02</t>
+          <t>5658949.14</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>399359.72</t>
+          <t>502342.37</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>7595404.81</t>
+          <t>6500324.69</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -41561,17 +41561,17 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>2369404.54</t>
+          <t>2570759.32</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6664.72</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>3830325.22</t>
+          <t>3628970.44</t>
         </is>
       </c>
       <c r="L664" t="inlineStr">
@@ -41623,7 +41623,7 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>405673.71</t>
+          <t>7129092.83</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
@@ -41633,7 +41633,7 @@
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>10524301.85</t>
+          <t>3800882.73</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
@@ -41747,17 +41747,17 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>15624439.46</t>
+          <t>23874408.23</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357219.59</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>26360138.65</t>
+          <t>18110169.88</t>
         </is>
       </c>
       <c r="L667" t="inlineStr">
@@ -41995,17 +41995,17 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>865117.08</t>
+          <t>1551053.42</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>36023.22</t>
+          <t>44779.27</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>19259882.92</t>
+          <t>18573946.58</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -42181,17 +42181,17 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82269.93</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6584.71</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>10619818.83</t>
+          <t>10537548.9</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -42367,17 +42367,17 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>1555371.56</t>
+          <t>2214018.44</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>190823.62</t>
+          <t>281482.05</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>12842674.51</t>
+          <t>12184027.63</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
@@ -43235,17 +43235,17 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>598527.91</t>
+          <t>978088.35</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>66572.01</t>
+          <t>107753.76</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>32606534.49</t>
+          <t>32226974.05</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -43956,7 +43956,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -43966,7 +43966,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43981,10 +43981,14 @@
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L703" t="inlineStr"/>
+          <t>9289765.74</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -44014,7 +44018,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -44024,7 +44028,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -44039,10 +44043,14 @@
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L704" t="inlineStr"/>
+          <t>9289765.74</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -44072,7 +44080,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -44082,7 +44090,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -44097,10 +44105,14 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L705" t="inlineStr"/>
+          <t>18914979.77</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -44130,7 +44142,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -44140,7 +44152,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -44155,10 +44167,14 @@
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L706" t="inlineStr"/>
+          <t>18914979.77</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -44327,17 +44343,17 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99429.13</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3171.78</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>35890569</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
@@ -44597,12 +44613,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44612,17 +44628,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44632,7 +44648,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44647,24 +44663,24 @@
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44674,61 +44690,57 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1085396</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123110.02</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32018655.9</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>9497685</t>
-        </is>
-      </c>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
       <c r="C716" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44741,12 +44753,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44756,7 +44768,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44771,26 +44783,18 @@
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>14264750.82</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr">
-        <is>
-          <t>2301762 000023/2025</t>
-        </is>
-      </c>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>9414460</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44798,57 +44802,57 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>32018655.9</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B718" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C718" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44856,17 +44860,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44876,25 +44880,29 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204666.13</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6528.84</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>1768342.65</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr"/>
+          <t>35828532.09</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -44961,12 +44969,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44976,17 +44984,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44996,39 +45004,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45038,17 +45046,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45058,39 +45066,39 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>84001.16</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>2679.63</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>77814893.14</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45100,17 +45108,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45120,39 +45128,39 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>1093860.13</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>133799.82</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>23738603.08</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45162,17 +45170,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45182,39 +45190,39 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442302.76</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51291.02</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>33979775.59</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45224,17 +45232,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45244,39 +45252,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>2055531.14</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>214571.53</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>28547666.73</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45291,12 +45299,12 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45306,211 +45314,25 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>706164.05</t>
+          <t>3122723.66</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>69286.32</t>
+          <t>352855.67</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>24126299.16</t>
+          <t>28049810.92</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
-        <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E726" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
-        </is>
-      </c>
-      <c r="F726" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="G726" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H726" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="I726" t="inlineStr">
-        <is>
-          <t>442302.76</t>
-        </is>
-      </c>
-      <c r="J726" t="inlineStr">
-        <is>
-          <t>51291.02</t>
-        </is>
-      </c>
-      <c r="K726" t="inlineStr">
-        <is>
-          <t>33979775.59</t>
-        </is>
-      </c>
-      <c r="L726" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
-        <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
-        </is>
-      </c>
-      <c r="F727" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H727" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="I727" t="inlineStr">
-        <is>
-          <t>1284027.29</t>
-        </is>
-      </c>
-      <c r="J727" t="inlineStr">
-        <is>
-          <t>108112.79</t>
-        </is>
-      </c>
-      <c r="K727" t="inlineStr">
-        <is>
-          <t>29319170.58</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>DM-008/2024-A</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>9422064</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="I728" t="inlineStr">
-        <is>
-          <t>3122723.66</t>
-        </is>
-      </c>
-      <c r="J728" t="inlineStr">
-        <is>
-          <t>352855.67</t>
-        </is>
-      </c>
-      <c r="K728" t="inlineStr">
-        <is>
-          <t>28049810.92</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L725"/>
+  <dimension ref="A1:L731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26263,17 +26263,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>4365171.24</t>
+          <t>4472200.27</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>441674.27</t>
+          <t>456904.48</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>3211750.86</t>
+          <t>3104721.83</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -28123,17 +28123,17 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>38850140.53</t>
+          <t>40721579.09</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>2809692.02</t>
+          <t>3108783.54</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>2951840.1</t>
+          <t>1080401.54</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -28867,17 +28867,17 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>32487325.6</t>
+          <t>33905390.5</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>1803563.04</t>
+          <t>1938493.49</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>2497193.65</t>
+          <t>1079128.75</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>35353156.02</t>
+          <t>37433918.31</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>17805632.83</t>
+          <t>15724870.54</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29487,17 +29487,17 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>30474934.34</t>
+          <t>31316238.1</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>1407677.98</t>
+          <t>1471522.11</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>17683670.87</t>
+          <t>16842367.11</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -29549,17 +29549,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>694073.51</t>
+          <t>705045.28</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>26559.17</t>
+          <t>27373.27</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>165695.5</t>
+          <t>154723.73</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -30099,17 +30099,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>365496.06</t>
+          <t>1170016</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>21299.64</t>
+          <t>98632.72</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>8377416.9</t>
+          <t>7572896.96</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -30223,17 +30223,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>674271.65</t>
+          <t>678573.03</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>30626.77</t>
+          <t>30945.93</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>250412.77</t>
+          <t>246111.39</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -31153,17 +31153,17 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>4021883.98</t>
+          <t>4689306.05</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>2366.45</t>
+          <t>4266.85</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>1957116.01</t>
+          <t>1289693.94</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -31773,17 +31773,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>4299228.98</t>
+          <t>5027911.86</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>69734.94</t>
+          <t>92979.92</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>17561257.42</t>
+          <t>16832574.54</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -31835,17 +31835,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>1228299.11</t>
+          <t>1499335.05</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>37334.68</t>
+          <t>47119.06</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>8182046.78</t>
+          <t>7911010.84</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -32889,17 +32889,17 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>636725.02</t>
+          <t>639290.82</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>79200.95</t>
+          <t>79596.33</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>1155650.6</t>
+          <t>1153084.8</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -33013,17 +33013,17 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>1779576.31</t>
+          <t>1781832.93</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>203736.13</t>
+          <t>204083.87</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>1941709.92</t>
+          <t>1939453.3</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -37105,17 +37105,17 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>391652.73</t>
+          <t>404605.37</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>35338.15</t>
+          <t>37058.26</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>1530991.55</t>
+          <t>1518038.91</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -37477,17 +37477,17 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>27333370.56</t>
+          <t>28183468.37</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>1363482.96</t>
+          <t>1425134.61</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>22728683.72</t>
+          <t>21878585.91</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -37539,17 +37539,17 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>27091255.57</t>
+          <t>28269743.87</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>1108710.91</t>
+          <t>1193907.62</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>22040465.68</t>
+          <t>20861977.38</t>
         </is>
       </c>
       <c r="L599" t="inlineStr">
@@ -37663,17 +37663,17 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>30685601.38</t>
+          <t>33019188.67</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>1357081.56</t>
+          <t>1495979.22</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>17073231.85</t>
+          <t>14739644.56</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
@@ -37849,17 +37849,17 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>955292.07</t>
+          <t>986664.68</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>41246.94</t>
+          <t>43574.78</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>529488.75</t>
+          <t>498116.14</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -38779,17 +38779,17 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>966914.63</t>
+          <t>1809547.16</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>43684.1</t>
+          <t>118361.06</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>3950885.8</t>
+          <t>3108253.27</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -39151,17 +39151,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>264833.81</t>
+          <t>317335.77</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>24497.1</t>
+          <t>31469.36</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>9395163.27</t>
+          <t>9342661.31</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -39275,17 +39275,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>2080303.32</t>
+          <t>2227471.49</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>88175.76</t>
+          <t>97506.22</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>3694449.12</t>
+          <t>3547280.95</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -39957,17 +39957,17 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>5724611.63</t>
+          <t>6596838.39</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>49661.35</t>
+          <t>65380.93</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>43368927.82</t>
+          <t>42496701.06</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -40143,17 +40143,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>3299582.84</t>
+          <t>3896181.61</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>60442.41</t>
+          <t>76548.09</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>6223409.45</t>
+          <t>5626810.68</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -40267,17 +40267,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>6563149.56</t>
+          <t>7434834.03</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>60601.39</t>
+          <t>76419.87</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>44397599.82</t>
+          <t>43525915.35</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -40329,17 +40329,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>11440004.49</t>
+          <t>15916258.01</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>195949.38</t>
+          <t>312586.36</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>41916787.23</t>
+          <t>37440533.71</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -40391,17 +40391,17 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>13376312.96</t>
+          <t>14534993.85</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>189993.16</t>
+          <t>226029.9</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>39865561.42</t>
+          <t>38706880.53</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -40515,17 +40515,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>7700082.26</t>
+          <t>17034916.84</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>95028.74</t>
+          <t>286639.5</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>45873917.73</t>
+          <t>36539083.15</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -40577,17 +40577,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>485335.3</t>
+          <t>607490.03</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>12098.6</t>
+          <t>16508.38</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>1170337.92</t>
+          <t>1048183.19</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -40635,17 +40635,17 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>1879558.63</t>
+          <t>2251277.05</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>53960.85</t>
+          <t>67379.88</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>7404850.23</t>
+          <t>7033131.81</t>
         </is>
       </c>
       <c r="L649" t="inlineStr"/>
@@ -40755,17 +40755,17 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>4375479.93</t>
+          <t>6245920.11</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>117451.13</t>
+          <t>155918.68</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>60608825.41</t>
+          <t>58738385.23</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -41628,7 +41628,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296100.03</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
@@ -42491,17 +42491,17 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135793.06</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12064.42</t>
         </is>
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>2962697.76</t>
+          <t>2826904.7</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -42699,32 +42699,28 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>9496643</t>
-        </is>
-      </c>
+          <t>DM-9512044/2026</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
+          <t>Recuperação funcional AMG-0555, Entrº BR-482 (Piranga) - Presidente Bernardes</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>79488.85</t>
+          <t>11358610.11</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -42734,7 +42730,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>79488.85</t>
+          <t>11358610.11</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42749,14 +42745,10 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>79488.85</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>1301606 000002/2025</t>
-        </is>
-      </c>
+          <t>11358610.11</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -42771,7 +42763,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -42781,12 +42773,12 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
+          <t xml:space="preserve"> Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>5579340.09</t>
+          <t>79488.85</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -42796,7 +42788,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>5579340.09</t>
+          <t>79488.85</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42811,7 +42803,7 @@
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>5579340.09</t>
+          <t>79488.85</t>
         </is>
       </c>
       <c r="L684" t="inlineStr">
@@ -42823,12 +42815,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -42838,17 +42830,17 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Prestação de serviços especiais de apoio à coordenação e apoio técnico na Diretoria de Construção - Lote 1 - Supervisão de Projetos</t>
+          <t>Implantação de Passarela na Rodovia MG-010 Km 15+850, trecho Belo Horizonte - Lagoa Santa (Cidade Administrativa), extensão de 312,00m</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>23052682.68</t>
+          <t>5579340.09</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -42858,12 +42850,12 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>23052682.68</t>
+          <t>5579340.09</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>544858.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
@@ -42873,24 +42865,24 @@
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>22507823.82</t>
+          <t>5579340.09</t>
         </is>
       </c>
       <c r="L685" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -42900,17 +42892,17 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Trevo de Acesso</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação da interseção de acesso ao Presídio de Iturama, na via Municipal - Extensão 2,000km</t>
+          <t>Prestação de serviços especiais de apoio à coordenação e apoio técnico na Diretoria de Construção - Lote 1 - Supervisão de Projetos</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>3700000</t>
+          <t>23052682.68</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -42920,39 +42912,39 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>3700000</t>
+          <t>23052682.68</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1167399.12</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22971.73</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>3700000</t>
+          <t>21885283.56</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -42962,17 +42954,17 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Trevo de Acesso</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
+          <t>Melhoramento e Pavimentação da interseção de acesso ao Presídio de Iturama, na via Municipal - Extensão 2,000km</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>12246076.65</t>
+          <t>3700000</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -42982,7 +42974,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>12246076.65</t>
+          <t>3700000</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42997,24 +42989,24 @@
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>12246076.65</t>
+          <t>3700000</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -43024,17 +43016,17 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
+          <t>Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>29302939.12</t>
+          <t>12246076.65</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -43044,39 +43036,39 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>29302939.12</t>
+          <t>12246076.65</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>430460.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>45845.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>28872478.43</t>
+          <t>12246076.65</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -43091,12 +43083,12 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>36954174.97</t>
+          <t>29302939.12</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -43106,39 +43098,39 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>36954174.97</t>
+          <t>29302939.12</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>2293831.31</t>
+          <t>839183.28</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>207512.68</t>
+          <t>116266.05</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>34660343.66</t>
+          <t>28463755.84</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -43148,17 +43140,17 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>5342582.88</t>
+          <t>36954174.97</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -43168,39 +43160,39 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>5342582.88</t>
+          <t>36954174.97</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>112220.23</t>
+          <t>2293831.31</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207512.68</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>5230362.65</t>
+          <t>34660343.66</t>
         </is>
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -43210,17 +43202,17 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
+          <t>Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>33205062.4</t>
+          <t>5342582.88</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -43230,59 +43222,59 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>33205062.4</t>
+          <t>5342582.88</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>978088.35</t>
+          <t>112220.23</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>107753.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>32226974.05</t>
+          <t>5230362.65</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00)</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>4005503.13</t>
+          <t>33205062.4</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -43292,27 +43284,27 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>4005503.13</t>
+          <t>33205062.4</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>978088.35</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107753.76</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>4005503.13</t>
+          <t>32226974.05</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
@@ -43329,7 +43321,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -43339,12 +43331,12 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00)</t>
+          <t>Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00)</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2520936.14</t>
+          <t>4005503.13</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -43354,7 +43346,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>2520936.14</t>
+          <t>4005503.13</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -43369,7 +43361,7 @@
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>2520936.14</t>
+          <t>4005503.13</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
@@ -43391,7 +43383,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -43401,12 +43393,12 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
+          <t>Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00)</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>3287560.73</t>
+          <t>2520936.14</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -43416,7 +43408,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>3287560.73</t>
+          <t>2520936.14</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -43431,7 +43423,7 @@
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>3287560.73</t>
+          <t>2520936.14</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -43443,32 +43435,32 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
+          <t>Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>31813334.15</t>
+          <t>3287560.73</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -43478,7 +43470,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>31813334.15</t>
+          <t>3287560.73</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43493,24 +43485,24 @@
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>31813334.15</t>
+          <t>3287560.73</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -43520,17 +43512,17 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>4506718.06</t>
+          <t>31813334.15</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -43540,39 +43532,39 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>4506718.06</t>
+          <t>31813334.15</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>123432.43</t>
+          <t>850758.92</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>62987.56</t>
+          <t>92437.35</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>4383285.63</t>
+          <t>30962575.23</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -43582,17 +43574,17 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
+          <t>serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>36950516.6</t>
+          <t>4506718.06</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -43602,39 +43594,39 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>36950516.6</t>
+          <t>4506718.06</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123432.43</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62987.56</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>36950516.6</t>
+          <t>4383285.63</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -43649,12 +43641,12 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 16ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>42542200.39</t>
+          <t>36950516.6</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -43664,22 +43656,22 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>42542200.39</t>
+          <t>36950516.6</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1030693.14</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115066.24</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>42542200.39</t>
+          <t>35919823.46</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
@@ -43691,12 +43683,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -43711,12 +43703,12 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 28ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 16ª URG</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>34497775.12</t>
+          <t>42542200.39</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -43726,7 +43718,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>34497775.12</t>
+          <t>42542200.39</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43741,7 +43733,7 @@
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>34497775.12</t>
+          <t>42542200.39</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">
@@ -43753,12 +43745,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -43768,17 +43760,17 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 28ª URG</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>37600000</t>
+          <t>34497775.12</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -43788,59 +43780,55 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>37600000</t>
+          <t>34497775.12</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>708590.2</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78030.21</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>37600000</t>
+          <t>33789184.92</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
-        </is>
-      </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>9275590</t>
-        </is>
-      </c>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>Restauração da interseção na Rodovia MGC-354, km 179, trecho: Av Marabá (Patos de Minas) - Entr BR 365</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>7919248.4</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -43850,7 +43838,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>7919248.4</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43865,19 +43853,15 @@
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>1099724.43</t>
-        </is>
-      </c>
-      <c r="L701" t="inlineStr">
-        <is>
-          <t>2301901 000003/2021</t>
-        </is>
-      </c>
+          <t>7919248.4</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -43888,17 +43872,17 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
+          <t>Restauração da interseção na Rodovia MGC-354, km 150,9, trecho: Travessia Urbana de Presidente Olegário</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>4277399.55</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -43908,7 +43892,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>4277399.55</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43923,7 +43907,7 @@
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>4277399.55</t>
         </is>
       </c>
       <c r="L702" t="inlineStr"/>
@@ -43931,17 +43915,13 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
-        </is>
-      </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>9507997</t>
-        </is>
-      </c>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -43951,12 +43931,12 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Restauração da interseção na Rodovia MGC-354, km 176,2, trecho: Av Marabá (Patos de Minas) - Entr BR 365</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>3773464.12</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -43966,7 +43946,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>3773464.12</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43981,26 +43961,18 @@
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>9289765.74</t>
-        </is>
-      </c>
-      <c r="L703" t="inlineStr">
-        <is>
-          <t>1301606 000002/2026</t>
-        </is>
-      </c>
+          <t>3773464.12</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
-        </is>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>9507997</t>
-        </is>
-      </c>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -44013,12 +43985,12 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Recuperação de erosão em talude de corte na Rodovia MGC-354, km 167,8, trecho: Ribeirão da Mata - Av Marabá (Patos de Minas)</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>209886.65</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -44028,7 +44000,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>209886.65</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -44043,24 +44015,20 @@
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>9289765.74</t>
-        </is>
-      </c>
-      <c r="L704" t="inlineStr">
-        <is>
-          <t>1301606 000002/2026</t>
-        </is>
-      </c>
+          <t>209886.65</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -44075,12 +44043,12 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Complementação obras melhoramentos e pavimentação, trecho Santa Rita do Itueto - Entr° BR-259 (Resplendor), rodovia AMG-2320, extensão de 13,400km</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -44090,7 +44058,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -44105,44 +44073,44 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>37600000</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -44152,7 +44120,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -44167,24 +44135,24 @@
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -44194,17 +44162,17 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -44214,59 +44182,59 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>98942.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>3156.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>47251056.25</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -44276,59 +44244,59 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>94619.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>3018.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>31605379.81</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44338,39 +44306,39 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>99429.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>3171.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>35890569</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -44380,17 +44348,17 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44400,39 +44368,39 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>236173.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>7533.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>23198826.14</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -44442,17 +44410,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44462,39 +44430,39 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>31997186.78</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44504,17 +44472,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44524,39 +44492,39 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98942.18</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3156.24</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47251056.25</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44566,17 +44534,17 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44586,39 +44554,39 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94619.15</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3018.34</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31605379.81</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44628,17 +44596,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44648,39 +44616,39 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99429.13</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3171.78</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35890569</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44690,57 +44658,61 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>1085396</t>
+          <t>236173.66</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>123110.02</t>
+          <t>7533.93</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>32018655.9</t>
+          <t>23198826.14</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
+          <t>DO-009482055/2025-L5</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>9482055</t>
+        </is>
+      </c>
       <c r="C716" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44748,17 +44720,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44768,33 +44740,41 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100813.18</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3215.93</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>14124998.39</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr"/>
+          <t>31997186.78</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C717" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44807,12 +44787,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44822,7 +44802,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44837,10 +44817,14 @@
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>1768342.65</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -44860,17 +44844,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44880,22 +44864,22 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
@@ -44907,12 +44891,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44922,17 +44906,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44942,39 +44926,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>204666.13</t>
+          <t>485014.38</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>6528.84</t>
+          <t>33558.09</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>35828532.09</t>
+          <t>13779736.44</t>
         </is>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44984,59 +44968,59 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2434106.96</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289651.76</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>30669944.94</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45046,17 +45030,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45066,41 +45050,37 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45108,17 +45088,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45128,39 +45108,35 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>1093860.13</t>
+          <t>90411.87</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>133799.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>23738603.08</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>1677930.78</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45170,17 +45146,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45190,39 +45166,39 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>442302.76</t>
+          <t>520822.24</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>51291.02</t>
+          <t>16614.21</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>33979775.59</t>
+          <t>35512375.98</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45232,17 +45208,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45252,87 +45228,451 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>2055531.14</t>
+          <t>520822.24</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>214571.53</t>
+          <t>16614.21</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>28547666.73</t>
+          <t>35512375.98</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>84001.16</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>2679.63</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>77814893.14</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr"/>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>1093860.13</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>133799.82</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>23738603.08</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>1529448.46</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>216118.92</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>32892629.89</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>2055531.14</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>214571.53</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>28547666.73</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr">
+      <c r="E731" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F725" t="inlineStr">
+      <c r="F731" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G725" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H725" t="inlineStr">
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I725" t="inlineStr">
-        <is>
-          <t>3122723.66</t>
-        </is>
-      </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>352855.67</t>
-        </is>
-      </c>
-      <c r="K725" t="inlineStr">
-        <is>
-          <t>28049810.92</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr">
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>3709418.34</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>447768.42</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>27463116.24</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -23535,17 +23535,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>30099564.8</t>
+          <t>30324593.57</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>1590840.45</t>
+          <t>1621494.03</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>6156338.77</t>
+          <t>5931310</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -23597,17 +23597,17 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>3323873.3</t>
+          <t>4891957.08</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>180663.59</t>
+          <t>314950.7</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>31011738.18</t>
+          <t>29443654.4</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -27813,17 +27813,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>371349.63</t>
+          <t>379999.19</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>47860.47</t>
+          <t>49193.36</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>1023560.54</t>
+          <t>1014910.98</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -29239,17 +29239,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>31846402.08</t>
+          <t>33079639.23</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>1523518.61</t>
+          <t>1598755.26</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>15788185.96</t>
+          <t>14554948.81</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>37433918.31</t>
+          <t>35353156.02</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>15724870.54</t>
+          <t>17805632.83</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29789,17 +29789,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>16100052.36</t>
+          <t>16613750.86</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>220109.24</t>
+          <t>246679.7</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>8307028.14</t>
+          <t>7793329.64</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30409,17 +30409,17 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>15678020.81</t>
+          <t>16864716.77</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>371802.99</t>
+          <t>406450.41</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>13277048.59</t>
+          <t>12090352.63</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30905,17 +30905,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>2228969.36</t>
+          <t>2590128.01</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>58718</t>
+          <t>71755.81</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>6918964.89</t>
+          <t>6557806.24</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31339,17 +31339,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>3889704.5</t>
+          <t>5493423.52</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>80510.37</t>
+          <t>118135.92</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>42029294.45</t>
+          <t>40425575.43</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -31897,17 +31897,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>1671073.29</t>
+          <t>1982867.2</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>50888.07</t>
+          <t>62143.81</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>7529714.58</t>
+          <t>7217920.67</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -33075,17 +33075,17 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>1826197.75</t>
+          <t>1830541.74</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>235418.42</t>
+          <t>236087.82</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>625414.59</t>
+          <t>621070.6</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -37291,17 +37291,17 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>32992827.05</t>
+          <t>33898181.2</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>1452411.3</t>
+          <t>1515085.1</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>14563963.21</t>
+          <t>13658609.06</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -37973,17 +37973,17 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>46516423.88</t>
+          <t>47974122.69</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>1395457.53</t>
+          <t>1540779.52</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>15305049.33</t>
+          <t>13847350.52</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -39089,17 +39089,17 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>27438666.59</t>
+          <t>27988715.04</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>343426.89</t>
+          <t>356282.35</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>4209337.76</t>
+          <t>3659289.31</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
@@ -39337,17 +39337,17 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>3668445.77</t>
+          <t>3864645.99</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>133016.83</t>
+          <t>146170.15</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>4747054.04</t>
+          <t>4550853.82</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
@@ -39399,17 +39399,17 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>3811147.4</t>
+          <t>4071228.78</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>125510.2</t>
+          <t>146736.4</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>965834.18</t>
+          <t>705752.8</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
@@ -39647,17 +39647,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>352010.15</t>
+          <t>443804.47</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>15314.77</t>
+          <t>23328.41</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>451361.24</t>
+          <t>359566.92</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -40693,17 +40693,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>1253158.75</t>
+          <t>1529552.24</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>40697.25</t>
+          <t>50675.04</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>7965313.74</t>
+          <t>7688920.25</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -40817,17 +40817,17 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>3334781.36</t>
+          <t>5686230.5</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>357089.45</t>
+          <t>593908.91</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>11370115.55</t>
+          <t>9018666.41</t>
         </is>
       </c>
       <c r="L652" t="inlineStr">
@@ -40879,17 +40879,17 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>2671611.78</t>
+          <t>3406303.37</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>207169.47</t>
+          <t>262833.76</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>9731418.09</t>
+          <t>8996726.5</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -40941,17 +40941,17 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>366122.67</t>
+          <t>486318.7</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>9783.8</t>
+          <t>13618.05</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>2258786.42</t>
+          <t>2138590.39</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
@@ -41065,17 +41065,17 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>2076298.69</t>
+          <t>2952899.09</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>192219.5</t>
+          <t>286623.48</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>12640903.29</t>
+          <t>11764302.89</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
@@ -41313,17 +41313,17 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>1225033.21</t>
+          <t>2605666.71</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>54549.02</t>
+          <t>80545.16</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>56242570.54</t>
+          <t>54861937.04</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
@@ -41437,17 +41437,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>484650.83</t>
+          <t>651822.35</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>15460.35</t>
+          <t>20793.12</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>2543398.13</t>
+          <t>2376226.61</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -41933,17 +41933,17 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>269098.43</t>
+          <t>368180.22</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>8584.22</t>
+          <t>11744.92</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>4055187.25</t>
+          <t>3956105.46</t>
         </is>
       </c>
       <c r="L670" t="inlineStr">
@@ -42543,12 +42543,12 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>5760127.9</t>
+          <t>5760127.67</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42563,7 +42563,7 @@
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>5760127.9</t>
+          <t>5760127.67</t>
         </is>
       </c>
       <c r="L680" t="inlineStr">
@@ -42615,7 +42615,7 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>754828.33</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -42625,7 +42625,7 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>19798000</t>
+          <t>19043171.67</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
@@ -43723,17 +43723,17 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>998910.01</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96764.76</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>42542200.39</t>
+          <t>41543290.38</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L731"/>
+  <dimension ref="A1:L727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6595470.42</t>
+          <t>6724996.26</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>7640597.15</t>
+          <t>7808493.21</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>890004.45</t>
+          <t>760478.61</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -28929,17 +28929,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>2485734.75</t>
+          <t>2588346.4</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>209371.92</t>
+          <t>222629.34</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>859964.38</t>
+          <t>757352.73</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29549,17 +29549,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>705045.28</t>
+          <t>715056.82</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>27373.27</t>
+          <t>28116.12</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>154723.73</t>
+          <t>144712.19</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -30223,17 +30223,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>678573.03</t>
+          <t>684184.78</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>30945.93</t>
+          <t>31362.32</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>246111.39</t>
+          <t>240499.64</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -30471,17 +30471,17 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>2282985.62</t>
+          <t>2439813.51</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>102303.87</t>
+          <t>107940.93</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>27293193.79</t>
+          <t>27136365.9</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -30719,17 +30719,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>4925478.97</t>
+          <t>5503746.21</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>133432.55</t>
+          <t>154307.98</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>25946593.33</t>
+          <t>25368326.09</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -31215,17 +31215,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>35442897.44</t>
+          <t>47234608.96</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>553588.77</t>
+          <t>738396.06</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>145966117.56</t>
+          <t>134174406.04</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -31401,17 +31401,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>5546633.76</t>
+          <t>5964256.69</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>110994.77</t>
+          <t>122008.42</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4087492.48</t>
+          <t>3669869.55</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -31525,17 +31525,17 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>377721.68</t>
+          <t>474332.25</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>10474.18</t>
+          <t>13961.82</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>5526225.81</t>
+          <t>5429615.24</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -31587,17 +31587,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>152236.05</t>
+          <t>203500.85</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>4579.16</t>
+          <t>6429.81</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>1000138.2</t>
+          <t>948873.4</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -31711,17 +31711,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>7635030.52</t>
+          <t>8001489.7</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>29661.44</t>
+          <t>38040.64</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>6983969.48</t>
+          <t>6617510.3</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -37849,17 +37849,17 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>986664.68</t>
+          <t>1003176.58</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>43574.78</t>
+          <t>44799.96</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>498116.14</t>
+          <t>481604.24</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -38035,7 +38035,7 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>5041293.17</t>
+          <t>5087668.17</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>4843937.65</t>
+          <t>4797562.65</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -39647,17 +39647,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>443804.47</t>
+          <t>467301.3</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>23328.41</t>
+          <t>25379.68</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>359566.92</t>
+          <t>336070.09</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -41127,17 +41127,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>3178378.52</t>
+          <t>3991099.03</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>677291.89</t>
+          <t>850480.61</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>24816004.51</t>
+          <t>24003284</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -41251,17 +41251,17 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>3731967.69</t>
+          <t>4520277.95</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>792028.13</t>
+          <t>959356.12</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>15017964.08</t>
+          <t>14229653.82</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -41375,17 +41375,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>1369796.14</t>
+          <t>1624332.96</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>294153.53</t>
+          <t>348817.13</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>13559550.81</t>
+          <t>13305013.99</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>1110292.85</t>
+          <t>1735990.26</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>236825.56</t>
+          <t>370302.69</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>23382430.31</t>
+          <t>22756732.9</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41809,17 +41809,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>478613.8</t>
+          <t>768085.73</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>101466.03</t>
+          <t>162834.04</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>8828016.4</t>
+          <t>8538544.47</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -41871,17 +41871,17 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>333054.32</t>
+          <t>478830.48</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>10624.42</t>
+          <t>15274.67</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>2854484.84</t>
+          <t>2708708.68</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
@@ -41995,17 +41995,17 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>1551053.42</t>
+          <t>2857130.14</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>44779.27</t>
+          <t>68579.53</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>18573946.58</t>
+          <t>17267869.86</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -42057,17 +42057,17 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>1361505.52</t>
+          <t>1777707.89</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>60143.35</t>
+          <t>75112.42</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>58528494.06</t>
+          <t>58112291.69</t>
         </is>
       </c>
       <c r="L672" t="inlineStr">
@@ -42119,17 +42119,17 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>470619.49</t>
+          <t>646153.82</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>15012.75</t>
+          <t>20612.29</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>6206784.84</t>
+          <t>6031250.51</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
@@ -42702,7 +42702,11 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr"/>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
       <c r="C683" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -42748,7 +42752,11 @@
           <t>11358610.11</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr"/>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>2301762 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -43227,7 +43235,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>112220.23</t>
+          <t>249842.9</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -43237,7 +43245,7 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>5230362.65</t>
+          <t>5092739.98</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -43599,17 +43607,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>123432.43</t>
+          <t>336759.53</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>62987.56</t>
+          <t>183730.69</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>4383285.63</t>
+          <t>4169958.53</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -43810,7 +43818,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C701" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -43856,7 +43868,11 @@
           <t>7919248.4</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr"/>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -43864,7 +43880,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43910,7 +43930,11 @@
           <t>4277399.55</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr"/>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -43918,7 +43942,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -43964,7 +43992,11 @@
           <t>3773464.12</t>
         </is>
       </c>
-      <c r="L703" t="inlineStr"/>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -43972,7 +44004,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C704" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -44018,7 +44054,11 @@
           <t>209886.65</t>
         </is>
       </c>
-      <c r="L704" t="inlineStr"/>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -44125,17 +44165,17 @@
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87823.31</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29008.03</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>1011901.12</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
@@ -44281,7 +44321,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -44291,12 +44331,12 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44306,7 +44346,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -44321,7 +44361,7 @@
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="L709" t="inlineStr">
@@ -44333,12 +44373,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -44348,17 +44388,17 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44368,39 +44408,39 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167084.18</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5329.96</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>47182914.25</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -44410,17 +44450,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44430,39 +44470,39 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159783.86</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5097.09</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>31540215.1</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -44477,12 +44517,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44492,22 +44532,22 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>98942.18</t>
+          <t>167906.5</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>3156.24</t>
+          <t>5356.2</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>47251056.25</t>
+          <t>35822091.63</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -44519,12 +44559,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44539,12 +44579,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44554,22 +44594,22 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>94619.15</t>
+          <t>594602.84</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>3018.34</t>
+          <t>18967.82</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>31605379.81</t>
+          <t>22840396.96</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -44581,12 +44621,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44601,12 +44641,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44616,22 +44656,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>99429.13</t>
+          <t>100813.18</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>3171.78</t>
+          <t>3215.93</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>35890569</t>
+          <t>31997186.78</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44643,12 +44683,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44658,17 +44698,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44678,39 +44718,39 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>236173.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>7533.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>23198826.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44720,17 +44760,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44740,39 +44780,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>485014.38</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>33558.09</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>31997186.78</t>
+          <t>13779736.44</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44782,59 +44822,59 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2434106.96</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289651.76</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30669944.94</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44844,17 +44884,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44864,7 +44904,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44879,26 +44919,22 @@
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>9497685</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44906,17 +44942,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44926,39 +44962,35 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>485014.38</t>
+          <t>180823.74</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>33558.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>13779736.44</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr">
-        <is>
-          <t>2301762 000023/2025</t>
-        </is>
-      </c>
+          <t>1587518.91</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44968,59 +45000,59 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>2434106.96</t>
+          <t>883000.37</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>289651.76</t>
+          <t>28167.69</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>30669944.94</t>
+          <t>35150197.85</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45030,17 +45062,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45050,7 +45082,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -45065,22 +45097,26 @@
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr"/>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
       <c r="C722" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45088,17 +45124,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45108,35 +45144,39 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>90411.87</t>
+          <t>138602.75</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4421.42</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>1677930.78</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr"/>
+          <t>77760291.55</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45146,17 +45186,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45166,39 +45206,39 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>520822.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>16614.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>35512375.98</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45208,17 +45248,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45228,39 +45268,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>520822.24</t>
+          <t>1093860.13</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>16614.21</t>
+          <t>133799.82</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>35512375.98</t>
+          <t>23738603.08</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45270,17 +45310,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45290,39 +45330,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1529448.46</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>216118.92</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32892629.89</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45332,17 +45372,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45352,37 +45392,41 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>30603197.87</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>84001.16</t>
+          <t>2055531.14</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2679.63</t>
+          <t>214571.53</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>77814893.14</t>
+          <t>28547666.73</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B727" t="inlineStr"/>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
       <c r="C727" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45395,12 +45439,12 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -45410,269 +45454,25 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>31172534.58</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3709418.34</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447768.42</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>44002130</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr"/>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
-        <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E728" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
-        </is>
-      </c>
-      <c r="F728" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="G728" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>24832463.21</t>
-        </is>
-      </c>
-      <c r="I728" t="inlineStr">
-        <is>
-          <t>1093860.13</t>
-        </is>
-      </c>
-      <c r="J728" t="inlineStr">
-        <is>
-          <t>133799.82</t>
-        </is>
-      </c>
-      <c r="K728" t="inlineStr">
-        <is>
-          <t>23738603.08</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
-        <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
-        </is>
-      </c>
-      <c r="F729" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="G729" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>34422078.35</t>
-        </is>
-      </c>
-      <c r="I729" t="inlineStr">
-        <is>
-          <t>1529448.46</t>
-        </is>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>216118.92</t>
-        </is>
-      </c>
-      <c r="K729" t="inlineStr">
-        <is>
-          <t>32892629.89</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
-        <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
-        </is>
-      </c>
-      <c r="F730" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="G730" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>30603197.87</t>
-        </is>
-      </c>
-      <c r="I730" t="inlineStr">
-        <is>
-          <t>2055531.14</t>
-        </is>
-      </c>
-      <c r="J730" t="inlineStr">
-        <is>
-          <t>214571.53</t>
-        </is>
-      </c>
-      <c r="K730" t="inlineStr">
-        <is>
-          <t>28547666.73</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
-        <is>
-          <t>DM-008/2024-A</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>9422064</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>Manutenção Rodoviária</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
-        </is>
-      </c>
-      <c r="F731" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H731" t="inlineStr">
-        <is>
-          <t>31172534.58</t>
-        </is>
-      </c>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>3709418.34</t>
-        </is>
-      </c>
-      <c r="J731" t="inlineStr">
-        <is>
-          <t>447768.42</t>
-        </is>
-      </c>
-      <c r="K731" t="inlineStr">
-        <is>
           <t>27463116.24</t>
         </is>
       </c>
-      <c r="L731" t="inlineStr">
+      <c r="L727" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L727"/>
+  <dimension ref="A1:L731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26263,17 +26263,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>4472200.27</t>
+          <t>4580601.22</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>456904.48</t>
+          <t>472329.91</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>3104721.83</t>
+          <t>2996320.88</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -29053,17 +29053,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>43658709.16</t>
+          <t>44421190.56</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>1639945.68</t>
+          <t>1697795.98</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>6598044.38</t>
+          <t>5835562.98</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -29363,17 +29363,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>35353156.02</t>
+          <t>37433918.31</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>1631513.09</t>
+          <t>1779865.91</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>17805632.83</t>
+          <t>15724870.54</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -30285,17 +30285,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>4059210.05</t>
+          <t>5025826.6</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>108617.7</t>
+          <t>135089.76</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>3050463.1</t>
+          <t>2083846.55</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30347,17 +30347,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>41509825.74</t>
+          <t>47268489.9</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>1230592.5</t>
+          <t>1390431.21</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>10729822.19</t>
+          <t>4971158.03</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -30399,12 +30399,12 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>3973616.9</t>
+          <t>5770491.09</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>28955069.4</t>
+          <t>30751943.59</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>12090352.63</t>
+          <t>13887226.82</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30657,17 +30657,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>37813731.11</t>
+          <t>38208071.57</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>549433.12</t>
+          <t>561423.69</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>5975624.77</t>
+          <t>5581284.31</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -31029,17 +31029,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>2499057.24</t>
+          <t>3122251.79</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>72046.7</t>
+          <t>94544</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>19959849.46</t>
+          <t>19336654.91</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31329,12 +31329,12 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440912.38</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>45918998.95</t>
+          <t>46359911.33</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31349,7 +31349,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>40425575.43</t>
+          <t>40866487.81</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -35793,12 +35793,12 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>9534505.1</t>
+          <t>14807719.89</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>75282924.23</t>
+          <t>80556139.02</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35813,7 +35813,7 @@
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>16550207.41</t>
+          <t>21823422.2</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
@@ -38965,17 +38965,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>24578876.25</t>
+          <t>33707081.69</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>683991.5</t>
+          <t>927538.71</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>14755695.74</t>
+          <t>5627490.3</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -39027,17 +39027,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>254883.93</t>
+          <t>322107.18</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>13463.55</t>
+          <t>18451.5</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>1991213.67</t>
+          <t>1923990.42</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -39523,17 +39523,17 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>198591.25</t>
+          <t>209714.4</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>10354.88</t>
+          <t>11180.21</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>1147755.21</t>
+          <t>1136632.06</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -40205,17 +40205,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>10061390.16</t>
+          <t>10462255.46</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>191977.36</t>
+          <t>199968.05</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>41753185.28</t>
+          <t>41352319.98</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -41003,17 +41003,17 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>3995405.43</t>
+          <t>4842504.05</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>852669.83</t>
+          <t>1033446.24</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>18172425.04</t>
+          <t>17325326.42</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -41499,17 +41499,17 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>4876229.77</t>
+          <t>6003549.84</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>468624.36</t>
+          <t>587462.18</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>10428766.42</t>
+          <t>9301446.35</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -41623,17 +41623,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>7129092.83</t>
+          <t>8072464.42</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>296100.03</t>
+          <t>342147.52</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>3800882.73</t>
+          <t>2857511.14</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
@@ -41747,17 +41747,17 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>23874408.23</t>
+          <t>30738580.11</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>357219.59</t>
+          <t>654392.01</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>18110169.88</t>
+          <t>11245998</t>
         </is>
       </c>
       <c r="L667" t="inlineStr">
@@ -41985,12 +41985,12 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1362538.79</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>20125000</t>
+          <t>21487538.79</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -42005,7 +42005,7 @@
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>17267869.86</t>
+          <t>18630408.65</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -42305,17 +42305,17 @@
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>3730159.05</t>
+          <t>4130041.06</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>489500.96</t>
+          <t>532522.66</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>9460833.84</t>
+          <t>9060951.83</t>
         </is>
       </c>
       <c r="L676" t="inlineStr">
@@ -43173,17 +43173,17 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>2293831.31</t>
+          <t>3110884.79</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>207512.68</t>
+          <t>275977.49</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>34660343.66</t>
+          <t>33843290.18</t>
         </is>
       </c>
       <c r="L690" t="inlineStr">
@@ -43297,17 +43297,17 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>978088.35</t>
+          <t>1525125.07</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>107753.76</t>
+          <t>162712.84</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>32226974.05</t>
+          <t>31679937.33</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
@@ -44165,17 +44165,17 @@
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>87823.31</t>
+          <t>175646.62</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>29008.03</t>
+          <t>58016.06</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>1011901.12</t>
+          <t>924077.81</t>
         </is>
       </c>
       <c r="L706" t="inlineStr">
@@ -44373,32 +44373,32 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44408,41 +44408,37 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>167084.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>5329.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>47182914.25</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
-        </is>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>9493205</t>
-        </is>
-      </c>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr"/>
       <c r="C711" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44450,17 +44446,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44470,59 +44466,55 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>159783.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>5097.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>31540215.1</t>
-        </is>
-      </c>
-      <c r="L711" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>4742883</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44532,39 +44524,39 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>167906.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>5356.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>35822091.63</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -44574,17 +44566,17 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44594,39 +44586,39 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>594602.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>18967.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>22840396.96</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44641,12 +44633,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44656,22 +44648,22 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>100813.18</t>
+          <t>167084.18</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>3215.93</t>
+          <t>5329.96</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>31997186.78</t>
+          <t>47182914.25</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -44683,12 +44675,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44698,17 +44690,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44718,39 +44710,39 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159783.86</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5097.09</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31540215.1</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44760,17 +44752,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44780,39 +44772,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>485014.38</t>
+          <t>167906.5</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>33558.09</t>
+          <t>5356.2</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>13779736.44</t>
+          <t>35822091.63</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44822,59 +44814,59 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>2434106.96</t>
+          <t>594602.84</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>289651.76</t>
+          <t>18967.82</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>30669944.94</t>
+          <t>22840396.96</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -44884,17 +44876,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44904,37 +44896,41 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100813.18</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3215.93</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>31997186.78</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B719" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C719" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44947,12 +44943,12 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44962,12 +44958,12 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>180823.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
@@ -44977,20 +44973,24 @@
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>1587518.91</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -45000,17 +45000,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -45020,39 +45020,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>883000.37</t>
+          <t>485014.38</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>28167.69</t>
+          <t>33558.09</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>35150197.85</t>
+          <t>13779736.44</t>
         </is>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45062,59 +45062,59 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2434106.96</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289651.76</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>30669944.94</t>
         </is>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45124,17 +45124,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45144,41 +45144,37 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>138602.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>4421.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>77760291.55</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>9512043</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45186,17 +45182,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45206,12 +45202,12 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180823.74</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
@@ -45221,24 +45217,20 @@
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>44002130</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>2301762 000004/2026</t>
-        </is>
-      </c>
+          <t>1587518.91</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45248,17 +45240,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45268,39 +45260,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>1093860.13</t>
+          <t>883000.37</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>133799.82</t>
+          <t>28167.69</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>23738603.08</t>
+          <t>35150197.85</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45310,17 +45302,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45330,39 +45322,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>1529448.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>216118.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>32892629.89</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45372,17 +45364,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45392,87 +45384,335 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>2055531.14</t>
+          <t>138602.75</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>214571.53</t>
+          <t>4421.42</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>28547666.73</t>
+          <t>77760291.55</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>2301762 000004/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>1549222.57</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>209376.64</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>23283240.64</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>1529448.46</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>216118.92</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>32892629.89</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>2410184.11</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>274971.65</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>28193013.76</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B731" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr">
+      <c r="E731" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F727" t="inlineStr">
+      <c r="F731" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H727" t="inlineStr">
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I727" t="inlineStr">
+      <c r="I731" t="inlineStr">
         <is>
           <t>3709418.34</t>
         </is>
       </c>
-      <c r="J727" t="inlineStr">
+      <c r="J731" t="inlineStr">
         <is>
           <t>447768.42</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr">
+      <c r="K731" t="inlineStr">
         <is>
           <t>27463116.24</t>
         </is>
       </c>
-      <c r="L727" t="inlineStr">
+      <c r="L731" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L731"/>
+  <dimension ref="A1:L732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23535,17 +23535,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>30324593.57</t>
+          <t>30430293.24</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>1621494.03</t>
+          <t>1629953.97</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>5931310</t>
+          <t>5825610.33</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -23597,17 +23597,17 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>4891957.08</t>
+          <t>5313643.48</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>314950.7</t>
+          <t>354762.9</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>29443654.4</t>
+          <t>29021968</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -26201,17 +26201,17 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>8514031.87</t>
+          <t>9245263.81</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>552492.78</t>
+          <t>606927.57</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>1293904.59</t>
+          <t>562672.65</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -27627,17 +27627,17 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>1177999.68</t>
+          <t>1249934.4</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>73492.97</t>
+          <t>80657.66</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>235415.12</t>
+          <t>163480.4</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -28929,17 +28929,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>2588346.4</t>
+          <t>2686956.24</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>222629.34</t>
+          <t>235369.73</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>757352.73</t>
+          <t>658742.89</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29239,17 +29239,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>33079639.23</t>
+          <t>33654947.6</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>1598755.26</t>
+          <t>1642467.09</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>14554948.81</t>
+          <t>13979640.44</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29363,17 +29363,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>37433918.31</t>
+          <t>39027703.34</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>1779865.91</t>
+          <t>1891474.74</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>15724870.54</t>
+          <t>14131085.51</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29425,17 +29425,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>22583302.95</t>
+          <t>23306725.44</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>1151934.58</t>
+          <t>1205445.2</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>23185643.5</t>
+          <t>22462221.01</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29487,17 +29487,17 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>31316238.1</t>
+          <t>32540557.03</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>1471522.11</t>
+          <t>1571471.61</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>16842367.11</t>
+          <t>15618048.18</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -29727,17 +29727,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>2789988.76</t>
+          <t>3186430.4</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>117571.97</t>
+          <t>137830.13</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>8192413.01</t>
+          <t>7795971.37</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -29913,17 +29913,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>76206166.6</t>
+          <t>81374691.06</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>3184891.93</t>
+          <t>3437170.5</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>75970063.13</t>
+          <t>70801538.67</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30471,17 +30471,17 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>2439813.51</t>
+          <t>2504228.1</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>107940.93</t>
+          <t>109818.76</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>27136365.9</t>
+          <t>27071951.31</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -30533,17 +30533,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>32208027.4</t>
+          <t>40389382.05</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>2039206.85</t>
+          <t>2872215.34</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>63453645.53</t>
+          <t>55272290.88</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -30781,17 +30781,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>2904800.14</t>
+          <t>3229362.49</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>821885.87</t>
+          <t>930086.32</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>7459311.33</t>
+          <t>7134748.98</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -30905,17 +30905,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>2590128.01</t>
+          <t>2935575.13</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>71755.81</t>
+          <t>84226.44</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>6557806.24</t>
+          <t>6212359.12</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -30967,17 +30967,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>5728167.91</t>
+          <t>6598239.8</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>92366.17</t>
+          <t>112652.65</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>38844832.09</t>
+          <t>37974760.2</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31215,17 +31215,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>47234608.96</t>
+          <t>59591534.81</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>738396.06</t>
+          <t>1034658.04</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>134174406.04</t>
+          <t>121817480.19</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -31453,12 +31453,12 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1982368.8</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>21429526.4</t>
+          <t>23411895.2</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31473,7 +31473,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>17680461.43</t>
+          <t>19662830.23</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31587,17 +31587,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>203500.85</t>
+          <t>210644.38</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>6429.81</t>
+          <t>6687.69</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>948873.4</t>
+          <t>941729.87</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -31711,17 +31711,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>8001489.7</t>
+          <t>8226554.46</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>38040.64</t>
+          <t>42694.38</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>6617510.3</t>
+          <t>6392445.54</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -31773,17 +31773,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>5027911.86</t>
+          <t>5756594.74</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>92979.92</t>
+          <t>116224.9</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>16832574.54</t>
+          <t>16103891.66</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -31897,17 +31897,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>1982867.2</t>
+          <t>2292488.1</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>62143.81</t>
+          <t>73321.11</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>7217920.67</t>
+          <t>6908299.77</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -32021,17 +32021,17 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>172556.71</t>
+          <t>204409.85</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>10888.3</t>
+          <t>12898.23</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>1914026.81</t>
+          <t>1882173.67</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -35803,17 +35803,17 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>58732716.82</t>
+          <t>61906101.85</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>3614380.02</t>
+          <t>3873327.65</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>21823422.2</t>
+          <t>18650037.17</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
@@ -37415,17 +37415,17 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>26478243.14</t>
+          <t>27204370.02</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>1453592.1</t>
+          <t>1509691.5</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>24855512.19</t>
+          <t>24129385.31</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
@@ -37663,17 +37663,17 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>33019188.67</t>
+          <t>35714973.58</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>1495979.22</t>
+          <t>1671479.62</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>14739644.56</t>
+          <t>12043859.65</t>
         </is>
       </c>
       <c r="L601" t="inlineStr">
@@ -38779,17 +38779,17 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>1809547.16</t>
+          <t>2653334.37</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>118361.06</t>
+          <t>190638.71</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>3108253.27</t>
+          <t>2264466.06</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -39151,17 +39151,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>317335.77</t>
+          <t>379059.92</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>31469.36</t>
+          <t>39666.32</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>9342661.31</t>
+          <t>9280937.16</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -39275,17 +39275,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>2227471.49</t>
+          <t>2371518.36</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>97506.22</t>
+          <t>106638.79</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>3547280.95</t>
+          <t>3403234.08</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -39337,17 +39337,17 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>3864645.99</t>
+          <t>4231364.19</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>146170.15</t>
+          <t>173272.84</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>4550853.82</t>
+          <t>4184135.62</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
@@ -39709,17 +39709,17 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>5255390.3</t>
+          <t>5811950.9</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>1484860.68</t>
+          <t>1670269.09</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>8678658.08</t>
+          <t>8122097.48</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -39771,17 +39771,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>2984078.68</t>
+          <t>3336765.92</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>846058.74</t>
+          <t>963689.45</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>6120818.73</t>
+          <t>5768131.49</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
@@ -39833,17 +39833,17 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>4700012.81</t>
+          <t>5212533.2</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>1327844.46</t>
+          <t>1498552.75</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>10576728.28</t>
+          <t>10064207.89</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -40267,17 +40267,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>7434834.03</t>
+          <t>9044532.78</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>76419.87</t>
+          <t>113240.03</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>43525915.35</t>
+          <t>41916216.6</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -40329,17 +40329,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>15916258.01</t>
+          <t>20009499.71</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>312586.36</t>
+          <t>410438.09</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>37440533.71</t>
+          <t>33347292.01</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -40391,17 +40391,17 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>14534993.85</t>
+          <t>15049515.51</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>226029.9</t>
+          <t>233018.53</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>38706880.53</t>
+          <t>38192358.87</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -40453,17 +40453,17 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>27755030.86</t>
+          <t>30099472.8</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>297185.39</t>
+          <t>342497.01</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>31544364.11</t>
+          <t>29199922.17</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -40515,17 +40515,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>17034916.84</t>
+          <t>25157250.25</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>286639.5</t>
+          <t>498167.22</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>36539083.15</t>
+          <t>28416749.74</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -40635,17 +40635,17 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>2251277.05</t>
+          <t>2643626.87</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>67379.88</t>
+          <t>81543.69</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>7033131.81</t>
+          <t>6640781.99</t>
         </is>
       </c>
       <c r="L649" t="inlineStr"/>
@@ -40693,17 +40693,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>1529552.24</t>
+          <t>1807108.52</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>50675.04</t>
+          <t>60694.81</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>7688920.25</t>
+          <t>7411363.97</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -40755,17 +40755,17 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>6245920.11</t>
+          <t>8404927.7</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>155918.68</t>
+          <t>210463.27</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>58738385.23</t>
+          <t>56579377.64</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -40879,17 +40879,17 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>3406303.37</t>
+          <t>4482078.41</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>262833.76</t>
+          <t>336226.99</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>8996726.5</t>
+          <t>7920951.46</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -40941,17 +40941,17 @@
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>486318.7</t>
+          <t>607771.44</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>13618.05</t>
+          <t>17492.39</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>2138590.39</t>
+          <t>2017137.65</t>
         </is>
       </c>
       <c r="L654" t="inlineStr">
@@ -41127,17 +41127,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>3991099.03</t>
+          <t>4799556.95</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>850480.61</t>
+          <t>1022765.69</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>24003284</t>
+          <t>23194826.08</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -41251,17 +41251,17 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>4520277.95</t>
+          <t>5317792.5</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>959356.12</t>
+          <t>1128109.25</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>14229653.82</t>
+          <t>13432139.27</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -41561,17 +41561,17 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>2570759.32</t>
+          <t>4443636.11</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>6664.72</t>
+          <t>95147.28</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>3628970.44</t>
+          <t>1756093.65</t>
         </is>
       </c>
       <c r="L664" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>1735990.26</t>
+          <t>2366973.95</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>370302.69</t>
+          <t>504865.43</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>22756732.9</t>
+          <t>22125749.21</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41809,17 +41809,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>768085.73</t>
+          <t>1051785.7</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>162834.04</t>
+          <t>222978.39</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>8538544.47</t>
+          <t>8254844.5</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -41933,17 +41933,17 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>368180.22</t>
+          <t>467262.01</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>11744.92</t>
+          <t>14905.62</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>3956105.46</t>
+          <t>3857023.67</t>
         </is>
       </c>
       <c r="L670" t="inlineStr">
@@ -42925,17 +42925,17 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>1167399.12</t>
+          <t>1805778.44</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>22971.73</t>
+          <t>46527.92</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>21885283.56</t>
+          <t>21246904.24</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -43111,17 +43111,17 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>839183.28</t>
+          <t>1190171.64</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>116266.05</t>
+          <t>175729.77</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>28463755.84</t>
+          <t>28112767.48</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -43545,17 +43545,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>850758.92</t>
+          <t>1168021.94</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>92437.35</t>
+          <t>126740.8</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>30962575.23</t>
+          <t>30645312.21</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -43731,17 +43731,17 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>998910.01</t>
+          <t>1521198.62</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>96764.76</t>
+          <t>155019.55</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>41543290.38</t>
+          <t>41021001.77</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">
@@ -43793,17 +43793,17 @@
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>708590.2</t>
+          <t>1547216.89</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>78030.21</t>
+          <t>157887.02</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>33789184.92</t>
+          <t>32950558.23</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -45109,14 +45109,10 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>9500304</t>
-        </is>
-      </c>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45124,17 +45120,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45144,7 +45140,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -45159,22 +45155,22 @@
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>14124998.39</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>2301762 000027/2025</t>
-        </is>
-      </c>
+          <t>120800000</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B723" t="inlineStr"/>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
       <c r="C723" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45182,17 +45178,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45202,12 +45198,12 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>180823.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
@@ -45217,22 +45213,22 @@
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>1587518.91</t>
-        </is>
-      </c>
-      <c r="L723" t="inlineStr"/>
+          <t>14124998.39</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>2301762 000027/2025</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45240,17 +45236,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45260,39 +45256,35 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>883000.37</t>
+          <t>180823.74</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>28167.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>35150197.85</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>1587518.91</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45302,59 +45294,59 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>883000.37</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28167.69</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36281731.86</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45369,12 +45361,12 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45384,22 +45376,22 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>138602.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>4421.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>77760291.55</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
@@ -45411,12 +45403,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45426,17 +45418,17 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -45446,39 +45438,39 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138602.75</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4421.42</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>77760291.55</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -45493,12 +45485,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45508,39 +45500,39 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>1549222.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>209376.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>23283240.64</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -45555,12 +45547,12 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45570,22 +45562,22 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>1529448.46</t>
+          <t>1549222.57</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>216118.92</t>
+          <t>209376.64</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>32892629.89</t>
+          <t>23283240.64</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -45597,12 +45589,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -45617,12 +45609,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45632,22 +45624,22 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>2410184.11</t>
+          <t>2345896.62</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>274971.65</t>
+          <t>337318.43</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>28193013.76</t>
+          <t>32076181.73</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
@@ -45659,60 +45651,122 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>2410184.11</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>274971.65</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>28193013.76</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
+      <c r="B732" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D731" t="inlineStr">
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E731" t="inlineStr">
+      <c r="E732" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F731" t="inlineStr">
+      <c r="F732" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G731" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H731" t="inlineStr">
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t>3709418.34</t>
-        </is>
-      </c>
-      <c r="J731" t="inlineStr">
-        <is>
-          <t>447768.42</t>
-        </is>
-      </c>
-      <c r="K731" t="inlineStr">
-        <is>
-          <t>27463116.24</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr">
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>4215392.16</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>531866.62</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>26957142.42</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>
